--- a/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v7.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v7.xlsx
@@ -648,12 +648,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Elicits others’ views and opinions to develop and refine ideas.</t>
+          <t>Elicits others’ views and integrates feedback to refine ideas during collaborative discussions.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>active listening, stakeholder engagement, feedback, communication, empathy</t>
+          <t>active listening, stakeholder engagement, feedback, communication, collaboration</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="AH2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
@@ -815,12 +815,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Compares project concepts against industry best‑practice examples of similar products in terms of alignment with recognised standards.</t>
+          <t>Compares project concepts against industry best‑practice examples of similar products to identify improvement opportunities.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>benchmarking, best practice, performance metrics, competitive analysis, industry standards</t>
+          <t>benchmarking, best practice examples, similar products, performance metrics, industry standards</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -935,15 +935,15 @@
         </is>
       </c>
       <c r="AH3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>benchmarking, best practice, performance metrics, competitive analysis, industry standards</t>
+        </is>
+      </c>
+      <c r="AJ3" t="b">
         <v>1</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>benchmarking, best practice, performance metrics, competitive analysis, industry standards</t>
-        </is>
-      </c>
-      <c r="AJ3" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -982,12 +982,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Brainstorms ideas to address the identified issue.</t>
+          <t>Generates diverse solutions by leading focused brainstorming sessions to address identified issues.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>brainstorm ideas, ideation, creative problem solving, mind mapping, group facilitation</t>
+          <t>ideation, brainstorming, idea generation, creative problem solving, group facilitation</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="AH4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>analytical processes, systematic evaluation, concept feasibility, design thinking, ideation processes</t>
+          <t>systematic analytical processes, concept evaluation, feasibility analysis, design thinking, ideation processes</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name uses "Planning" but evidence describes gathering and evaluating concepts, not planning</t>
+          <t>MIS re-refinement: Skill name uses 'Planning' but evidence describes gathering and evaluating concepts, not planning</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Skill name uses "Planning" but evidence describes gathering and evaluating concepts, not planning</t>
+          <t>Skill name uses 'Planning' but evidence describes gathering and evaluating concepts, not planning</t>
         </is>
       </c>
       <c r="AF5" t="b">
@@ -1328,12 +1328,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Uses creative thinking techniques to generate innovative solutions to workplace challenges.</t>
+          <t>Applies creative thinking techniques to develop innovative solutions to workplace challenges.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ideation, innovation, brainstorming, design thinking, problem solving</t>
+          <t>creative thinking techniques, ideation, innovation, brainstorming, design thinking</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1436,15 +1436,15 @@
         </is>
       </c>
       <c r="AH6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>ideation, innovation, brainstorming, design thinking, problem solving</t>
+        </is>
+      </c>
+      <c r="AJ6" t="b">
         <v>1</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>ideation, innovation, brainstorming, design thinking, problem solving</t>
-        </is>
-      </c>
-      <c r="AJ6" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Documents feedback in accordance with organisational requirements to maintain accurate, consistent and compliant records for future reference.</t>
+          <t>Records and formats feedback in line with organisational standards to ensure consistent documentation.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="AH7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Evaluates ideas by systematically comparing them against identified factors affecting viability.</t>
+          <t>Assesses ideas by systematically comparing them against identified viability factors.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="AH8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
@@ -1805,12 +1805,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Selects an issue to be explored, consulting relevant personnel to ensure appropriate focus within the project scope.</t>
+          <t>Collaborates with relevant personnel to identify and select consultation issues for focused analysis.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>stakeholder engagement, problem identification, needs assessment, consultation processes, active listening</t>
+          <t>stakeholder engagement, issue selection, consultation processes, problem identification, decision‑making</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="AH9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Prepares proposals and plans for relevant stakeholders incorporating appropriate vocabulary.</t>
+          <t>Drafts detailed proposals and plans using sector‑specific terminology for stakeholder review.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2055,7 +2055,7 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="AH10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
@@ -2131,12 +2131,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Researches relevant information on possible solutions to the identified issue to support decision‑making within organisational guidelines.</t>
+          <t>Gathers and evaluates relevant data to identify viable solutions to the identified issue.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>literature review, data collection, search strategies, online databases, evidence‑based analysis</t>
+          <t>literature review, search strategies, online databases, evidence‑based analysis, possible solutions</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -2243,15 +2243,15 @@
         </is>
       </c>
       <c r="AH11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>literature review, data collection, search strategies, online databases, evidence‑based analysis</t>
+        </is>
+      </c>
+      <c r="AJ11" t="b">
         <v>1</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>literature review, data collection, search strategies, online databases, evidence‑based analysis</t>
-        </is>
-      </c>
-      <c r="AJ11" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Selects the most appropriate solution format and presents a tailored solution to stakeholders for decision‑making.</t>
+          <t>Selects appropriate solution formats and delivers tailored presentations to stakeholders.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>stakeholder communication, visual presentation tools, solution pitching, format selection, business briefings</t>
+          <t>solution presentation, stakeholder communication, format selection, visual presentation tools, business briefings</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -2373,7 +2373,7 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>keep:6, "Solution Presentation":1</t>
+          <t>keep:4, "Solution Presentation":3</t>
         </is>
       </c>
       <c r="Z12" t="b">
@@ -2406,15 +2406,15 @@
         </is>
       </c>
       <c r="AH12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>stakeholder communication, visual presentation tools, solution pitching, format selection, business briefings</t>
+        </is>
+      </c>
+      <c r="AJ12" t="b">
         <v>1</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>stakeholder communication, visual presentation tools, solution pitching, format selection, business briefings</t>
-        </is>
-      </c>
-      <c r="AJ12" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>requirements analysis, design optimisation, prototype testing, continuous improvement, validation feedback</t>
+          <t>requirements analysis, solution finalisation, task requirements, validation feedback, continuous improvement</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -2540,7 +2540,7 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Solution Refinement":1</t>
         </is>
       </c>
       <c r="Z13" t="b">
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="AJ13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Assesses possible solutions to a business issue and identifies restrictions to determine appropriate feasible options.</t>
+          <t>Evaluates alternative solutions to a business problem, identifying constraints to determine feasible options.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>feasibility analysis, constraint identification, business issue evaluation, risk assessment, decision matrices</t>
+          <t>feasibility analysis, constraint identification, business issue evaluation, risk assessment, solution viability</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -2728,15 +2728,15 @@
         </is>
       </c>
       <c r="AH14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>feasibility analysis, constraint identification, business issue evaluation, risk assessment, decision matrices</t>
+        </is>
+      </c>
+      <c r="AJ14" t="b">
         <v>1</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>feasibility analysis, constraint identification, business issue evaluation, risk assessment, decision matrices</t>
-        </is>
-      </c>
-      <c r="AJ14" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Proactively seeks stakeholder feedback on ideas.</t>
+          <t>Proactively seeks stakeholder input on ideas to refine concepts and align expectations.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>active listening, stakeholder engagement, feedback collection, surveys, interviews</t>
+          <t>stakeholder engagement, feedback collection, surveys, interviews, active elicitation</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="AH15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
@@ -2938,12 +2938,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Collaborates with others to facilitate effective group interaction and achieve shared outcomes.</t>
+          <t>Guides group discussions, encourages participation and coordinates tasks to achieve shared outcomes.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>active listening, group dynamics, meeting facilitation, conflict resolution, consensus building</t>
+          <t>group dynamics, meeting facilitation, conflict resolution, consensus building, active listening</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>keep:1, "Discussion Facilitation":5, "Group Interaction Facilitation":1</t>
+          <t>keep:1, "Discussion Facilitation":6</t>
         </is>
       </c>
       <c r="Z16" t="b">
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="AH16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
@@ -3105,12 +3105,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Creates and updates cyber security awareness program reflecting organisation‑wide best practice.</t>
+          <t>Designs, implements and updates organisation‑wide cyber security awareness programs in line with best practice.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>cyber security, security awareness training, phishing simulations, best practice, awareness program</t>
+          <t>cyber security awareness, security awareness program, organisation-wide best practice, phishing simulations, compliance governance</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -3193,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr">
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="AH17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
@@ -3269,12 +3269,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Uses clear, specific and industry-related cyber security terminology consistently in workplace documents to convey technical information.</t>
+          <t>Uses clear, specific and industry-related cyber security terminology in workplace documents.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>cyber security terminology, technical documentation, information security policies, industry standards, clear specific terminology</t>
+          <t>cyber security terminology, technical documentation, industry standards, information security policies, clear specific language</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Establishes cyber security awareness level in the work area by conducting surveys and interviews to set a baseline.</t>
+          <t>Assesses cyber security awareness within the work area through surveys and interviews to establish baseline levels.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>cyber security, awareness program, current level, threat intelligence, risk awareness</t>
+          <t>cyber security awareness, security awareness program, risk awareness, threat intelligence, security posture</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="AH19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Communicates review outcomes and cyber security improvement requirements in accordance with organisational policies and procedures.</t>
+          <t>Communicates review results and cyber security improvement needs in accordance with organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>cyber security, policy compliance, risk communication, security standards, stakeholder reporting</t>
+          <t>cyber security improvement, review outcomes, security standards, policy compliance, stakeholder reporting</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -3686,15 +3686,15 @@
         </is>
       </c>
       <c r="AH20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>cyber security, policy compliance, risk communication, security standards, stakeholder reporting</t>
+        </is>
+      </c>
+      <c r="AJ20" t="b">
         <v>1</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>cyber security, policy compliance, risk communication, security standards, stakeholder reporting</t>
-        </is>
-      </c>
-      <c r="AJ20" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Presents concise, relevant insight presentations derived from reviews and training clearly to designated personnel in a timely manner.</t>
+          <t>Delivers concise insight presentations derived from reviews and training to designated personnel.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>stakeholder communication, knowledge transfer, visual storytelling, training briefings, presentation tools</t>
+          <t>stakeholder communication, knowledge transfer, visual storytelling, review outcomes, presentation tools</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -3846,15 +3846,15 @@
         </is>
       </c>
       <c r="AH21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>stakeholder communication, knowledge transfer, visual storytelling, training briefings, presentation tools</t>
+        </is>
+      </c>
+      <c r="AJ21" t="b">
         <v>1</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>stakeholder communication, knowledge transfer, visual storytelling, training briefings, presentation tools</t>
-        </is>
-      </c>
-      <c r="AJ21" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Interprets Notifiable Data Breach and related Australian privacy legislation for organisational data protection implications and compliance requirements.</t>
+          <t>Interprets Notifiable Data Breach and related privacy legislation to assess impacts on organisational data protection.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Notifiable Data Breach, Australian Privacy Act, data protection compliance, privacy law interpretation, regulatory risk assessment</t>
+          <t>Notifiable Data Breach, Australian Privacy Act, data breach legislation, data protection implications, privacy laws</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -4002,15 +4002,15 @@
         </is>
       </c>
       <c r="AH22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Notifiable Data Breach, Australian Privacy Act, data protection compliance, privacy law interpretation, regulatory risk assessment</t>
+        </is>
+      </c>
+      <c r="AJ22" t="b">
         <v>1</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Notifiable Data Breach, Australian Privacy Act, data protection compliance, privacy law interpretation, regulatory risk assessment</t>
-        </is>
-      </c>
-      <c r="AJ22" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Documents review outcomes and suggested improvements for consideration by required personnel.</t>
+          <t>Documents detailed review outcome reports outlining improvement recommendations for relevant personnel.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>document outcomes, improvement recommendations, stakeholder communication, record‑keeping, cyber security</t>
+          <t>review outcomes, improvement recommendations, stakeholder communication, record‑keeping, document outcomes</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -4133,7 +4133,7 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Contributes to developing cyber security policies and procedures and communicates them to required personnel within the organisation.</t>
+          <t>Drafts cyber security policies and procedures and disseminates them to relevant staff.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="AH24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>cyber security, policy compliance, risk assessment, security governance, best practice</t>
+          <t>cyber security practices, policy compliance, security governance, audit controls, risk assessment</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>cyber security documentation, information security records, compliance logging, data governance, audit trail management</t>
+          <t>cyber security documentation, information security records, compliance logging, data governance, security protection</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -4658,7 +4658,7 @@
         </is>
       </c>
       <c r="AJ26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Consults with relevant stakeholders through meetings and surveys to gather input that effectively informs decision‑making.</t>
+          <t>Engages relevant stakeholders through meetings and surveys to gather input that informs decision‑making.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>stakeholder engagement, consultation workshops, decision support, needs analysis, facilitation</t>
+          <t>stakeholder engagement, decision support, needs analysis, facilitation, communication</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -4802,15 +4802,15 @@
         </is>
       </c>
       <c r="AH27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>stakeholder engagement, consultation workshops, decision support, needs analysis, facilitation</t>
+        </is>
+      </c>
+      <c r="AJ27" t="b">
         <v>1</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>stakeholder engagement, consultation workshops, decision support, needs analysis, facilitation</t>
-        </is>
-      </c>
-      <c r="AJ27" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -4849,12 +4849,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Collaborates with interdisciplinary teams to promote cyber security in the work area.</t>
+          <t>Collaborates with interdisciplinary teams to review and promote cyber security in the workplace.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>interdisciplinary teamwork, cyber security coordination, cross‑functional communication, stakeholder engagement, collaboration tools</t>
+          <t>interdisciplinary teamwork, cyber security coordination, cross‑functional communication, stakeholder engagement, cyber security awareness</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -4966,7 +4966,7 @@
         </is>
       </c>
       <c r="AJ28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>cyber security, security platforms, SIEM, threat monitoring, awareness program</t>
+          <t>technology platforms, cyber security awareness, security platforms, SIEM, threat monitoring</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -5089,7 +5089,7 @@
         <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>keep:6, "Technology Platform Utilisation":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z29" t="b">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Reviews latest cyber security threat reports and trends, analysing potential impacts on the organisation and summarising findings.</t>
+          <t>Analyses current cyber threat reports to assess organisational impacts and advise on security measures.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>cyber security, threat intelligence, trend monitoring, vulnerability assessment, security analytics</t>
+          <t>cyber security threats, threat intelligence, trend monitoring, security analytics, cyber security trends</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -5282,15 +5282,15 @@
         </is>
       </c>
       <c r="AH30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>cyber security, threat intelligence, trend monitoring, vulnerability assessment, security analytics</t>
+        </is>
+      </c>
+      <c r="AJ30" t="b">
         <v>1</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>cyber security, threat intelligence, trend monitoring, vulnerability assessment, security analytics</t>
-        </is>
-      </c>
-      <c r="AJ30" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Arranges training and information updates as required and maintains related records.</t>
+          <t>Coordinates training sessions and information updates by scheduling, delivering and recording activities.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>training schedules, record management, information updates, training logistics, documentation relating</t>
+          <t>training schedules, record management, information updates, training logistics, cyber security awareness</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="AH31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
@@ -5605,12 +5605,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Installs and runs latest anti‑malware on each device.</t>
+          <t>Installs and runs up‑to‑date anti‑malware on all workstations to ensure continuous protection.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>anti-malware, endpoint protection, device based, signature updates, security hygiene</t>
+          <t>anti-malware, endpoint protection, malware scanning, signature updates, cyber security</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Reviews the number of breaches and associated business impact over the review period.</t>
+          <t>Analyses breach volumes and assesses business impacts across review periods to inform risk mitigation.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>breaches, business impact, incident tracking, risk assessment, cyber security</t>
+          <t>business impact analysis, breach review, incident tracking, risk assessment, security metrics</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="AH35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Device Configuration</t>
+          <t>Device Configuration Setup</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Ensures new devices are updated and configured correctly as part of the initial start‑up procedure.</t>
+          <t>Performs initial device set‑up by updating firmware and configuring settings on new devices.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -6003,19 +6003,15 @@
         </is>
       </c>
       <c r="V36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 5/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>keep:2, "Device Configuration":5</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z36" t="b">
@@ -6039,7 +6035,7 @@
         </is>
       </c>
       <c r="AH36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
@@ -6086,7 +6082,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Encrypts each device according to provided instructions, ensuring data protection and compliance with organisational security policies.</t>
+          <t>Implements device encryption in accordance with prescribed procedures to secure hardware.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -6194,7 +6190,7 @@
         </is>
       </c>
       <c r="AH37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
@@ -6241,12 +6237,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Creates and maintains a register of digital devices on the organisation’s network.</t>
+          <t>Creates and updates a register of networked devices to support inventory tracking and asset management.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>IT asset tracking, hardware registers, network inventories, CMDB, digital devices</t>
+          <t>IT asset tracking, hardware registers, network inventories, CMDB, digital device register</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -6369,7 +6365,7 @@
         </is>
       </c>
       <c r="AH38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
@@ -6416,12 +6412,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Conducts comprehensive gap analyses to evaluate the effectiveness of implemented best‑practice security strategies across digital devices.</t>
+          <t>Conducts gap analyses to assess and benchmark best‑practice implementation effectiveness.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>benchmarking, performance metrics, best‑practice assessment, process improvement, effectiveness evaluation</t>
+          <t>gap analysis, best practice strategies, effectiveness evaluation, benchmarking, performance metrics</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -6532,15 +6528,15 @@
         </is>
       </c>
       <c r="AH39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>benchmarking, performance metrics, best‑practice assessment, process improvement, effectiveness evaluation</t>
+        </is>
+      </c>
+      <c r="AJ39" t="b">
         <v>1</v>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>benchmarking, performance metrics, best‑practice assessment, process improvement, effectiveness evaluation</t>
-        </is>
-      </c>
-      <c r="AJ39" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -6579,12 +6575,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Creates strong, unique passwords for personal and work accounts in line with approved complexity criteria.</t>
+          <t>Generates robust, unique passwords for personal and work accounts in line with approved complexity criteria.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>password complexity, entropy, cyber security, password managers, strong passwords</t>
+          <t>authentication, password complexity, entropy, cyber security, password managers</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -6658,12 +6654,12 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Password Creation":1</t>
         </is>
       </c>
       <c r="Z40" t="b">
@@ -6687,7 +6683,7 @@
         </is>
       </c>
       <c r="AH40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
@@ -6695,7 +6691,7 @@
         </is>
       </c>
       <c r="AJ40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -6734,12 +6730,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Develops a physical security plan and communicates it to the whole organisation to ensure coordinated protection.</t>
+          <t>Develops comprehensive physical security plans and disseminates them organisation‑wide to ensure coordinated protection.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>risk assessment, access control systems, security policy development, facility protection, stakeholder communication</t>
+          <t>physical security plan, access control systems, facility protection, stakeholder communication, risk assessment</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -6830,9 +6826,13 @@
         </is>
       </c>
       <c r="Z41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Security Plan Communication</t>
+        </is>
+      </c>
       <c r="AB41" t="b">
         <v>0</v>
       </c>
@@ -6850,15 +6850,15 @@
         </is>
       </c>
       <c r="AH41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>risk assessment, access control systems, security policy development, facility protection, stakeholder communication</t>
+        </is>
+      </c>
+      <c r="AJ41" t="b">
         <v>1</v>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>risk assessment, access control systems, security policy development, facility protection, stakeholder communication</t>
-        </is>
-      </c>
-      <c r="AJ41" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Categorises the level of risk for each device based on the sensitivity of information stored.</t>
+          <t>Assesses device data sensitivity to assign appropriate risk categories for security management.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>risk assessment, information sensitivity, device classification, cyber security, business impact</t>
+          <t>risk assessment, information sensitivity, device classification, cyber security, risk matrices</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c r="AH42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         </is>
       </c>
       <c r="AJ42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Develops the physical security plan and communicates it organisation‑wide to ensure understanding and compliance.</t>
+          <t>Delivers organisation‑wide briefings on physical security plans to support understanding and compliance.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>physical security, security policy, stakeholder communication, access control, cyber security</t>
+          <t>physical security, security plan, stakeholder communication, risk assessment, security policy</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -7147,22 +7147,18 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>keep:6, "Physical Security Plan Communication":1</t>
+          <t>keep:5, "Physical Security Plan Communication/Physical Security Communication":2</t>
         </is>
       </c>
       <c r="Z43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>Physical Security Planning</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="b">
         <v>0</v>
       </c>
@@ -7180,7 +7176,7 @@
         </is>
       </c>
       <c r="AH43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
@@ -7227,12 +7223,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Selects required security protocol for each device to manage its associated risk level.</t>
+          <t>Selects appropriate security protocols for each device to mitigate identified risk levels.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>risk assessment, encryption standards, device hardening, cyber security governance, protocol compliance</t>
+          <t>risk assessment, security protocol, device hardening, cyber security governance, physical security</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -7343,15 +7339,15 @@
         </is>
       </c>
       <c r="AH44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>risk assessment, encryption standards, device hardening, cyber security governance, protocol compliance</t>
+        </is>
+      </c>
+      <c r="AJ44" t="b">
         <v>1</v>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>risk assessment, encryption standards, device hardening, cyber security governance, protocol compliance</t>
-        </is>
-      </c>
-      <c r="AJ44" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -7390,12 +7386,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Supports the organisation to select the most appropriate security strategies.</t>
+          <t>Advises the organisation by evaluating options and recommending optimal security strategies.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>cyber security governance, risk assessment, security frameworks, threat modelling, ISO 27001</t>
+          <t>security strategies, cyber security governance, risk assessment, security frameworks, ISO 27001</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -7477,7 +7473,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr">
@@ -7506,15 +7502,15 @@
         </is>
       </c>
       <c r="AH45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>cyber security governance, risk assessment, security frameworks, threat modelling, ISO 27001</t>
+        </is>
+      </c>
+      <c r="AJ45" t="b">
         <v>1</v>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>cyber security governance, risk assessment, security frameworks, threat modelling, ISO 27001</t>
-        </is>
-      </c>
-      <c r="AJ45" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -7553,7 +7549,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Monitors emerging digital security developments.</t>
+          <t>Monitors emerging digital security developments to inform risk assessments and protective measures.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -7641,7 +7637,7 @@
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>keep:5, "Security Development Monitoring":2</t>
+          <t>keep:4, "Security Development Monitoring":3</t>
         </is>
       </c>
       <c r="Z46" t="b">
@@ -7665,7 +7661,7 @@
         </is>
       </c>
       <c r="AH46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
@@ -7712,12 +7708,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Applies updates to software and applications on own desktop and mobile devices.</t>
+          <t>Installs and configures software patches on desktop and mobile devices to maintain system security.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>patch management, software updates, endpoint management, mobile device management, cyber security</t>
+          <t>patch management, software updates, endpoint management, mobile device management, desktop devices</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -7828,7 +7824,7 @@
         </is>
       </c>
       <c r="AH47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
@@ -7875,12 +7871,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Switches on two‑factor authentication on all supported devices where available to enhance account security for users.</t>
+          <t>Enables multi‑factor authentication on supported systems to strengthen account security.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>multi‑factor authentication, two‑factor authentication, OTP, access control, cyber security</t>
+          <t>multi-factor authentication, two-factor authentication, OTP, access control, cyber security</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -7995,7 +7991,7 @@
         </is>
       </c>
       <c r="AH48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
@@ -8042,7 +8038,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Develops comprehensive action plans that implement proposed changes, include a prioritised schedule and ensure consistency with organisational policies and procedures.</t>
+          <t>Develops detailed action plans aligned with policies, prioritising tasks and scheduling implementation.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -8141,7 +8137,7 @@
         </is>
       </c>
       <c r="AH49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
@@ -8188,7 +8184,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Prioritises proposed changes to refine improvement opportunities and assist implementation scheduling.</t>
+          <t>Ranks proposed changes to clarify improvement opportunities and inform implementation scheduling.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -8291,7 +8287,7 @@
         </is>
       </c>
       <c r="AH50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
@@ -8338,7 +8334,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Uses and investigates new digital technologies to manage and manipulate data and communicate effectively across the organisation.</t>
+          <t>Explores emerging digital tools to organise and analyse data and support effective communication.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -8441,7 +8437,7 @@
         </is>
       </c>
       <c r="AH51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
@@ -8468,7 +8464,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Evaluation Documentation Preparation</t>
+          <t>Evaluation Documentation</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -8488,7 +8484,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Documents the evaluation process and provides the documentation to the superior for feedback and further guidance.</t>
+          <t>Prepares evaluation documents, organises findings and submits them to a supervisor for review.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -8558,16 +8554,16 @@
         <v>1</v>
       </c>
       <c r="W52" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>keep:0, "Evaluation Documentation Preparation":5, "Evaluation Documentation":2</t>
+          <t>keep:0, "Evaluation Documentation":7</t>
         </is>
       </c>
       <c r="Z52" t="b">
@@ -8591,7 +8587,7 @@
         </is>
       </c>
       <c r="AH52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
@@ -8638,12 +8634,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Compares strategic plan objectives with current ICT state to determine ICT gaps, improvement opportunities and proposed changes.</t>
+          <t>Analyses strategic objectives against current ICT capability in hybrid environments to identify gaps and propose improvements.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>gap analysis, strategic alignment, ICT governance, digital transformation, changes gaps</t>
+          <t>gap analysis, strategic alignment, ICT gaps, improvement opportunities, proposed changes</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -8725,7 +8721,7 @@
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>keep:4, "ICT Gap Identification":3</t>
+          <t>keep:5, "ICT Gap Identification":2</t>
         </is>
       </c>
       <c r="Z53" t="b">
@@ -8749,7 +8745,7 @@
         </is>
       </c>
       <c r="AH53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
@@ -8796,12 +8792,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Evaluates the impact of proposed ICT system and product changes against the organisation's strategic objectives.</t>
+          <t>Assesses proposed ICT system and product changes in hybrid environments for alignment with organisational strategic objectives.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>impact assessment, ICT systems, strategic alignment, change management, performance metrics</t>
+          <t>impact assessment, ICT systems, strategic objectives, change management, performance metrics</t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -8919,7 +8915,7 @@
         </is>
       </c>
       <c r="AJ54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -9028,12 +9024,12 @@
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Innovative Idea Investigation":1</t>
         </is>
       </c>
       <c r="Z55" t="b">
@@ -9109,7 +9105,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>financial analysis, quantitative modelling, cost‑benefit assessment, Excel, statistical calculations</t>
+          <t>financial analysis, quantitative modelling, cost‑benefit assessment, numerical data interpretation, mathematical calculations</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -9174,12 +9170,12 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>keep:6, "Financial Impact Interpretation":1</t>
+          <t>keep:2, "Financial Impact Assessment":3, "Financial Impact Interpretation":2</t>
         </is>
       </c>
       <c r="Z56" t="b">
@@ -9211,7 +9207,7 @@
         </is>
       </c>
       <c r="AJ56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -9250,12 +9246,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Details the required standards, targets and implementation methods within the action plan to guide organisational change.</t>
+          <t>Assesses policy compliance by documenting standards, targets and implementation approaches within action plans.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>regulatory standards, compliance frameworks, risk assessment, policy implementation planning, action plan</t>
+          <t>regulatory standards, compliance frameworks, policy implementation planning, action plan, implementation methods</t>
         </is>
       </c>
       <c r="J57" t="n">
@@ -9349,7 +9345,7 @@
         </is>
       </c>
       <c r="AH57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
@@ -9396,7 +9392,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Develops action plan that includes a prioritised schedule to implement the proposed changes.</t>
+          <t>Develops detailed action plans with prioritised schedules to implement change initiatives efficiently.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -9495,7 +9491,7 @@
         </is>
       </c>
       <c r="AH58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI58" t="inlineStr">
         <is>
@@ -9522,7 +9518,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Implementation Difficulty Evaluation</t>
+          <t>Difficulty Evaluation</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -9542,12 +9538,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Evaluates the difficulty of implementing proposed ICT system and product changes to inform implementation planning.</t>
+          <t>Assesses the difficulty of implementing proposed changes to ICT systems and products.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ICT systems, change management, implementation complexity, risk analysis, impact assessment</t>
+          <t>implementation complexity, change management, ICT systems, difficulty evaluation, impact assessment</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -9612,16 +9608,16 @@
         <v>1</v>
       </c>
       <c r="W59" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name uses 'Planning' but evidence describes evaluating difficulty, not planning</t>
+          <t>MIS re-refinement: Skill name includes 'Planning' which is not present in the evidence; evidence only involves evaluating difficulty</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Implementation Difficulty Assessment":1</t>
         </is>
       </c>
       <c r="Z59" t="b">
@@ -9637,7 +9633,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>Skill name uses 'Planning' but evidence describes evaluating difficulty, not planning</t>
+          <t>Skill name includes 'Planning' which is not present in the evidence; evidence only involves evaluating difficulty</t>
         </is>
       </c>
       <c r="AF59" t="b">
@@ -9657,7 +9653,7 @@
         </is>
       </c>
       <c r="AJ59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -9696,12 +9692,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Reports proposed changes, identified gaps and improvement opportunities to the superior in concise written form.</t>
+          <t>Prepares concise reports outlining changes, gaps and improvement opportunities for senior staff.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>executive communication, gap analysis, change management, improvement recommendations, business reporting</t>
+          <t>gap analysis, improvement opportunities, proposed changes, executive communication, business reporting</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -9778,7 +9774,7 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr">
@@ -9807,15 +9803,15 @@
         </is>
       </c>
       <c r="AH60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>executive communication, gap analysis, change management, improvement recommendations, business reporting</t>
+        </is>
+      </c>
+      <c r="AJ60" t="b">
         <v>1</v>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>executive communication, gap analysis, change management, improvement recommendations, business reporting</t>
-        </is>
-      </c>
-      <c r="AJ60" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -9854,7 +9850,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Analyses the organisation’s current strategic plan against the industry environment and organisational objectives, documenting findings in a concise report.</t>
+          <t>Analyses the organisation’s strategic plan against the industry environment and objectives, documenting findings.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -9969,7 +9965,7 @@
         </is>
       </c>
       <c r="AH61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI61" t="inlineStr">
         <is>
@@ -10016,12 +10012,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Applies structured analytical frameworks to systematically evaluate options and resolve complex, non‑routine problems in organisational contexts.</t>
+          <t>Uses structured analytical frameworks to evaluate options and resolve complex, non‑routine problems.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>decision analysis, analytical reasoning, structured methodologies, risk assessment, scenario modelling</t>
+          <t>analytical decision making, systematic decision processes, complex decision analysis, non-routine decision modelling, risk assessment</t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -10115,15 +10111,15 @@
         </is>
       </c>
       <c r="AH62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>decision analysis, analytical reasoning, structured methodologies, risk assessment, scenario modelling</t>
+        </is>
+      </c>
+      <c r="AJ62" t="b">
         <v>1</v>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>decision analysis, analytical reasoning, structured methodologies, risk assessment, scenario modelling</t>
-        </is>
-      </c>
-      <c r="AJ62" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -10167,7 +10163,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>plain language, jargon translation, stakeholder communication, technical writing, audience adaptation</t>
+          <t>plain English, technical terminology translation, stakeholder communication, technical writing, audience adaptation</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -10269,7 +10265,7 @@
         </is>
       </c>
       <c r="AJ63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -10313,7 +10309,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>legislative compliance, policy analysis, regulatory standards, complex text, decision outcomes</t>
+          <t>legislative compliance, regulatory standards, policy analysis, industry standards, certification requirements</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -10441,7 +10437,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Compliance Management</t>
+          <t>Compliance Review</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -10461,12 +10457,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Reviews the organisational privacy policy and procedures and determines compliance with relevant industry standard requirements.</t>
+          <t>Evaluates organisational privacy policies and procedures against industry standards to ensure compliance in hybrid environments.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>privacy policy, regulatory standards, compliance, confidentiality security, decision making</t>
+          <t>privacy policy, industry standard requirements, regulatory standards, compliance review, data protection</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -10531,12 +10527,16 @@
         </is>
       </c>
       <c r="V65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W65" t="n">
-        <v>0.9514285714285714</v>
-      </c>
-      <c r="X65" t="inlineStr"/>
+        <v>0.95</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>MIS re-refinement: Skill name uses 'Management' which is not reflected in evidence verbs 'review' and 'determine', indicating a different activity</t>
+        </is>
+      </c>
       <c r="Y65" t="inlineStr">
         <is>
           <t>keep:7</t>
@@ -10551,9 +10551,13 @@
       </c>
       <c r="AC65" t="inlineStr"/>
       <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>Skill name uses 'Management' which is not reflected in evidence verbs 'review' and 'determine', indicating a different activity</t>
+        </is>
+      </c>
       <c r="AF65" t="b">
         <v>0</v>
       </c>
@@ -10610,12 +10614,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Reviews ethical practices and feedback and determines application of the organisational code of ethics according to organisational requirements.</t>
+          <t>Reviews ethical practices and feedback and determines the appropriate application of the organisational code of ethics in line with organisational requirements.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>professional ethics, codes of conduct, compliance, organisational governance, ethical frameworks</t>
+          <t>professional ethics, codes of conduct, ethical work practices, organisational governance, ethical frameworks</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -10720,7 +10724,7 @@
         </is>
       </c>
       <c r="AJ66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -10759,7 +10763,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Seeks and responds to feedback on review and grievance procedure documents from required personnel promptly.</t>
+          <t>Collects and addresses feedback on review and grievance documentation from designated personnel.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -10837,7 +10841,7 @@
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>keep:5, "Feedback Management":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z67" t="b">
@@ -10861,7 +10865,7 @@
         </is>
       </c>
       <c r="AH67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
@@ -10908,12 +10912,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tests information integrity, confidentiality, security and availability against industry standards.</t>
+          <t>Conducts industry‑standard tests to assess information integrity, confidentiality, security and availability.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>penetration testing, vulnerability assessment, ISO 27001, CIA triad, confidentiality</t>
+          <t>penetration testing, vulnerability assessment, ISO 27001, CIA triad, security controls</t>
         </is>
       </c>
       <c r="J68" t="n">
@@ -11010,7 +11014,7 @@
         </is>
       </c>
       <c r="AH68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI68" t="inlineStr">
         <is>
@@ -11018,7 +11022,7 @@
         </is>
       </c>
       <c r="AJ68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -11057,12 +11061,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Integrates diverse sources into cohesive written material, utilising specialised language and supporting documentation.</t>
+          <t>Synthesises diverse sources into cohesive written reports using specialised terminology and supporting documentation.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>source integration, technical writing, citation management, knowledge synthesis, cohesive language</t>
+          <t>information synthesis, source integration, technical writing, citation management, cohesive language</t>
         </is>
       </c>
       <c r="J69" t="n">
@@ -11159,7 +11163,7 @@
         </is>
       </c>
       <c r="AH69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI69" t="inlineStr">
         <is>
@@ -11206,12 +11210,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Identifies relevant industry‑standard intellectual property and copyright legislation, policies and procedures to ensure organisational compliance.</t>
+          <t>Analyses and interprets intellectual property and copyright legislation to ensure organisational compliance.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>intellectual property law, copyright legislation, policy compliance, legal research, regulatory analysis</t>
+          <t>intellectual property law, copyright legislation, industry standards, policy compliance, regulatory analysis</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -11308,15 +11312,15 @@
         </is>
       </c>
       <c r="AH70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>intellectual property law, copyright legislation, policy compliance, legal research, regulatory analysis</t>
+        </is>
+      </c>
+      <c r="AJ70" t="b">
         <v>1</v>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>intellectual property law, copyright legislation, policy compliance, legal research, regulatory analysis</t>
-        </is>
-      </c>
-      <c r="AJ70" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -11355,12 +11359,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Distributes revised policy, procedures and ethics to required personnel.</t>
+          <t>Delivers updated policies, procedures and ethics documentation to designated personnel.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>document dissemination, compliance communication, stakeholder engagement, internal governance, ethics training</t>
+          <t>document dissemination, policy distribution, ethics training, stakeholder engagement, internal governance</t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -11457,15 +11461,15 @@
         </is>
       </c>
       <c r="AH71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>document dissemination, compliance communication, stakeholder engagement, internal governance, ethics training</t>
+        </is>
+      </c>
+      <c r="AJ71" t="b">
         <v>1</v>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>document dissemination, compliance communication, stakeholder engagement, internal governance, ethics training</t>
-        </is>
-      </c>
-      <c r="AJ71" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -11509,7 +11513,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>privacy legislation, policy management, codes of ethics, regulatory documentation, confidentiality security</t>
+          <t>privacy legislation, privacy policy, code of ethics, regulatory documentation, policy management</t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -11581,12 +11585,12 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>keep:1, "Privacy Policy Documentation":6</t>
+          <t>keep:2, "Privacy Policy Documentation":5</t>
         </is>
       </c>
       <c r="Z72" t="b">
@@ -11657,12 +11661,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Establishes and documents review and grievance procedures and submits them to required personnel promptly, according to organisational standards.</t>
+          <t>Develops, records and submits review and grievance procedures to designated personnel.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>policy drafting, grievance management, standard operating procedures, process documentation, compliance workflows</t>
+          <t>grievance procedure, policy drafting, standard operating procedures, process documentation, compliance workflows</t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -11759,15 +11763,15 @@
         </is>
       </c>
       <c r="AH73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>policy drafting, grievance management, standard operating procedures, process documentation, compliance workflows</t>
+        </is>
+      </c>
+      <c r="AJ73" t="b">
         <v>1</v>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>policy drafting, grievance management, standard operating procedures, process documentation, compliance workflows</t>
-        </is>
-      </c>
-      <c r="AJ73" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -11806,12 +11810,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Sequences and schedules complex project activities, monitors implementation and manages communication to sustain delivery momentum.</t>
+          <t>Sequences and schedules complex activities, monitors progress and coordinates communication to maintain delivery momentum.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>scheduling, resource allocation, stakeholder communication, project monitoring, Gantt charts</t>
+          <t>scheduling, resource allocation, stakeholder communication, project monitoring, sequences and schedules</t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -11912,15 +11916,15 @@
         </is>
       </c>
       <c r="AH74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>scheduling, resource allocation, stakeholder communication, project monitoring, Gantt charts</t>
+        </is>
+      </c>
+      <c r="AJ74" t="b">
         <v>1</v>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>scheduling, resource allocation, stakeholder communication, project monitoring, Gantt charts</t>
-        </is>
-      </c>
-      <c r="AJ74" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -11959,12 +11963,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Identifies and analyses changes to legislation and regulations affecting own rights and responsibilities within the organisation.</t>
+          <t>Identifies and analyses legislative changes to ensure ongoing compliance with rights and responsibilities.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>compliance, legislation monitoring, regulatory analysis, policy tracking, legal research</t>
+          <t>legislation monitoring, regulatory analysis, policy tracking, legal research, rights and responsibilities</t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -12069,7 +12073,7 @@
         </is>
       </c>
       <c r="AJ75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -12113,7 +12117,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>cyber security, data protection, information governance, privacy compliance, confidentiality security</t>
+          <t>cyber security, data protection, information governance, privacy compliance, digital technologies</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -12181,12 +12185,12 @@
         <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>0.952</v>
+        <v>0.95</v>
       </c>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>keep:5, "Digital Information Security":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z76" t="b">
@@ -12257,7 +12261,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Distributes new or revised policy and procedures to stakeholders as per the established organisational procedures.</t>
+          <t>Distributes updated policies to stakeholders in accordance with organisational protocols.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -12330,16 +12334,16 @@
         <v>1</v>
       </c>
       <c r="W77" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>keep:0, "Policy Distribution":7</t>
+          <t>keep:2, "Policy Distribution":5</t>
         </is>
       </c>
       <c r="Z77" t="b">
@@ -12367,7 +12371,7 @@
         </is>
       </c>
       <c r="AH77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
@@ -12414,7 +12418,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Participates in verbal exchange of ideas, listening and questioning to elicit others’ views and perspectives.</t>
+          <t>Engages in verbal idea exchange, actively listening and questioning to draw out others’ views.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -12516,7 +12520,7 @@
         </is>
       </c>
       <c r="AH78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
@@ -12563,12 +12567,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Sets up the required blockchain platform in accordance with the design plan.</t>
+          <t>Installs and configures blockchain platform components in line with approved design specifications.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>distributed ledger, node deployment, consensus configuration, Ethereum, Docker</t>
+          <t>distributed ledger, node deployment, consensus configuration, blockchain platform, design plan</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -12672,15 +12676,15 @@
         </is>
       </c>
       <c r="AH79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>distributed ledger, node deployment, consensus configuration, Ethereum, Docker</t>
+        </is>
+      </c>
+      <c r="AJ79" t="b">
         <v>1</v>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>distributed ledger, node deployment, consensus configuration, Ethereum, Docker</t>
-        </is>
-      </c>
-      <c r="AJ79" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -12719,12 +12723,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Recognises and remedies blockchain anomalies by focusing on contextual cues to detect subtle deviations from normal expectations.</t>
+          <t>Identifies and resolves blockchain anomalies through contextual analysis to detect subtle deviations.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>anomaly detection, blockchain analytics, smart contract debugging, cryptographic forensics, pattern recognition</t>
+          <t>anomaly detection, blockchain analytics, smart contract debugging, cryptographic forensics, nuanced understanding</t>
         </is>
       </c>
       <c r="J80" t="n">
@@ -12799,16 +12803,16 @@
         <v>1</v>
       </c>
       <c r="W80" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>keep:0, "Blockchain Anomaly Resolution":6, "Blockchain Anomaly Solving":1</t>
+          <t>keep:0, "Blockchain Anomaly Resolution":7</t>
         </is>
       </c>
       <c r="Z80" t="b">
@@ -12820,7 +12824,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Foundation Skill describes problem‑solving capability that is already embedded in multiple performance criteria and other skills; it does not represent a distinct task for this unit</t>
+          <t>Foundation Skill describes problem‑solving capability that is already embedded in other skills and PCs; it does not represent a distinct task for this unit</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -12836,15 +12840,15 @@
         </is>
       </c>
       <c r="AH80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>anomaly detection, blockchain analytics, smart contract debugging, cryptographic forensics, pattern recognition</t>
+        </is>
+      </c>
+      <c r="AJ80" t="b">
         <v>1</v>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>anomaly detection, blockchain analytics, smart contract debugging, cryptographic forensics, pattern recognition</t>
-        </is>
-      </c>
-      <c r="AJ80" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -12883,12 +12887,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Establishes blockchain objectives, purpose and requirements according to organisational needs.</t>
+          <t>Establishes blockchain objectives, purpose and requirements aligned with organisational needs in hybrid environments.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>blockchain objectives, stakeholder analysis, business needs, smart contract design, governance frameworks</t>
+          <t>distributed ledger, blockchain objectives, stakeholder analysis, business needs, governance frameworks</t>
         </is>
       </c>
       <c r="J81" t="n">
@@ -13039,12 +13043,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Implements the required consensus portal according to project requirements as part of the blockchain solution.</t>
+          <t>Implements consensus mechanisms by configuring and deploying required system components.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>blockchain, distributed ledger, consensus algorithms, peer‑to‑peer networking, Byzantine fault tolerance</t>
+          <t>blockchain, consensus algorithms, peer-to-peer networking, Byzantine fault tolerance, consensus portal</t>
         </is>
       </c>
       <c r="J82" t="n">
@@ -13148,15 +13152,15 @@
         </is>
       </c>
       <c r="AH82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>blockchain, distributed ledger, consensus algorithms, peer‑to‑peer networking, Byzantine fault tolerance</t>
+        </is>
+      </c>
+      <c r="AJ82" t="b">
         <v>1</v>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>blockchain, distributed ledger, consensus algorithms, peer‑to‑peer networking, Byzantine fault tolerance</t>
-        </is>
-      </c>
-      <c r="AJ82" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -13195,12 +13199,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Documents the design plan in accordance with organisational needs to guide solution development.</t>
+          <t>Produces detailed design documentation aligned with organisational requirements to support project delivery.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>technical specifications, design standards, engineering documentation, organisational requirements, business needs</t>
+          <t>design plan, organisational requirements, technical specifications, engineering documentation, design standards</t>
         </is>
       </c>
       <c r="J83" t="n">
@@ -13304,7 +13308,7 @@
         </is>
       </c>
       <c r="AH83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI83" t="inlineStr">
         <is>
@@ -13351,12 +13355,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Submits documentation to required personnel, seeks feedback and responds promptly in a timely manner to any comments received.</t>
+          <t>Submits documentation for review, seeks feedback and incorporates approved amendments.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>record‑keeping, feedback loops, compliance, workflow approvals, electronic filing</t>
+          <t>record‑keeping, feedback loops, documentation submission, workflow approvals, compliance</t>
         </is>
       </c>
       <c r="J84" t="n">
@@ -13460,15 +13464,15 @@
         </is>
       </c>
       <c r="AH84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>record‑keeping, feedback loops, compliance, workflow approvals, electronic filing</t>
+        </is>
+      </c>
+      <c r="AJ84" t="b">
         <v>1</v>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>record‑keeping, feedback loops, compliance, workflow approvals, electronic filing</t>
-        </is>
-      </c>
-      <c r="AJ84" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -13507,7 +13511,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Designs integration workflow to meet organisational need, outlining required steps and ensuring alignment with business objectives.</t>
+          <t>Designs integration workflows by mapping data flows and configuring tools to meet organisational needs.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -13616,7 +13620,7 @@
         </is>
       </c>
       <c r="AH85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI85" t="inlineStr">
         <is>
@@ -13663,12 +13667,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Determines and documents the maintenance schedule in accordance with specified requirements.</t>
+          <t>Develops and records maintenance schedules aligned with equipment requirements and timelines.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>preventive maintenance, asset management, CMMS, work order scheduling, reliability engineering</t>
+          <t>preventive maintenance, asset management, CMMS, work order scheduling, maintenance schedule</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -13772,15 +13776,15 @@
         </is>
       </c>
       <c r="AH86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>preventive maintenance, asset management, CMMS, work order scheduling, reliability engineering</t>
+        </is>
+      </c>
+      <c r="AJ86" t="b">
         <v>1</v>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>preventive maintenance, asset management, CMMS, work order scheduling, reliability engineering</t>
-        </is>
-      </c>
-      <c r="AJ86" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -13819,12 +13823,12 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Determines and conducts maintenance tests on equipment to ensure functionality and compliance.</t>
+          <t>Determines and conducts maintenance tests to verify equipment functionality and compliance.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>preventive maintenance, test procedures, equipment inspection, reliability testing, compliance standards</t>
+          <t>preventive maintenance, maintenance testing, equipment inspection, reliability testing, compliance standards</t>
         </is>
       </c>
       <c r="J87" t="n">
@@ -13940,7 +13944,7 @@
         </is>
       </c>
       <c r="AJ87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -13979,7 +13983,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Determines appropriate security measures and platform specifications for blockchain solutions to meet organisational requirements effectively.</t>
+          <t>Determines the security measures and platform for blockchain solutions, informed by risk assessments.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -14135,12 +14139,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Executes the required smart command on the required blockchain platform in accordance with the blockchain solution.</t>
+          <t>Executes the required smart command on the designated blockchain platform in accordance with the solution specifications.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>blockchain technology, smart contract execution, Ethereum platform, Solidity programming, Web3 decentralised applications</t>
+          <t>blockchain, Ethereum, Solidity, smart command execution, decentralised applications</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -14291,12 +14295,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Debugs blockchain solution issues and scales the solution to support increased transaction volumes across multiple nodes.</t>
+          <t>Diagnoses and resolves blockchain solution issues and optimises performance for scalable deployment.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>blockchain, smart contracts, Solidity, distributed ledger, performance scaling</t>
+          <t>blockchain, smart contracts, Solidity, performance scaling, solution debugging</t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -14400,15 +14404,15 @@
         </is>
       </c>
       <c r="AH90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>blockchain, smart contracts, Solidity, distributed ledger, performance scaling</t>
+        </is>
+      </c>
+      <c r="AJ90" t="b">
         <v>1</v>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>blockchain, smart contracts, Solidity, distributed ledger, performance scaling</t>
-        </is>
-      </c>
-      <c r="AJ90" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -14447,12 +14451,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Tests solution performance against organisational strategic needs and regulatory requirements for required business outcomes effectively.</t>
+          <t>Tests solution performance against organisational needs and requirements to confirm suitability.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>benchmarking, requirements compliance, load testing, service level agreements, performance metrics</t>
+          <t>benchmarking, load testing, service level agreements, performance metrics, organisational requirements</t>
         </is>
       </c>
       <c r="J91" t="n">
@@ -14564,7 +14568,7 @@
         </is>
       </c>
       <c r="AJ91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -14603,7 +14607,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Obtains information from stakeholders to confirm requirements and responsibilities distinctly, effectively using appropriate industry language.</t>
+          <t>Obtains information to confirm requirements and responsibilities using appropriate industry terminology.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -14759,12 +14763,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Identifies organisational use cases that directly address the specific needs and objectives of the organisation.</t>
+          <t>Identifies organisational use cases aligned with business needs by analysing hybrid environments.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>business needs, stakeholder mapping, use‑case modelling, functional requirements, blockchain technology</t>
+          <t>requirements analysis, business analysis, stakeholder mapping, use‑case modelling, business needs</t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -14915,12 +14919,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Ingests data logs into the analytic platform according to user instructions.</t>
+          <t>Ingests data logs into analytics platforms as instructed to support monitoring and analysis.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>data ingestion, log analytics, ETL pipelines, analytics platforms, data logs</t>
+          <t>data ingestion, log analytics, analytic platform, ETL pipelines, user instructions</t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -15035,7 +15039,7 @@
         </is>
       </c>
       <c r="AH94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI94" t="inlineStr">
         <is>
@@ -15087,7 +15091,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>regulatory compliance, legislation, policy analysis, threat intelligence, risk assessment</t>
+          <t>legislative requirements, organisational policies, threat data analysis, data log requirements, regulatory compliance</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -15206,7 +15210,7 @@
         </is>
       </c>
       <c r="AJ95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -15245,7 +15249,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Detects and describes data discrepancies and inconsistencies in datasets through systematic analysis to support accurate threat assessment.</t>
+          <t>Examines datasets to identify, document and resolve data discrepancies and inconsistencies.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -15357,7 +15361,7 @@
         </is>
       </c>
       <c r="AH96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI96" t="inlineStr">
         <is>
@@ -15404,12 +15408,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Collects alerts, logs and reported events and creates a dataset in line with organisational policies and procedures.</t>
+          <t>Compiles alerts, logs and event reports into structured datasets in line with organisational policies.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>log analysis, data ingestion, security monitoring, data governance, ETL processes</t>
+          <t>log analysis, data ingestion, dataset creation, alerts and logs, data governance</t>
         </is>
       </c>
       <c r="J97" t="n">
@@ -15524,15 +15528,15 @@
         </is>
       </c>
       <c r="AH97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>log analysis, data ingestion, security monitoring, data governance, ETL processes</t>
+        </is>
+      </c>
+      <c r="AJ97" t="b">
         <v>1</v>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>log analysis, data ingestion, security monitoring, data governance, ETL processes</t>
-        </is>
-      </c>
-      <c r="AJ97" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -15571,12 +15575,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Checks test results for false positives and false negatives, with a documented list of any discrepancies.</t>
+          <t>Reviews test results to identify and correct false positives and false negatives.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>anomaly detection, false positive detection, false negative detection, validation testing, statistical significance</t>
+          <t>false positives, false negatives, type I error, anomaly detection, statistical significance</t>
         </is>
       </c>
       <c r="J98" t="n">
@@ -15691,7 +15695,7 @@
         </is>
       </c>
       <c r="AH98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI98" t="inlineStr">
         <is>
@@ -15738,12 +15742,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Documents results, findings and recommendations in a report according to organisational procedures.</t>
+          <t>Produces formal investigation reports outlining findings and recommendations in accordance with organisational procedures.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>incident reporting, root‑cause analysis, procedural compliance, report writing, data logs</t>
+          <t>incident reporting, report writing, procedural compliance, root‑cause analysis, findings documentation</t>
         </is>
       </c>
       <c r="J99" t="n">
@@ -15846,7 +15850,7 @@
         </is>
       </c>
       <c r="AH99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI99" t="inlineStr">
         <is>
@@ -15893,12 +15897,12 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Suggests and confirms lessons learnt, action steps, recommendations and mitigation strategies with required personnel in the organisation.</t>
+          <t>Suggests and confirms lessons learned, action steps, recommendations and mitigation strategies with required personnel.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>risk management, lessons learned, action steps, mitigation planning, cyber threats</t>
+          <t>lessons learned, action steps, mitigation strategies, recommendations, stakeholder engagement</t>
         </is>
       </c>
       <c r="J100" t="n">
@@ -16056,12 +16060,12 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Discusses and assesses identified threats, their likelihood and impact to determine organisational overall risk levels.</t>
+          <t>Assesses threats by evaluating likelihood and impact to prioritise risk mitigation actions.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>risk assessment, probability analysis, threat modelling, impact evaluation, risk matrices</t>
+          <t>risk assessment, threat modelling, likelihood of occurrence, impacts of risks, cyber threats</t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -16172,15 +16176,15 @@
         </is>
       </c>
       <c r="AH101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>risk assessment, probability analysis, threat modelling, impact evaluation, risk matrices</t>
+        </is>
+      </c>
+      <c r="AJ101" t="b">
         <v>1</v>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>risk assessment, probability analysis, threat modelling, impact evaluation, risk matrices</t>
-        </is>
-      </c>
-      <c r="AJ101" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -16219,12 +16223,12 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Identifies network and data‑source security equipment using system diagrams and technical documentation, in line with organisational policies.</t>
+          <t>Identifies network and data‑source security equipment using system diagrams and technical documentation.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>cyber security, network security, asset inventories, IDS, firewalls</t>
+          <t>security equipment, network security, asset inventories, data sources, cyber security</t>
         </is>
       </c>
       <c r="J102" t="n">
@@ -16331,15 +16335,15 @@
         </is>
       </c>
       <c r="AH102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>cyber security, network security, asset inventories, IDS, firewalls</t>
+        </is>
+      </c>
+      <c r="AJ102" t="b">
         <v>1</v>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>cyber security, network security, asset inventories, IDS, firewalls</t>
-        </is>
-      </c>
-      <c r="AJ102" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -16378,12 +16382,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Ingests data logs into the analytic platform according to user instructions.</t>
+          <t>Imports security logs into analytics platforms to support monitoring and threat detection.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>log aggregation, SIEM, data ingestion, security analytics, ELK stack</t>
+          <t>log aggregation, data ingestion, security analytics, SIEM, analytic platform</t>
         </is>
       </c>
       <c r="J103" t="n">
@@ -16470,13 +16474,9 @@
         </is>
       </c>
       <c r="Z103" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>Data Log Ingestion</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA103" t="inlineStr"/>
       <c r="AB103" t="b">
         <v>0</v>
       </c>
@@ -16494,15 +16494,15 @@
         </is>
       </c>
       <c r="AH103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>log aggregation, SIEM, data ingestion, security analytics, ELK stack</t>
+        </is>
+      </c>
+      <c r="AJ103" t="b">
         <v>1</v>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>log aggregation, SIEM, data ingestion, security analytics, ELK stack</t>
-        </is>
-      </c>
-      <c r="AJ103" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -16541,12 +16541,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Discusses and reviews threat data and results with required personnel.</t>
+          <t>Communicates threat findings through structured discussions and reviews with relevant personnel.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>stakeholder engagement, threat intelligence, risk reporting, data briefings, cyber security communication</t>
+          <t>threat data review, stakeholder engagement, risk reporting, data briefings, cyber security communication</t>
         </is>
       </c>
       <c r="J104" t="n">
@@ -16653,15 +16653,15 @@
         </is>
       </c>
       <c r="AH104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>stakeholder engagement, threat intelligence, risk reporting, data briefings, cyber security communication</t>
+        </is>
+      </c>
+      <c r="AJ104" t="b">
         <v>1</v>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>stakeholder engagement, threat intelligence, risk reporting, data briefings, cyber security communication</t>
-        </is>
-      </c>
-      <c r="AJ104" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -16700,12 +16700,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Collects information from alerts, logs and reported events and creates a dataset in accordance with organisational policies and procedures.</t>
+          <t>Collects and structures alerts, logs and event data in accordance with organisational data policies.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>threat intelligence, log analysis, SIEM, alerts, data logs</t>
+          <t>threat intelligence, log analysis, data ingestion, dataset creation, security monitoring</t>
         </is>
       </c>
       <c r="J105" t="n">
@@ -16816,7 +16816,7 @@
         </is>
       </c>
       <c r="AH105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI105" t="inlineStr">
         <is>
@@ -16863,12 +16863,12 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Identifies contextual factors, recognises anomalies and subtle deviations, focuses attention and remedies problems as they arise.</t>
+          <t>Monitors operational data to detect contextual anomalies and resolves deviations in a timely manner.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>outlier analysis, root‑cause analysis, statistical process control, monitoring and diagnostics</t>
+          <t>outlier analysis, root‑cause analysis, statistical process control, monitoring and diagnostics, anomaly detection</t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -16969,15 +16969,15 @@
         </is>
       </c>
       <c r="AH106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>outlier analysis, root‑cause analysis, statistical process control, monitoring and diagnostics</t>
+        </is>
+      </c>
+      <c r="AJ106" t="b">
         <v>1</v>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>outlier analysis, root‑cause analysis, statistical process control, monitoring and diagnostics</t>
-        </is>
-      </c>
-      <c r="AJ106" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Implements additional protection plan requirements and asset management processes in accordance with organisational requirements as required.</t>
+          <t>Implements additional protection plan requirements and asset management processes to safeguard assets.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>asset management, protection plans, risk mitigation, asset tracking, critical assets</t>
+          <t>asset management processes, protection plan requirements, additional protection methods, asset tracking, risk mitigation</t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -17093,7 +17093,7 @@
         <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X107" t="inlineStr"/>
       <c r="Y107" t="inlineStr">
@@ -17169,12 +17169,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Researches the organisation’s need for critical infrastructure protection and documents findings in accordance with organisational requirements.</t>
+          <t>Conducts critical infrastructure research to support protection planning and documentation requirements.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>critical infrastructure, infrastructure protection, risk assessment, threat modelling, resilience analysis</t>
+          <t>critical infrastructure protection, infrastructure protection, research findings, protection plan requirements, policy compliance</t>
         </is>
       </c>
       <c r="J108" t="n">
@@ -17275,7 +17275,7 @@
         </is>
       </c>
       <c r="AH108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI108" t="inlineStr">
         <is>
@@ -17322,12 +17322,12 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Backs up data in accordance with organisational policies and procedures.</t>
+          <t>Executes scheduled data backups in line with organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>backup data, backup software, data retention policies, storage replication, disaster recovery</t>
+          <t>backup software, data retention policies, storage replication, disaster recovery, backup data</t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -17428,7 +17428,7 @@
         </is>
       </c>
       <c r="AH109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI109" t="inlineStr">
         <is>
@@ -17475,12 +17475,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Secures devices in line with the protection plan and technical requirements.</t>
+          <t>Secures devices in accordance with the protection plan and technical requirements.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>endpoint protection, device hardening, encryption, mobile device management, asset management</t>
+          <t>endpoint protection, device hardening, security policies, encryption, protection plan requirements</t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -17628,12 +17628,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Submits protection plan to required personnel, actively seeks feedback and promptly responds to stakeholder input.</t>
+          <t>Submits protection plans to required personnel, seeks feedback, and incorporates stakeholder responses to improve outcomes.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>stakeholder communication, feedback loops, response management, plan documentation, compliance reporting</t>
+          <t>protection plan, stakeholder communication, feedback loops, response management, compliance reporting</t>
         </is>
       </c>
       <c r="J111" t="n">
@@ -17705,7 +17705,7 @@
         <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X111" t="inlineStr"/>
       <c r="Y111" t="inlineStr">
@@ -17742,7 +17742,7 @@
         </is>
       </c>
       <c r="AJ111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -17781,12 +17781,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Implements network segmentation throughout the network in accordance with the organisation's protection plan and specified technical requirements.</t>
+          <t>Implements network segmentation to isolate security zones in line with approved protection plans.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>VLANs, firewall policies, micro‑segmentation, zero‑trust architecture, network security zones</t>
+          <t>network segmentation, VLANs, firewall policies, micro‑segmentation, zero‑trust architecture</t>
         </is>
       </c>
       <c r="J112" t="n">
@@ -17887,15 +17887,15 @@
         </is>
       </c>
       <c r="AH112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>VLANs, firewall policies, micro‑segmentation, zero‑trust architecture, network security zones</t>
+        </is>
+      </c>
+      <c r="AJ112" t="b">
         <v>1</v>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>VLANs, firewall policies, micro‑segmentation, zero‑trust architecture, network security zones</t>
-        </is>
-      </c>
-      <c r="AJ112" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -17914,7 +17914,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Protection Strategy Coordination</t>
+          <t>Project Planning Coordination</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -17934,12 +17934,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Develops operational detail in stages and regularly reviews priorities and performance during strategy development and implementation.</t>
+          <t>Develops staged operational plans and regularly reviews priorities and performance during execution.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>operational planning, performance monitoring, resource allocation, timeline management, critical assets</t>
+          <t>operational planning, performance monitoring, resource allocation, timeline management, strategy development</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -18008,19 +18008,15 @@
         </is>
       </c>
       <c r="V113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W113" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 4/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>keep:3, "Protection Strategy Coordination":4</t>
+          <t>keep:4, "Protection Strategy Coordination":3</t>
         </is>
       </c>
       <c r="Z113" t="b">
@@ -18032,7 +18028,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Foundation Skill describes work style (planning and reviewing) already embedded in strategy development and implementation PCs</t>
+          <t>FS describes work style (planning and coordination) already embedded in PCs and other skills</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -18048,7 +18044,7 @@
         </is>
       </c>
       <c r="AH113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
@@ -18095,12 +18091,12 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Analyses the organisation’s existing critical infrastructure protection plan to assess its effectiveness.</t>
+          <t>Analyzes the organisation’s existing critical infrastructure protection plan.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>critical infrastructure, risk assessment, cyber security resilience, ISO 27001, vulnerability analysis</t>
+          <t>critical infrastructure protection, protection plan, infrastructure protection plan, critical assets, vulnerability analysis</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -18209,7 +18205,7 @@
         </is>
       </c>
       <c r="AJ114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -18248,12 +18244,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Develops and documents critical infrastructure protection plans in accordance with the organisational policies and procedures.</t>
+          <t>Develops and records critical infrastructure protection plans aligned with organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>critical infrastructure, risk assessment, security policy compliance, business continuity planning, incident response frameworks</t>
+          <t>critical infrastructure protection, protection plan, security policy compliance, business continuity planning, incident response frameworks</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -18354,15 +18350,15 @@
         </is>
       </c>
       <c r="AH115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>critical infrastructure, risk assessment, security policy compliance, business continuity planning, incident response frameworks</t>
+        </is>
+      </c>
+      <c r="AJ115" t="b">
         <v>1</v>
-      </c>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>critical infrastructure, risk assessment, security policy compliance, business continuity planning, incident response frameworks</t>
-        </is>
-      </c>
-      <c r="AJ115" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -18401,12 +18397,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Tests deployment of the protection plan in accordance with organisational policies and procedures as required.</t>
+          <t>Conducts protection plan testing to validate safeguards in line with organisational requirements.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>protection plan testing, cyber security, compliance testing, asset management, critical assets</t>
+          <t>protection plan, deployment testing, security policies, compliance testing, vulnerability testing</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -18511,7 +18507,7 @@
         </is>
       </c>
       <c r="AH116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI116" t="inlineStr">
         <is>
@@ -18558,7 +18554,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Obtains and analyses test results in accordance with organisational policies and procedures to inform outcomes.</t>
+          <t>Collects and analyses test results in accordance with organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -18711,12 +18707,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Determines protection, vulnerability, risk and mitigation levels in line with organisational requirements.</t>
+          <t>Determines the level of protection, vulnerability, risk and mitigation in line with organisational requirements.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>vulnerability analysis, mitigation planning, risk matrices, security governance, ISO 27001 compliance</t>
+          <t>vulnerability analysis, risk mitigation, protection plan, security governance, ISO 27001 compliance</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -18793,7 +18789,7 @@
       <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:5, "Risk Evaluation":1, "Risk Assessment":1</t>
         </is>
       </c>
       <c r="Z118" t="b">
@@ -18825,7 +18821,7 @@
         </is>
       </c>
       <c r="AJ118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -18864,12 +18860,12 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Applies software patches to devices according to documented technical requirements, ensuring correct installation and configuration.</t>
+          <t>Installs and configures software updates in line with documented technical specifications.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>patch management, vulnerability remediation, update deployment, configuration management, WSUS</t>
+          <t>patch management, vulnerability remediation, software patches, technical requirements, configuration management</t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -18970,15 +18966,15 @@
         </is>
       </c>
       <c r="AH119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>patch management, vulnerability remediation, update deployment, configuration management, WSUS</t>
+        </is>
+      </c>
+      <c r="AJ119" t="b">
         <v>1</v>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>patch management, vulnerability remediation, update deployment, configuration management, WSUS</t>
-        </is>
-      </c>
-      <c r="AJ119" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -19017,12 +19013,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Prepares complex workplace documentation that details processes and outcomes, using the required structure, layout and organisational language standards.</t>
+          <t>Produces workplace documentation using mandated structure, layout and organisational language standards.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>technical writing, process documentation, standard operating procedures, document formatting, complex language</t>
+          <t>technical writing, process documentation, standard operating procedures, document formatting, complex workplace documentation</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -19123,7 +19119,7 @@
         </is>
       </c>
       <c r="AH120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI120" t="inlineStr">
         <is>
@@ -19170,12 +19166,12 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Establishes all required data types to be included in the organisation's overall security architecture design.</t>
+          <t>Identifies and categorises data types to inform security architecture requirements.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>data types, security architecture, classification schemes, confidentiality levels, information security</t>
+          <t>security architecture, data types, classification schemes, confidentiality levels, information security</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -19262,7 +19258,7 @@
       <c r="X121" t="inlineStr"/>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:4, "Data Type Identification":3</t>
         </is>
       </c>
       <c r="Z121" t="b">
@@ -19286,7 +19282,7 @@
         </is>
       </c>
       <c r="AH121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI121" t="inlineStr">
         <is>
@@ -19333,12 +19329,12 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Submits required documentation to required personnel for initial feedback.</t>
+          <t>Submits required documentation promptly to obtain initial stakeholder feedback.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>documentation, stakeholder communication, feedback loops, record‑keeping, internal reporting</t>
+          <t>documentation, stakeholder communication, feedback loops, record‑keeping, initial feedback</t>
         </is>
       </c>
       <c r="J122" t="n">
@@ -19445,15 +19441,15 @@
         </is>
       </c>
       <c r="AH122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>documentation, stakeholder communication, feedback loops, record‑keeping, internal reporting</t>
+        </is>
+      </c>
+      <c r="AJ122" t="b">
         <v>1</v>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>documentation, stakeholder communication, feedback loops, record‑keeping, internal reporting</t>
-        </is>
-      </c>
-      <c r="AJ122" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -19492,12 +19488,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Researches and identifies industry‑standard design methodologies utilised in security architecture design.</t>
+          <t>Researches and documents industry‑standard design methodologies to inform security architecture planning.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>security architecture, design methodologies, industry standards, security frameworks, cyber security</t>
+          <t>security architecture, design methodologies, industry standards, security frameworks, security design</t>
         </is>
       </c>
       <c r="J123" t="n">
@@ -19600,7 +19596,7 @@
         </is>
       </c>
       <c r="AH123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI123" t="inlineStr">
         <is>
@@ -19627,7 +19623,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Security Anomaly Identification</t>
+          <t>Contextual Anomaly Identification</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -19647,12 +19643,12 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Uses understanding of context to recognise security anomalies and deviations from normal expectations within the organisation.</t>
+          <t>Applies contextual awareness to identify security anomalies and deviations from standard operating patterns.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>anomaly detection, pattern recognition, situational awareness, cyber security, context</t>
+          <t>anomaly detection, pattern recognition, situational awareness, contextual analysis, subtle deviations</t>
         </is>
       </c>
       <c r="J124" t="n">
@@ -19738,12 +19734,12 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>keep:0, "Security Anomaly Identification":4, "Security Contextual Problem Solving":3</t>
+          <t>keep:0, "Contextual Anomaly Identification":6, "Contextual Anomaly Detection":1</t>
         </is>
       </c>
       <c r="Z124" t="b">
@@ -19767,7 +19763,7 @@
         </is>
       </c>
       <c r="AH124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI124" t="inlineStr">
         <is>
@@ -19814,12 +19810,12 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Documents all security architecture findings and confirms them with the required personnel to ensure accuracy and agreement.</t>
+          <t>Documents and validates security architecture findings with relevant personnel.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>security architecture, architecture findings, cyber security, compliance frameworks, ISO 27001</t>
+          <t>security architecture findings, security design documentation, cyber security requirements, compliance frameworks, ISO 27001</t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -19906,7 +19902,7 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>keep:0, "Security Requirements Documentation/Security Findings Documentation":7</t>
+          <t>keep:0, "Security Requirements Documentation":7</t>
         </is>
       </c>
       <c r="Z125" t="b">
@@ -19930,7 +19926,7 @@
         </is>
       </c>
       <c r="AH125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI125" t="inlineStr">
         <is>
@@ -19977,12 +19973,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Presents security architecture documentation to stakeholders, including design specifications, risk assessments, and compliance with organisational policies.</t>
+          <t>Prepares and delivers documented security architecture presentations for stakeholder engagement.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>security architecture, enterprise architecture, security frameworks, cyber security, design methodologies</t>
+          <t>security architecture, technical presentations, information security, enterprise architecture, risk assessment</t>
         </is>
       </c>
       <c r="J126" t="n">
@@ -20089,7 +20085,7 @@
         </is>
       </c>
       <c r="AH126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI126" t="inlineStr">
         <is>
@@ -20136,12 +20132,12 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Demonstrates security design utilises major industry‑standard design methodologies consistently throughout the design process as required.</t>
+          <t>Validates security designs using industry‑recognised methodologies.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>security architecture, threat modelling, NIST framework, ISO 27001, design methodologies</t>
+          <t>security architecture, threat modelling, NIST framework, ISO 27001, industry standard design methodologies</t>
         </is>
       </c>
       <c r="J127" t="n">
@@ -20248,7 +20244,7 @@
         </is>
       </c>
       <c r="AH127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
@@ -20295,12 +20291,12 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Determines the required security level, perimeters, security features and security mode for the organisation's system.</t>
+          <t>Assesses assets to determine required security levels, perimeters, features and protection modes.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>security architecture, perimeter security, access control, cyber security, design security</t>
+          <t>security level, security features, security mode, perimeter security, security architecture</t>
         </is>
       </c>
       <c r="J128" t="n">
@@ -20411,7 +20407,7 @@
         </is>
       </c>
       <c r="AH128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI128" t="inlineStr">
         <is>
@@ -20463,7 +20459,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>cyber security governance, risk assessment, phased implementation, performance monitoring, project scheduling tools</t>
+          <t>phased implementation, performance monitoring, project scheduling, operational detail, priority review</t>
         </is>
       </c>
       <c r="J129" t="n">
@@ -20562,7 +20558,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>FS describes work style (planning and reviewing) not a distinct task; capability is implicit in design and implementation PCs</t>
+          <t>FS describes work style (planning and reviewing) not a distinct task; capability already embedded in PCs and other skills</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -20586,7 +20582,7 @@
         </is>
       </c>
       <c r="AJ129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -20625,12 +20621,12 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Analyses organisational operations and infrastructure, systematically reviewing processes and assets to identify specific security requirements.</t>
+          <t>Analyses organisational operations and infrastructure to identify specific security requirements.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>risk assessment, threat modelling, security architecture, compliance standards, vulnerability analysis</t>
+          <t>cyber security requirements, security architecture, risk assessment, compliance standards, vulnerability analysis</t>
         </is>
       </c>
       <c r="J130" t="n">
@@ -20704,7 +20700,7 @@
         <v>0</v>
       </c>
       <c r="W130" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X130" t="inlineStr"/>
       <c r="Y130" t="inlineStr">
@@ -20733,15 +20729,15 @@
         </is>
       </c>
       <c r="AH130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>risk assessment, threat modelling, security architecture, compliance standards, vulnerability analysis</t>
+        </is>
+      </c>
+      <c r="AJ130" t="b">
         <v>1</v>
-      </c>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>risk assessment, threat modelling, security architecture, compliance standards, vulnerability analysis</t>
-        </is>
-      </c>
-      <c r="AJ130" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -20780,12 +20776,12 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Designs and documents a security solution according to organisational requirements.</t>
+          <t>Designs and documents security solutions aligned with organisational standards and requirements.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>cyber security architecture, security compliance, solution documentation, threat modelling, design methodologies</t>
+          <t>security solution design, security architecture, security requirements, solution documentation, threat modelling</t>
         </is>
       </c>
       <c r="J131" t="n">
@@ -20896,7 +20892,7 @@
         </is>
       </c>
       <c r="AH131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI131" t="inlineStr">
         <is>
@@ -20943,12 +20939,12 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Prepares complex workplace documentation that details findings and solutions.</t>
+          <t>Produces detailed technical documentation outlining findings and proposed solutions.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>technical writing, documentation standards, reporting and analysis, knowledge management, architecture design</t>
+          <t>technical writing, documentation standards, findings and solutions, complex workplace documentation, knowledge management</t>
         </is>
       </c>
       <c r="J132" t="n">
@@ -21059,7 +21055,7 @@
         </is>
       </c>
       <c r="AH132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI132" t="inlineStr">
         <is>
@@ -21106,12 +21102,12 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Interprets technical, manufacturer and organisational documentation to determine and confirm job requirements.</t>
+          <t>Interprets technical, manufacturer and organisational documentation to determine and confirm job requirements before commencing work.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>technical documentation, specification standards, manufacturer manuals, job requirement analysis, engineering drawings</t>
+          <t>technical documentation, manufacturer manuals, job requirement analysis, engineering drawings, certification requirements</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -21234,7 +21230,7 @@
         </is>
       </c>
       <c r="AJ133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -21273,12 +21269,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Works autonomously to make high‑level decisions that improve organisational goals.</t>
+          <t>Makes independent strategic decisions to align actions with organisational objectives and improve performance.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>autonomy, strategic decision‑making, self‑management, leadership, organisational performance</t>
+          <t>autonomy, strategic decision‑making, self‑management, high‑level decisions, organisational performance</t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -21406,15 +21402,15 @@
         </is>
       </c>
       <c r="AH134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>autonomy, strategic decision‑making, self‑management, leadership, organisational performance</t>
+        </is>
+      </c>
+      <c r="AJ134" t="b">
         <v>1</v>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>autonomy, strategic decision‑making, self‑management, leadership, organisational performance</t>
-        </is>
-      </c>
-      <c r="AJ134" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -21453,12 +21449,12 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Develops a documented procedure for collecting and protecting forensic evidence throughout the incident response process.</t>
+          <t>Designs and implements forensic evidence collection processes to preserve data during incident response.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>chain of custody, evidence preservation, incident response, digital forensics tools, crime scene documentation</t>
+          <t>chain of custody, evidence preservation, incident response, forensic evidence, crime scene documentation</t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -21578,15 +21574,15 @@
         </is>
       </c>
       <c r="AH135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>chain of custody, evidence preservation, incident response, digital forensics tools, crime scene documentation</t>
+        </is>
+      </c>
+      <c r="AJ135" t="b">
         <v>1</v>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>chain of custody, evidence preservation, incident response, digital forensics tools, crime scene documentation</t>
-        </is>
-      </c>
-      <c r="AJ135" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -21625,12 +21621,12 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Documents detailed security incident reports of response actions and outcomes in line with task requirements.</t>
+          <t>Prepares detailed incident reports documenting response actions against task requirements.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>security incident response, incident reporting, ITIL, SIEM, compliance documentation</t>
+          <t>security incident response, incident reporting, incident response plan, incident response team, compliance documentation</t>
         </is>
       </c>
       <c r="J136" t="n">
@@ -21746,15 +21742,15 @@
         </is>
       </c>
       <c r="AH136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>security incident response, incident reporting, ITIL, SIEM, compliance documentation</t>
+        </is>
+      </c>
+      <c r="AJ136" t="b">
         <v>1</v>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>security incident response, incident reporting, ITIL, SIEM, compliance documentation</t>
-        </is>
-      </c>
-      <c r="AJ136" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -21793,7 +21789,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Assesses and documents the efficiency and effectiveness of incident response plan activities.</t>
+          <t>Evaluates incident response plans for effectiveness across hybrid operating environments.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -21922,7 +21918,7 @@
         </is>
       </c>
       <c r="AH137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI137" t="inlineStr">
         <is>
@@ -21969,12 +21965,12 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Develops incident response plans and documents them to meet the organisation's specified requirements and standards.</t>
+          <t>Develops and records incident response plans aligned with organisational requirements.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>incident handling, NIST framework, playbook development, risk management, incident response planning</t>
+          <t>incident response plan, incident handling, NIST framework, playbook development, risk management</t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -22094,7 +22090,7 @@
         </is>
       </c>
       <c r="AH138" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI138" t="inlineStr">
         <is>
@@ -22141,12 +22137,12 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Identifies and documents incident response team services clearly, ensuring they effectively meet organisational requirements and standards.</t>
+          <t>Identifies and documents incident response team roles and services to support coordinated response.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>incident response, service documentation, team coordination, organisational compliance, collaborative culture</t>
+          <t>incident response, incident response team, response team services, service documentation, organisational compliance</t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -22233,7 +22229,7 @@
         <v>0</v>
       </c>
       <c r="W139" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr">
@@ -22309,12 +22305,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Creates incident response exercises, red‑team activities and associated staffing and training requirements.</t>
+          <t>Designs incident response exercises, red‑team activities, and staffing and training plans.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>adversary simulation, incident response planning, threat modelling, security training programmes, MITRE ATT&amp;CK framework</t>
+          <t>incident response exercises, red‑teaming activities, incident response planning, staffing and training, MITRE ATT&amp;CK framework</t>
         </is>
       </c>
       <c r="J140" t="n">
@@ -22446,7 +22442,7 @@
         </is>
       </c>
       <c r="AJ140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -22485,7 +22481,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Assesses the effectiveness of communication between the incident response team and required internal and external organisations.</t>
+          <t>Evaluates the effectiveness of incident response communications across internal and external stakeholders.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -22610,7 +22606,7 @@
         </is>
       </c>
       <c r="AH141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI141" t="inlineStr">
         <is>
@@ -22657,12 +22653,12 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Interprets, analyses and documents numerical and technical system data in accordance with organisational requirements and standards.</t>
+          <t>Interprets, analyses and documents numerical and technical system data to support risk assessment.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>quantitative analysis, technical data interpretation, risk assessment, system modelling, data documentation</t>
+          <t>technical system data, quantitative analysis, data documentation, risk assessment, system modelling</t>
         </is>
       </c>
       <c r="J142" t="n">
@@ -22757,18 +22753,22 @@
         <v>0</v>
       </c>
       <c r="W142" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Technical Data Interpretation":1</t>
         </is>
       </c>
       <c r="Z142" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA142" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>Technical Data Interpretation</t>
+        </is>
+      </c>
       <c r="AB142" t="b">
         <v>0</v>
       </c>
@@ -22794,7 +22794,7 @@
         </is>
       </c>
       <c r="AJ142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -22833,12 +22833,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Applies response actions to reported security incidents in accordance with the documented incident response plan.</t>
+          <t>Executes incident response actions in accordance with approved incident response plans.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>incident response, security operations centres, SIEM, playbook execution, forensic analysis</t>
+          <t>incident response, incident response plan, security incident, response actions, security operations centre</t>
         </is>
       </c>
       <c r="J143" t="n">
@@ -22962,15 +22962,15 @@
         </is>
       </c>
       <c r="AH143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>incident response, security operations centres, SIEM, playbook execution, forensic analysis</t>
+        </is>
+      </c>
+      <c r="AJ143" t="b">
         <v>1</v>
-      </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>incident response, security operations centres, SIEM, playbook execution, forensic analysis</t>
-        </is>
-      </c>
-      <c r="AJ143" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -23009,12 +23009,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Develops and documents the incident management policy as defined by the organisation's task requirements for the organisation.</t>
+          <t>Develops and documents incident management policies aligned with organisational specifications.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>incident management, risk assessment, governance, compliance, ISO 27001</t>
+          <t>incident management policy, incident response, security incident, governance, ISO 27001</t>
         </is>
       </c>
       <c r="J144" t="n">
@@ -23138,15 +23138,15 @@
         </is>
       </c>
       <c r="AH144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>incident management, risk assessment, governance, compliance, ISO 27001</t>
+        </is>
+      </c>
+      <c r="AJ144" t="b">
         <v>1</v>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>incident management, risk assessment, governance, compliance, ISO 27001</t>
-        </is>
-      </c>
-      <c r="AJ144" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -23190,7 +23190,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>quantitative analysis, technical system data, data documentation, engineering diagnostics, calculate data</t>
+          <t>quantitative analysis, technical system data, data documentation, engineering diagnostics, numeracy interpretation</t>
         </is>
       </c>
       <c r="J145" t="n">
@@ -23365,12 +23365,12 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Evaluates system impact on business continuity.</t>
+          <t>Assesses system impacts on business continuity to identify risks and mitigation strategies.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>business continuity, impact analysis, disaster recovery, risk assessment, business risk</t>
+          <t>business continuity, impact analysis, business critical functions, risk assessment, resilience planning</t>
         </is>
       </c>
       <c r="J146" t="n">
@@ -23483,7 +23483,7 @@
         </is>
       </c>
       <c r="AH146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI146" t="inlineStr">
         <is>
@@ -23530,12 +23530,12 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Develops and implements compliance strategies to ensure organisational policies, procedures and regulatory requirements are met.</t>
+          <t>Designs and implements compliance strategies to meet organisational, commercial and regulatory requirements.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>regulatory compliance, policy enforcement, risk management, governance, audit</t>
+          <t>regulatory compliance, policy enforcement, risk management, governance, legislative requirements</t>
         </is>
       </c>
       <c r="J147" t="n">
@@ -23636,7 +23636,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>FS describes work style (ensuring compliance) rather than a distinct task; capability is implicit in other skills like Risk Analysis and Business Continuity Evaluation</t>
+          <t>FS describes work style and compliance activity already implicit in other skills; not a distinct task for this unit</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -23660,7 +23660,7 @@
         </is>
       </c>
       <c r="AJ147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -23699,12 +23699,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Develops a contingency plan that identifies organisational threats to support business continuity and operational resilience.</t>
+          <t>Develops contingency plans by identifying threats.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>risk assessment, business continuity, threat identification, mitigation strategies, scenario analysis</t>
+          <t>contingency planning, threat identification, business continuity, mitigation strategies, disaster recovery plan</t>
         </is>
       </c>
       <c r="J148" t="n">
@@ -23801,13 +23801,9 @@
         </is>
       </c>
       <c r="Z148" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA148" t="inlineStr">
-        <is>
-          <t>Disaster Recovery Planning</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA148" t="inlineStr"/>
       <c r="AB148" t="b">
         <v>0</v>
       </c>
@@ -23833,7 +23829,7 @@
         </is>
       </c>
       <c r="AJ148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -23872,12 +23868,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Evaluates and documents prevention and recovery options against business specifications and cost constraints in the organisation.</t>
+          <t>Evaluates and documents prevention and recovery options against business specifications and cost constraints.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>cost‑benefit analysis, business specifications, commercial requirements, risk assessment, financial modelling</t>
+          <t>cost constraints, business specifications, recovery options, disaster recovery plan, risk minimisation</t>
         </is>
       </c>
       <c r="J149" t="n">
@@ -24037,12 +24033,12 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Develops comprehensive disaster recovery plans detailing procedures, resources and recovery timeframes to support rapid restoration of essential services.</t>
+          <t>Develops comprehensive disaster recovery plans detailing procedures, resources and recovery timeframes.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>business continuity, disaster recovery testing, recovery time objectives, risk assessment, business critical</t>
+          <t>disaster recovery plan, business continuity, recovery time objectives, risk assessment, disaster recovery testing</t>
         </is>
       </c>
       <c r="J150" t="n">
@@ -24159,7 +24155,7 @@
         </is>
       </c>
       <c r="AH150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI150" t="inlineStr">
         <is>
@@ -24206,12 +24202,12 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Reviews industry standard operational procedures and checks that required risk safeguards are documented and implemented.</t>
+          <t>Reviews operational procedures against industry benchmarks to verify risk controls.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>compliance, risk management, standard operating procedures, regulatory guidance, certification requirements</t>
+          <t>industry standard operational, risk safeguards, standard operating procedures, compliance, risk management</t>
         </is>
       </c>
       <c r="J151" t="n">
@@ -24324,7 +24320,7 @@
         </is>
       </c>
       <c r="AH151" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI151" t="inlineStr">
         <is>
@@ -24540,12 +24536,12 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Formulates a prevention and recovery strategy for the organisation to improve system resilience.</t>
+          <t>Designs and implements prevention and recovery strategies to strengthen system resilience.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>risk assessment, mitigation planning, contingency strategies, recovery planning, scenario analysis</t>
+          <t>prevention strategy, recovery strategy, disaster recovery plan, contingency strategies, risk assessment</t>
         </is>
       </c>
       <c r="J153" t="n">
@@ -24662,15 +24658,15 @@
         </is>
       </c>
       <c r="AH153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>risk assessment, mitigation planning, contingency strategies, recovery planning, scenario analysis</t>
+        </is>
+      </c>
+      <c r="AJ153" t="b">
         <v>1</v>
-      </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>risk assessment, mitigation planning, contingency strategies, recovery planning, scenario analysis</t>
-        </is>
-      </c>
-      <c r="AJ153" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -24802,7 +24798,7 @@
         <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>0.95</v>
+        <v>0.9428571428571428</v>
       </c>
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="inlineStr">
@@ -24882,12 +24878,12 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Carries out risk analysis, disaster recovery and contingency planning to ensure organisational resilience and compliance with standards.</t>
+          <t>Conducts comprehensive risk assessments and develops disaster recovery and contingency solutions.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>risk assessment, disaster recovery, contingency planning, business continuity, business risk</t>
+          <t>risk assessment, disaster recovery, contingency planning, business continuity, threat modelling</t>
         </is>
       </c>
       <c r="J155" t="n">
@@ -25004,7 +25000,7 @@
         </is>
       </c>
       <c r="AH155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI155" t="inlineStr">
         <is>
@@ -25012,7 +25008,7 @@
         </is>
       </c>
       <c r="AJ155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -25051,12 +25047,12 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Submits required documents to designated personnel, actively seeks stakeholder feedback and promptly responds to their comments.</t>
+          <t>Engages stakeholders through timely document submission, feedback collection and response.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>stakeholder engagement, feedback loops, document management, communication protocols, collaborative culture</t>
+          <t>stakeholder engagement, feedback loops, document management, communication protocols, document disaster recovery</t>
         </is>
       </c>
       <c r="J156" t="n">
@@ -25169,7 +25165,7 @@
         </is>
       </c>
       <c r="AH156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI156" t="inlineStr">
         <is>
@@ -25216,7 +25212,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Demonstrates strategic planning of priorities and outcomes to achieve organisational objectives within the organisation effectively.</t>
+          <t>Develops and aligns hybrid work priorities and outcomes through structured strategic planning.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -25310,7 +25306,7 @@
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>keep:4, "Strategy Prioritisation":2, "Priority Planning":1</t>
+          <t>keep:4, "Strategy Prioritisation":3</t>
         </is>
       </c>
       <c r="Z157" t="b">
@@ -25322,7 +25318,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Foundation Skill describes a work style (strategic planning) that is already embedded in other skills and PCs</t>
+          <t>Foundation Skill describes a work style (strategic planning) that is already implicit in other skills and PCs</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -25338,7 +25334,7 @@
         </is>
       </c>
       <c r="AH157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI157" t="inlineStr">
         <is>
@@ -25390,7 +25386,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>communication tools, relationship building, collaborative culture, stakeholder engagement, interpersonal communication</t>
+          <t>communication tools, relationship building, stakeholder engagement, collaboration platforms, interpersonal communication</t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -25511,7 +25507,7 @@
         </is>
       </c>
       <c r="AJ158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -25555,7 +25551,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>specification drafting, process documentation, evaluation reporting, strategic articulation, document control</t>
+          <t>evaluation reporting, strategic articulation, document control, disaster strategy documentation, process documentation</t>
         </is>
       </c>
       <c r="J159" t="n">
@@ -25676,7 +25672,7 @@
         </is>
       </c>
       <c r="AJ159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
@@ -25715,7 +25711,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Evaluates system threats to inform mitigation planning.</t>
+          <t>Assesses system vulnerabilities through structured threat identification and analysis to support mitigation planning.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -25837,7 +25833,7 @@
         </is>
       </c>
       <c r="AH160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI160" t="inlineStr">
         <is>
@@ -25882,12 +25878,12 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Responds to stakeholder questions with clear, evidence‑based answers, supporting each response with relevant data or rationale.</t>
+          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting decisions with relevant data and reasoning.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>evidence based answers, substantiated responses, data support, analytical processes, stakeholder queries</t>
+          <t>evidence based answers, stakeholder queries, substantiated responses, data support, reasoning justification</t>
         </is>
       </c>
       <c r="J161" t="n">
@@ -25978,19 +25974,19 @@
       </c>
       <c r="AG161" t="inlineStr">
         <is>
-          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting each response with relevant data or rationale.</t>
+          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting decisions with relevant data and reasoning.</t>
         </is>
       </c>
       <c r="AH161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>evidence based answers, stakeholder queries, substantiated responses, data support, rationale provision</t>
+          <t>evidence based answers, stakeholder queries, substantiated responses, data support, reasoning justification</t>
         </is>
       </c>
       <c r="AJ161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -26027,7 +26023,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Confirms what information is held on each registered digital device.</t>
+          <t>Assists in confirming and documenting the types of information stored on each registered digital device.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -26127,7 +26123,7 @@
         </is>
       </c>
       <c r="AH162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI162" t="inlineStr">
         <is>
@@ -26172,16 +26168,16 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Obtains final sign‑off from designated personnel for the required documentation.</t>
+          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>approval process, stakeholder engagement, sign‑off acquisition, decision making, documentation review</t>
+          <t>approval process, stakeholder engagement, compliance confirmation, sign‑off management, finalisation</t>
         </is>
       </c>
       <c r="J163" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -26245,7 +26241,7 @@
         <v>0</v>
       </c>
       <c r="W163" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="X163" t="inlineStr">
         <is>
@@ -26270,19 +26266,19 @@
       </c>
       <c r="AG163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated personnel by organising, presenting, and confirming required sign‑off documentation.</t>
+          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
         </is>
       </c>
       <c r="AH163" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>approval process, stakeholder engagement, documentation review, sign‑off acquisition, finalisation</t>
+          <t>approval process, stakeholder engagement, compliance confirmation, sign‑off management, finalisation</t>
         </is>
       </c>
       <c r="AJ163" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -26319,12 +26315,12 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Identifies organisational processes and transaction types suitable for blockchain and determines relevant legislation, policies and their impact on the solution.</t>
+          <t>Identifies organisational processes and transaction types suitable for blockchain, and determines relevant legislation, organisational policies and procedures and their impact on the blockchain solution.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>blockchain technology, organisational processes, transactional types, legislation compliance, suitability assessment</t>
+          <t>blockchain suitability, transactional types, organisational processes, compliance impact, solution impact</t>
         </is>
       </c>
       <c r="J164" t="n">
@@ -26454,7 +26450,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Data Log Strategy Discussion</t>
+          <t>Log Requirement Consultation</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -26474,16 +26470,16 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Discusses and confirms data log requirements and processing strategy thoroughly with required personnel in the workplace.</t>
+          <t>Facilitates discussion with relevant personnel to confirm data log requirements and processing strategy.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel coordination, discussion facilitation, requirement confirmation</t>
+          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, collaborative discussion</t>
         </is>
       </c>
       <c r="J165" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -26538,14 +26534,14 @@
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>Data Log Strategy Discussion</t>
+          <t>Log Requirement Consultation</t>
         </is>
       </c>
       <c r="V165" t="b">
         <v>0</v>
       </c>
       <c r="W165" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="X165" t="inlineStr">
         <is>
@@ -26570,15 +26566,15 @@
       </c>
       <c r="AG165" t="inlineStr">
         <is>
-          <t>Facilitates discussions with relevant personnel to confirm data log requirements and processing strategies.</t>
+          <t>Facilitates discussion with relevant personnel to confirm data log requirements and processing strategy.</t>
         </is>
       </c>
       <c r="AH165" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel coordination, discussion facilitation, requirement confirmation</t>
+          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, collaborative discussion</t>
         </is>
       </c>
       <c r="AJ165" t="b">
@@ -26619,12 +26615,12 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Obtains and analyses threat data results to accurately confirm reliability and consistency before further processing.</t>
+          <t>Evaluates gathered threat data results to ensure reliability and consistency before further processing.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>reliability assessment, consistency verification, data validation, result evaluation, data logs</t>
+          <t>reliability assessment, consistency verification, data validation, result evaluation, false negative analysis</t>
         </is>
       </c>
       <c r="J166" t="n">
@@ -26719,7 +26715,7 @@
         </is>
       </c>
       <c r="AH166" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI166" t="inlineStr">
         <is>
@@ -26764,12 +26760,12 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Determines the plan’s effectiveness and alignment with organisational requirements and identifies operational systems, critical assets, segmentation and legislative obligations.</t>
+          <t>Evaluates the effectiveness and alignment of the existing protection plan with organisational requirements, and identifies operational systems, critical assets, network segmentation and legislative requirements.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>plan effectiveness, organisational requirements, critical assets, legislative compliance, asset management</t>
+          <t>plan effectiveness, organisational requirements, critical assets, legislative compliance, operational systems</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -26867,7 +26863,7 @@
       </c>
       <c r="AG167" t="inlineStr">
         <is>
-          <t>Evaluates how well the current protection plan meets organisational needs and regulatory requirements.</t>
+          <t>Evaluates how well the current protection plan meets organisational needs and regulatory standards.</t>
         </is>
       </c>
       <c r="AH167" t="b">
@@ -26901,7 +26897,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>DOMAIN_KNOWLEDGE</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -26911,17 +26907,17 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>THEORETICAL</t>
+          <t>PRACTICAL</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Determines and documents the plan’s alignment with requirements, submits the report and seeks and responds to feedback.</t>
+          <t>Determines and documents the alignment of the existing incident response plan against identified requirements, submits the documentation to required personnel, and seeks and responds to feedback.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment analysis, documentation, requirements mapping, stakeholder feedback</t>
+          <t>incident response plan, alignment, documentation, requirements, feedback</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -27026,7 +27022,7 @@
       </c>
       <c r="AG168" t="inlineStr">
         <is>
-          <t>Aligns the current incident response plan with required standards and documents the comparison for stakeholders.</t>
+          <t>Aligns the current incident response plan with requirements and documents the comparison for stakeholders.</t>
         </is>
       </c>
       <c r="AH168" t="b">
@@ -27034,7 +27030,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment analysis, documentation, requirements mapping, stakeholder feedback</t>
+          <t>incident response plan, alignment, documentation, requirements, feedback</t>
         </is>
       </c>
       <c r="AJ168" t="b">
@@ -27075,12 +27071,12 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Assist in collecting, processing, and preserving evidence in line with the organisation's established incident response requirements.</t>
+          <t>Assist in gathering, processing, and securely preserving evidence in line with established incident response requirements.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, incident response, assistance</t>
+          <t>evidence collection, evidence processing, evidence preservation, forensic evidence, incident response</t>
         </is>
       </c>
       <c r="J169" t="n">
@@ -27188,15 +27184,15 @@
         </is>
       </c>
       <c r="AH169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>evidence collection, evidence processing, evidence preservation, incident response, assistance</t>
+        </is>
+      </c>
+      <c r="AJ169" t="b">
         <v>1</v>
-      </c>
-      <c r="AI169" t="inlineStr">
-        <is>
-          <t>evidence collection, evidence processing, evidence preservation, incident response, assistance</t>
-        </is>
-      </c>
-      <c r="AJ169" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -27233,16 +27229,16 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Identify business critical functions, security environment, critical data/software, and assess impact of business risk and threats on ICT systems.</t>
+          <t>Identify essential business critical functions, the required security environment, critical data and software, and assess the potential impact of business risk and threats on ICT systems.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>business critical functions, security environment, critical data, software assets, risk impact assessment</t>
+          <t>business critical functions, security environment, critical data, software assets, ICT risk assessment</t>
         </is>
       </c>
       <c r="J170" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -27312,7 +27308,7 @@
         <v>0</v>
       </c>
       <c r="W170" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="X170" t="inlineStr">
         <is>
@@ -27337,7 +27333,7 @@
       </c>
       <c r="AG170" t="inlineStr">
         <is>
-          <t>Identify essential business functions, critical data, and software, and assess risk impacts on ICT systems.</t>
+          <t>Identify essential business functions, critical data, and software, and assess ICT risk impacts on them.</t>
         </is>
       </c>
       <c r="AH170" t="b">
@@ -27345,7 +27341,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>business critical functions, security environment, critical data, software assets, risk impact assessment</t>
+          <t>business critical functions, security environment, critical data, software assets, ICT risk assessment</t>
         </is>
       </c>
       <c r="AJ170" t="b">
@@ -27386,12 +27382,12 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Identify and document disaster strategy processes, required cut‑over criteria, and obtain necessary final task sign‑off.</t>
+          <t>Creates and records detailed disaster strategy processes, cut‑over criteria, and secures final task sign‑off.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>disaster strategy, process documentation, cut‑over criteria, task sign‑off, business risk</t>
+          <t>disaster strategy processes, cut‑over criteria plan, task sign‑off, disaster recovery plan, documentation</t>
         </is>
       </c>
       <c r="J171" t="n">
@@ -27494,7 +27490,7 @@
         </is>
       </c>
       <c r="AH171" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI171" t="inlineStr">
         <is>

--- a/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v7.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v7.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>active listening, stakeholder engagement, feedback, communication, collaboration</t>
+          <t>stakeholder engagement, feedback, empathy, communication, ideas elicitation</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -820,7 +820,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>benchmarking, best practice examples, similar products, performance metrics, industry standards</t>
+          <t>benchmarking, best practice, best practice examples, similar products, industry standards</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -987,7 +987,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ideation, brainstorming, idea generation, creative problem solving, group facilitation</t>
+          <t>ideation, brainstorming, creative problem solving, mind mapping, group facilitation</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>record‑keeping, compliance, audit trail, quality assurance, organisational standards</t>
+          <t>record‑keeping, compliance, audit trail, quality assurance, feedback documentation</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="AJ7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Solution Viability Assessment</t>
+          <t>Idea Viability Evaluation</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>feasibility analysis, risk assessment, criteria weighting, business case evaluation, market viability</t>
+          <t>feasibility analysis, criteria weighting, business case evaluation, market viability, viability assessment</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -1721,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1730,17 +1730,13 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>keep:0, "Solution Viability Assessment/Idea Viability Assessment":4, "Idea Viability Evaluation":3</t>
+          <t>keep:0, "Idea Viability Evaluation":4, "Solution Viability Assessment/Idea Viability Assessment":3</t>
         </is>
       </c>
       <c r="Z8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Solution Viability Assessment</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="b">
         <v>0</v>
       </c>
@@ -1766,7 +1762,7 @@
         </is>
       </c>
       <c r="AJ8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1810,7 +1806,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>stakeholder engagement, issue selection, consultation processes, problem identification, decision‑making</t>
+          <t>stakeholder engagement, problem identification, needs assessment, consultation processes, issue selection</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1977,7 +1973,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>stakeholder communication, business case development, grant and RFP responses, technical documentation, persuasive writing</t>
+          <t>stakeholder communication, business case development, grant and RFP responses, persuasive writing, proposal preparation</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -2092,7 +2088,7 @@
         </is>
       </c>
       <c r="AJ10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2136,7 +2132,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>literature review, search strategies, online databases, evidence‑based analysis, possible solutions</t>
+          <t>literature review, data collection, search strategies, online databases, evidence‑based analysis</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -2251,7 +2247,7 @@
         </is>
       </c>
       <c r="AJ11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2295,7 +2291,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>solution presentation, stakeholder communication, format selection, visual presentation tools, business briefings</t>
+          <t>solution presentation, stakeholder communication, visual presentation tools, format selection, solution pitching</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -2373,16 +2369,16 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>keep:4, "Solution Presentation":3</t>
+          <t>keep:3, "Solution Presentation":4</t>
         </is>
       </c>
       <c r="Z12" t="b">
@@ -2458,7 +2454,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>requirements analysis, solution finalisation, task requirements, validation feedback, continuous improvement</t>
+          <t>requirements analysis, design optimisation, prototype testing, validation feedback, solution finalisation</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -2540,7 +2536,7 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2549,7 +2545,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>keep:6, "Solution Refinement":1</t>
+          <t>keep:5, "Solution Refinement":2</t>
         </is>
       </c>
       <c r="Z13" t="b">
@@ -2625,7 +2621,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>feasibility analysis, constraint identification, business issue evaluation, risk assessment, solution viability</t>
+          <t>feasibility analysis, constraint identification, business issue evaluation, viability assessment, solution evaluation</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -2780,7 +2776,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>stakeholder engagement, feedback collection, surveys, interviews, active elicitation</t>
+          <t>stakeholder engagement, feedback collection, surveys, interviews, stakeholder feedback</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -2862,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr">
@@ -2918,7 +2914,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Discussion Facilitation</t>
+          <t>Group Interaction Facilitation</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3029,12 +3025,12 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>keep:1, "Discussion Facilitation":6</t>
+          <t>keep:0, "Group Interaction Facilitation":4, "Discussion Facilitation":3</t>
         </is>
       </c>
       <c r="Z16" t="b">
@@ -3105,7 +3101,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Designs, implements and updates organisation‑wide cyber security awareness programs in line with best practice.</t>
+          <t>Creates and updates cyber security awareness program that reflects organisation-wide best practice.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -3193,7 +3189,7 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr">
@@ -3222,7 +3218,7 @@
         </is>
       </c>
       <c r="AH17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
@@ -3269,12 +3265,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Uses clear, specific and industry-related cyber security terminology in workplace documents.</t>
+          <t>Writes workplace documents using precise cyber security terminology to clearly convey technical information.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>cyber security terminology, technical documentation, industry standards, information security policies, clear specific language</t>
+          <t>cyber security terminology, technical documentation, information security policies, industry standards (ISO 27001, NIST), risk assessment reporting</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -3374,7 +3370,7 @@
         </is>
       </c>
       <c r="AH18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
@@ -3382,7 +3378,7 @@
         </is>
       </c>
       <c r="AJ18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3426,7 +3422,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>cyber security awareness, security awareness program, risk awareness, threat intelligence, security posture</t>
+          <t>cyber security awareness, security awareness program, level of awareness, cyber security, risk awareness</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -3586,7 +3582,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>cyber security improvement, review outcomes, security standards, policy compliance, stakeholder reporting</t>
+          <t>cyber security, security improvement, review outcomes, policy compliance, stakeholder reporting</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -3738,7 +3734,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>stakeholder communication, knowledge transfer, visual storytelling, review outcomes, presentation tools</t>
+          <t>stakeholder communication, knowledge transfer, visual storytelling, presentation tools, review outcomes</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -3813,16 +3809,16 @@
         <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>keep:0, "Insight Presentation":7</t>
+          <t>keep:1, "Insight Presentation":6</t>
         </is>
       </c>
       <c r="Z21" t="b">
@@ -3898,7 +3894,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Notifiable Data Breach, Australian Privacy Act, data breach legislation, data protection implications, privacy laws</t>
+          <t>Notifiable Data Breach, Australian Privacy Act, data breach legislation, privacy law interpretation, data protection implications</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -4049,7 +4045,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Documents detailed review outcome reports outlining improvement recommendations for relevant personnel.</t>
+          <t>Prepares detailed review outcome reports outlining improvement recommendations for relevant personnel.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -4133,7 +4129,7 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr">
@@ -4162,7 +4158,7 @@
         </is>
       </c>
       <c r="AH23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
@@ -4378,7 +4374,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>cyber security practices, policy compliance, security governance, audit controls, risk assessment</t>
+          <t>cyber security practices, policy compliance, risk assessment, security governance, audit controls</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -4542,7 +4538,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>cyber security documentation, information security records, compliance logging, data governance, security protection</t>
+          <t>cyber security documentation, information security records, compliance logging, data governance, records and documentation</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -4702,7 +4698,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>stakeholder engagement, decision support, needs analysis, facilitation, communication</t>
+          <t>stakeholder engagement, consultation workshops, decision support, needs analysis, facilitation</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -4810,7 +4806,7 @@
         </is>
       </c>
       <c r="AJ27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -4849,7 +4845,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Collaborates with interdisciplinary teams to review and promote cyber security in the workplace.</t>
+          <t>Collaborates with interdisciplinary teams to promote cyber security.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -5169,12 +5165,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Analyses current cyber threat reports to assess organisational impacts and advise on security measures.</t>
+          <t>Reviews latest cyber security threats and trends impacting organisations.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>cyber security threats, threat intelligence, trend monitoring, security analytics, cyber security trends</t>
+          <t>cyber security threats, threat intelligence, trend monitoring, security analytics, trends impacting organisations</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -5282,7 +5278,7 @@
         </is>
       </c>
       <c r="AH30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
@@ -5334,7 +5330,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>training schedules, record management, information updates, training logistics, cyber security awareness</t>
+          <t>training schedules, learning management systems, record management, information updates, training coordination</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -5605,12 +5601,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Installs and runs up‑to‑date anti‑malware on all workstations to ensure continuous protection.</t>
+          <t>Installs and configures up‑to‑date anti‑malware on all workstations to ensure continuous protection.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>anti-malware, endpoint protection, malware scanning, signature updates, cyber security</t>
+          <t>anti-malware, endpoint protection, malware scanning, signature updates, security hygiene</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -5721,7 +5717,7 @@
         </is>
       </c>
       <c r="AH34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
@@ -5773,7 +5769,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>business impact analysis, breach review, incident tracking, risk assessment, security metrics</t>
+          <t>risk assessment, incident tracking, business impact analysis, breach review, security metrics</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -5907,7 +5903,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Device Configuration Setup</t>
+          <t>Device Configuration</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -6003,15 +5999,19 @@
         </is>
       </c>
       <c r="V36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X36" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 4/7: </t>
+        </is>
+      </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:3, "Device Configuration":4</t>
         </is>
       </c>
       <c r="Z36" t="b">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>encryption, device security, endpoint encryption, mobile device management, cryptography</t>
+          <t>encryption, device security, endpoint encryption, mobile device management, mobile devices</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -6198,7 +6198,7 @@
         </is>
       </c>
       <c r="AJ37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>IT asset tracking, hardware registers, network inventories, CMDB, digital device register</t>
+          <t>IT asset tracking, hardware registers, network inventories, CMDB, digital devices</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>gap analysis, best practice strategies, effectiveness evaluation, benchmarking, performance metrics</t>
+          <t>gap analysis, best practice strategies, effectiveness evaluation, performance metrics, process improvement</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -6826,13 +6826,9 @@
         </is>
       </c>
       <c r="Z41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>Security Plan Communication</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="b">
         <v>0</v>
       </c>
@@ -6902,7 +6898,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>risk assessment, information sensitivity, device classification, cyber security, risk matrices</t>
+          <t>risk assessment, information sensitivity, device classification, risk matrices, level of risk</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -6980,16 +6976,16 @@
         <v>1</v>
       </c>
       <c r="W42" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>keep:0, "Data Risk Categorisation":7</t>
+          <t>keep:1, "Data Risk Categorisation":6</t>
         </is>
       </c>
       <c r="Z42" t="b">
@@ -7021,7 +7017,7 @@
         </is>
       </c>
       <c r="AJ42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -7040,7 +7036,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Security Plan Communication</t>
+          <t>Physical Security Plan Communication</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -7065,7 +7061,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>physical security, security plan, stakeholder communication, risk assessment, security policy</t>
+          <t>physical security, risk assessment, security policy, stakeholder communication, access control</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -7144,21 +7140,29 @@
         </is>
       </c>
       <c r="V43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W43" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X43" t="inlineStr"/>
+        <v>0.905</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 4/7: </t>
+        </is>
+      </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>keep:5, "Physical Security Plan Communication/Physical Security Communication":2</t>
+          <t>keep:1, "Physical Security Plan Communication":4, "Physical Security Planning":2</t>
         </is>
       </c>
       <c r="Z43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Physical Security Planning</t>
+        </is>
+      </c>
       <c r="AB43" t="b">
         <v>0</v>
       </c>
@@ -7184,7 +7188,7 @@
         </is>
       </c>
       <c r="AJ43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -7228,7 +7232,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>risk assessment, security protocol, device hardening, cyber security governance, physical security</t>
+          <t>risk assessment, security protocol, device hardening, cyber security governance, protocol compliance</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -7391,7 +7395,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>security strategies, cyber security governance, risk assessment, security frameworks, ISO 27001</t>
+          <t>security strategies, security frameworks, risk assessment, cyber security governance, ISO 27001</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -7473,7 +7477,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr">
@@ -7529,7 +7533,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Security Trend Monitoring</t>
+          <t>Security Development Monitoring</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -7554,7 +7558,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>cyber security, threat intelligence, vulnerability tracking, security intelligence feeds, digital risk monitoring</t>
+          <t>digital security, cyber security, threat intelligence, vulnerability tracking, security intelligence feeds</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -7629,15 +7633,19 @@
         </is>
       </c>
       <c r="V46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X46" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 4/7: </t>
+        </is>
+      </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>keep:4, "Security Development Monitoring":3</t>
+          <t>keep:3, "Security Development Monitoring":4</t>
         </is>
       </c>
       <c r="Z46" t="b">
@@ -7669,7 +7677,7 @@
         </is>
       </c>
       <c r="AJ46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -7851,7 +7859,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Multi-factor Authentication Enablement</t>
+          <t>Two-factor Authentication Enablement</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -7876,7 +7884,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>multi-factor authentication, two-factor authentication, OTP, access control, cyber security</t>
+          <t>multi‑factor authentication, MFA, OTP, access control, cyber security</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -7958,16 +7966,16 @@
         <v>1</v>
       </c>
       <c r="W48" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>keep:3, "Multi-factor Authentication Enablement":4</t>
+          <t>keep:4, "Multi-factor Authentication Enablement":3</t>
         </is>
       </c>
       <c r="Z48" t="b">
@@ -7999,7 +8007,7 @@
         </is>
       </c>
       <c r="AJ48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -8184,7 +8192,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Ranks proposed changes to clarify improvement opportunities and inform implementation scheduling.</t>
+          <t>Prioritises proposed changes to refine opportunities and assist in scheduling implementation.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -8287,7 +8295,7 @@
         </is>
       </c>
       <c r="AH50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
@@ -8489,7 +8497,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>technical writing, document review, quality assurance, reporting standards, document control</t>
+          <t>technical writing, document review, quality assurance, document control, evaluation process</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -8554,16 +8562,16 @@
         <v>1</v>
       </c>
       <c r="W52" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>keep:0, "Evaluation Documentation":7</t>
+          <t>keep:0, "Evaluation Documentation":6, "Evaluation Documentation Preparation":1</t>
         </is>
       </c>
       <c r="Z52" t="b">
@@ -8595,7 +8603,7 @@
         </is>
       </c>
       <c r="AJ52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -8614,7 +8622,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ict Gap Identification</t>
+          <t>ICT Gap Identification</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -8634,12 +8642,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Analyses strategic objectives against current ICT capability in hybrid environments to identify gaps and propose improvements.</t>
+          <t>Compares strategic objectives with current ICT capability to identify gaps, improvement opportunities, and propose changes.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>gap analysis, strategic alignment, ICT gaps, improvement opportunities, proposed changes</t>
+          <t>gap analysis, strategic alignment, ICT governance, digital transformation, ICT gaps</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -8713,15 +8721,19 @@
         </is>
       </c>
       <c r="V53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W53" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X53" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/7: </t>
+        </is>
+      </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>keep:5, "ICT Gap Identification":2</t>
+          <t>keep:2, "ICT Gap Identification":5</t>
         </is>
       </c>
       <c r="Z53" t="b">
@@ -8745,7 +8757,7 @@
         </is>
       </c>
       <c r="AH53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
@@ -8792,7 +8804,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Assesses proposed ICT system and product changes in hybrid environments for alignment with organisational strategic objectives.</t>
+          <t>Assesses the impact of proposed ICT system and product changes in hybrid environments against organisational strategic objectives.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -8878,7 +8890,7 @@
         <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr">
@@ -8954,12 +8966,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Researches and tests innovative ideas, applying findings to refine work practices and processes.</t>
+          <t>Investigates innovative ideas and applies findings to refine work practices and processes.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>continuous improvement, process optimisation, ideation techniques, creative problem solving, innovation management</t>
+          <t>continuous improvement, process optimisation, ideation techniques, innovative ideas, innovation management</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -9024,12 +9036,12 @@
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>keep:6, "Innovative Idea Investigation":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z55" t="b">
@@ -9053,7 +9065,7 @@
         </is>
       </c>
       <c r="AH55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
@@ -9061,7 +9073,7 @@
         </is>
       </c>
       <c r="AJ55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -9105,7 +9117,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>financial analysis, quantitative modelling, cost‑benefit assessment, numerical data interpretation, mathematical calculations</t>
+          <t>financial analysis, quantitative modelling, cost‑benefit assessment, numerical data, mathematical calculations</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -9170,12 +9182,12 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0.95</v>
+        <v>0.952</v>
       </c>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>keep:2, "Financial Impact Assessment":3, "Financial Impact Interpretation":2</t>
+          <t>keep:5, "Financial Impact Interpretation":1, "Financial Impact Assessment":1</t>
         </is>
       </c>
       <c r="Z56" t="b">
@@ -9251,7 +9263,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>regulatory standards, compliance frameworks, policy implementation planning, action plan, implementation methods</t>
+          <t>regulatory standards, compliance frameworks, risk assessment, policy implementation planning, action plan</t>
         </is>
       </c>
       <c r="J57" t="n">
@@ -9518,7 +9530,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Difficulty Evaluation</t>
+          <t>Implementation Difficulty Evaluation</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -9538,12 +9550,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Assesses the difficulty of implementing proposed changes to ICT systems and products.</t>
+          <t>Evaluates the difficulty of implementing proposed changes to ICT systems and products.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>implementation complexity, change management, ICT systems, difficulty evaluation, impact assessment</t>
+          <t>ICT systems, change management, implementation difficulty, proposed changes, impact assessment</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -9608,16 +9620,16 @@
         <v>1</v>
       </c>
       <c r="W59" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name includes 'Planning' which is not present in the evidence; evidence only involves evaluating difficulty</t>
+          <t>MIS re-refinement: Skill name uses 'Planning' but evidence describes evaluating difficulty, not planning</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>keep:6, "Implementation Difficulty Assessment":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z59" t="b">
@@ -9633,7 +9645,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>Skill name includes 'Planning' which is not present in the evidence; evidence only involves evaluating difficulty</t>
+          <t>Skill name uses 'Planning' but evidence describes evaluating difficulty, not planning</t>
         </is>
       </c>
       <c r="AF59" t="b">
@@ -9697,7 +9709,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>gap analysis, improvement opportunities, proposed changes, executive communication, business reporting</t>
+          <t>executive communication, gap analysis, improvement recommendations, business reporting, proposed changes</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -9774,7 +9786,7 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr">
@@ -9855,7 +9867,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>strategic alignment, industry benchmarking, SWOT analysis, organisational objectives, gap analysis</t>
+          <t>strategic plan, industry environment, organisational objectives, SWOT analysis, gap analysis</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -9973,7 +9985,7 @@
         </is>
       </c>
       <c r="AJ61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -10017,7 +10029,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>analytical decision making, systematic decision processes, complex decision analysis, non-routine decision modelling, risk assessment</t>
+          <t>decision analysis, analytical reasoning, systematic decision making, risk assessment, scenario modelling</t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -10163,7 +10175,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>plain English, technical terminology translation, stakeholder communication, technical writing, audience adaptation</t>
+          <t>plain language, jargon translation, stakeholder communication, technical writing, audience adaptation</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -10265,7 +10277,7 @@
         </is>
       </c>
       <c r="AJ63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -10309,7 +10321,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>legislative compliance, regulatory standards, policy analysis, industry standards, certification requirements</t>
+          <t>legislative compliance, policy analysis, regulatory standards, qualitative analysis, legislative standards</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -10437,7 +10449,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Compliance Review</t>
+          <t>Compliance Management</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -10457,12 +10469,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Evaluates organisational privacy policies and procedures against industry standards to ensure compliance in hybrid environments.</t>
+          <t>Evaluates organisational privacy policies against industry standards to ensure compliance in hybrid environments.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>privacy policy, industry standard requirements, regulatory standards, compliance review, data protection</t>
+          <t>privacy policy, industry standard requirements, compliance assessment, regulatory standards, data protection</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -10527,16 +10539,12 @@
         </is>
       </c>
       <c r="V65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W65" t="n">
         <v>0.95</v>
       </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>MIS re-refinement: Skill name uses 'Management' which is not reflected in evidence verbs 'review' and 'determine', indicating a different activity</t>
-        </is>
-      </c>
+      <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr">
         <is>
           <t>keep:7</t>
@@ -10551,13 +10559,9 @@
       </c>
       <c r="AC65" t="inlineStr"/>
       <c r="AD65" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE65" t="inlineStr">
-        <is>
-          <t>Skill name uses 'Management' which is not reflected in evidence verbs 'review' and 'determine', indicating a different activity</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="b">
         <v>0</v>
       </c>
@@ -10567,7 +10571,7 @@
         </is>
       </c>
       <c r="AH65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
@@ -10614,12 +10618,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Reviews ethical practices and feedback and determines the appropriate application of the organisational code of ethics in line with organisational requirements.</t>
+          <t>Reviews ethical practices and feedback and applies the organisational code of ethics to guide decisions.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>professional ethics, codes of conduct, ethical work practices, organisational governance, ethical frameworks</t>
+          <t>professional ethics, codes of conduct, ethical frameworks, ethical work practices, organisational governance</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -10716,7 +10720,7 @@
         </is>
       </c>
       <c r="AH66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
@@ -10836,12 +10840,12 @@
         <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Feedback Management":1</t>
         </is>
       </c>
       <c r="Z67" t="b">
@@ -10917,7 +10921,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>penetration testing, vulnerability assessment, ISO 27001, CIA triad, security controls</t>
+          <t>penetration testing, vulnerability assessment, ISO 27001, CIA triad, industry standards</t>
         </is>
       </c>
       <c r="J68" t="n">
@@ -11022,7 +11026,7 @@
         </is>
       </c>
       <c r="AJ68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -11066,7 +11070,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>information synthesis, source integration, technical writing, citation management, cohesive language</t>
+          <t>literature review, source integration, technical writing, citation management, knowledge synthesis</t>
         </is>
       </c>
       <c r="J69" t="n">
@@ -11171,7 +11175,7 @@
         </is>
       </c>
       <c r="AJ69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -11215,7 +11219,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>intellectual property law, copyright legislation, industry standards, policy compliance, regulatory analysis</t>
+          <t>intellectual property law, copyright legislation, industry standard legislation, policy compliance, regulatory analysis</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -11364,7 +11368,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>document dissemination, policy distribution, ethics training, stakeholder engagement, internal governance</t>
+          <t>policy distribution, document dissemination, compliance communication, stakeholder engagement, ethics training</t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -11488,7 +11492,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Privacy Policy Documentation</t>
+          <t>Policy Documentation</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -11513,7 +11517,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>privacy legislation, privacy policy, code of ethics, regulatory documentation, policy management</t>
+          <t>privacy legislation, policy management, codes of ethics, privacy policy, regulatory documentation</t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -11578,19 +11582,15 @@
         </is>
       </c>
       <c r="V72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 5/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>keep:2, "Privacy Policy Documentation":5</t>
+          <t>keep:4, "Privacy Policy Documentation":3</t>
         </is>
       </c>
       <c r="Z72" t="b">
@@ -11734,7 +11734,7 @@
         <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>scheduling, resource allocation, stakeholder communication, project monitoring, sequences and schedules</t>
+          <t>scheduling, stakeholder communication, project monitoring, Gantt charts, sequences and schedules</t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -11883,12 +11883,12 @@
         <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Project Sequencing":1</t>
         </is>
       </c>
       <c r="Z74" t="b">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Identifies and analyses legislative changes to ensure ongoing compliance with rights and responsibilities.</t>
+          <t>Monitors and analyses legislative changes to ensure ongoing compliance with rights and responsibilities.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -12065,7 +12065,7 @@
         </is>
       </c>
       <c r="AH75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI75" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Uses digital technologies and systems safely, legally and ethically when gathering, storing, accessing and sharing information.</t>
+          <t>Manages digital information securely by lawfully collecting, storing, accessing and sharing data using compliant systems.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -12185,12 +12185,12 @@
         <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>0.95</v>
+        <v>0.9516666666666667</v>
       </c>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Digital Information Security":1</t>
         </is>
       </c>
       <c r="Z76" t="b">
@@ -12214,7 +12214,7 @@
         </is>
       </c>
       <c r="AH76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>policy dissemination, stakeholder engagement, communication protocols, change management, organisational compliance</t>
+          <t>policy dissemination, stakeholder engagement, communication protocols, change management, policy distribution</t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -12334,16 +12334,16 @@
         <v>1</v>
       </c>
       <c r="W77" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>keep:2, "Policy Distribution":5</t>
+          <t>keep:0, "Policy Distribution":7</t>
         </is>
       </c>
       <c r="Z77" t="b">
@@ -12379,7 +12379,7 @@
         </is>
       </c>
       <c r="AJ77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -12423,7 +12423,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>active listening, questioning techniques, stakeholder engagement, dialogue facilitation, interpersonal communication</t>
+          <t>active listening, questioning techniques, verbal exchange, stakeholder engagement, interpersonal communication</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -12528,7 +12528,7 @@
         </is>
       </c>
       <c r="AJ78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -12572,7 +12572,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>distributed ledger, node deployment, consensus configuration, blockchain platform, design plan</t>
+          <t>distributed ledger, node deployment, consensus configuration, Ethereum, platform for blockchain</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -12647,12 +12647,12 @@
         <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Blockchain Platform Installation":1</t>
         </is>
       </c>
       <c r="Z79" t="b">
@@ -12803,16 +12803,16 @@
         <v>1</v>
       </c>
       <c r="W80" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>keep:0, "Blockchain Anomaly Resolution":7</t>
+          <t>keep:0, "Blockchain Anomaly Resolution":5, "Blockchain Anomaly Problem Solving":2</t>
         </is>
       </c>
       <c r="Z80" t="b">
@@ -12820,13 +12820,9 @@
       </c>
       <c r="AA80" t="inlineStr"/>
       <c r="AB80" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Foundation Skill describes problem‑solving capability that is already embedded in other skills and PCs; it does not represent a distinct task for this unit</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC80" t="inlineStr"/>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -12887,12 +12883,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Establishes blockchain objectives, purpose and requirements aligned with organisational needs in hybrid environments.</t>
+          <t>Establishes blockchain objectives, purpose and requirements aligned with organisational needs, including consideration of hybrid environments.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>distributed ledger, blockchain objectives, stakeholder analysis, business needs, governance frameworks</t>
+          <t>distributed ledger, blockchain objectives, stakeholder analysis, smart contract design, governance frameworks</t>
         </is>
       </c>
       <c r="J81" t="n">
@@ -13204,7 +13200,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>design plan, organisational requirements, technical specifications, engineering documentation, design standards</t>
+          <t>design plan, organisational requirements, engineering documentation, technical specifications, design standards</t>
         </is>
       </c>
       <c r="J83" t="n">
@@ -13360,7 +13356,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>record‑keeping, feedback loops, documentation submission, workflow approvals, compliance</t>
+          <t>documentation submission, feedback response, record‑keeping, workflow approvals, electronic filing</t>
         </is>
       </c>
       <c r="J84" t="n">
@@ -13516,7 +13512,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>systems integration, workflow orchestration, process automation, ETL, API middleware</t>
+          <t>systems integration, workflow orchestration, process automation, integration workflow, design integration</t>
         </is>
       </c>
       <c r="J85" t="n">
@@ -13628,7 +13624,7 @@
         </is>
       </c>
       <c r="AJ85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -13672,7 +13668,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>preventive maintenance, asset management, CMMS, work order scheduling, maintenance schedule</t>
+          <t>preventive maintenance, asset management, CMMS, work order scheduling, reliability engineering</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -13784,7 +13780,7 @@
         </is>
       </c>
       <c r="AJ86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -13803,7 +13799,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Maintenance Testing</t>
+          <t>Maintenance Testing Execution</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -13823,12 +13819,12 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Determines and conducts maintenance tests to verify equipment functionality and compliance.</t>
+          <t>Plans, selects and conducts maintenance tests to verify equipment functionality and compliance.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>preventive maintenance, maintenance testing, equipment inspection, reliability testing, compliance standards</t>
+          <t>preventive maintenance, maintenance tests, test procedures, equipment inspection, reliability testing</t>
         </is>
       </c>
       <c r="J87" t="n">
@@ -13900,19 +13896,15 @@
         </is>
       </c>
       <c r="V87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W87" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 4/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>keep:3, "Maintenance Testing":4</t>
+          <t>keep:4, "Maintenance Testing":3</t>
         </is>
       </c>
       <c r="Z87" t="b">
@@ -13936,7 +13928,7 @@
         </is>
       </c>
       <c r="AH87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
@@ -13983,12 +13975,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Determines the security measures and platform for blockchain solutions, informed by risk assessments.</t>
+          <t>Selects and configures security platforms for blockchain solutions based on risk assessments.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>blockchain, security architecture, platform evaluation, cryptography, risk assessment</t>
+          <t>blockchain, security architecture, platform evaluation, security and platform, risk assessment</t>
         </is>
       </c>
       <c r="J88" t="n">
@@ -14092,15 +14084,15 @@
         </is>
       </c>
       <c r="AH88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>blockchain, security architecture, platform evaluation, cryptography, risk assessment</t>
+        </is>
+      </c>
+      <c r="AJ88" t="b">
         <v>1</v>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>blockchain, security architecture, platform evaluation, cryptography, risk assessment</t>
-        </is>
-      </c>
-      <c r="AJ88" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -14139,12 +14131,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Executes the required smart command on the designated blockchain platform in accordance with the solution specifications.</t>
+          <t>Executes smart commands on the required blockchain platform in accordance with the blockchain solution specifications.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>blockchain, Ethereum, Solidity, smart command execution, decentralised applications</t>
+          <t>blockchain, Ethereum, Solidity, decentralised applications, smart command</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -14300,7 +14292,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>blockchain, smart contracts, Solidity, performance scaling, solution debugging</t>
+          <t>blockchain, smart contracts, Solidity, distributed ledger, debug</t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -14451,7 +14443,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Tests solution performance against organisational needs and requirements to confirm suitability.</t>
+          <t>Tests solution performance against organisational needs and requirements.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -14607,7 +14599,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Obtains information to confirm requirements and responsibilities using appropriate industry terminology.</t>
+          <t>Engages stakeholders to clarify requirements and accountabilities using appropriate industry terminology.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -14716,7 +14708,7 @@
         </is>
       </c>
       <c r="AH92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI92" t="inlineStr">
         <is>
@@ -14763,7 +14755,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Identifies organisational use cases aligned with business needs by analysing hybrid environments.</t>
+          <t>Identifies organisational use cases aligned with business needs.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -14924,7 +14916,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>data ingestion, log analytics, analytic platform, ETL pipelines, user instructions</t>
+          <t>data ingestion, log analytics, ETL pipelines, analytic platform, data logs</t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -15091,7 +15083,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>legislative requirements, organisational policies, threat data analysis, data log requirements, regulatory compliance</t>
+          <t>legislative requirements, organisational policies, threat data, data analysis, regulatory compliance</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -15254,7 +15246,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>data validation, anomaly detection, data quality, data auditing, profiling</t>
+          <t>data validation, anomaly detection, data quality, data auditing, data discrepancy</t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -15369,7 +15361,7 @@
         </is>
       </c>
       <c r="AJ96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -15413,7 +15405,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>log analysis, data ingestion, dataset creation, alerts and logs, data governance</t>
+          <t>log analysis, data ingestion, dataset creation, alerts, reported events</t>
         </is>
       </c>
       <c r="J97" t="n">
@@ -15495,12 +15487,12 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>keep:2, "Dataset Creation":5</t>
+          <t>keep:1, "Dataset Creation":6</t>
         </is>
       </c>
       <c r="Z97" t="b">
@@ -15580,7 +15572,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>false positives, false negatives, type I error, anomaly detection, statistical significance</t>
+          <t>false positives, false negatives, type I error, anomaly detection, precision‑recall analysis</t>
         </is>
       </c>
       <c r="J98" t="n">
@@ -15747,7 +15739,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>incident reporting, report writing, procedural compliance, root‑cause analysis, findings documentation</t>
+          <t>incident reporting, root‑cause analysis, procedural compliance, report writing, safety management</t>
         </is>
       </c>
       <c r="J99" t="n">
@@ -15858,7 +15850,7 @@
         </is>
       </c>
       <c r="AJ99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -15902,7 +15894,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>lessons learned, action steps, mitigation strategies, recommendations, stakeholder engagement</t>
+          <t>lessons learned, action steps, recommendations, mitigation strategies, stakeholder engagement</t>
         </is>
       </c>
       <c r="J100" t="n">
@@ -16065,7 +16057,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>risk assessment, threat modelling, likelihood of occurrence, impacts of risks, cyber threats</t>
+          <t>risk assessment, threat modelling, likelihood of occurrence, impact evaluation, cyber threats</t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -16228,7 +16220,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>security equipment, network security, asset inventories, data sources, cyber security</t>
+          <t>security equipment, network security, asset inventories, data sources, IDS</t>
         </is>
       </c>
       <c r="J102" t="n">
@@ -16387,7 +16379,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>log aggregation, data ingestion, security analytics, SIEM, analytic platform</t>
+          <t>log aggregation, SIEM, data ingestion, security analytics, analytic platform</t>
         </is>
       </c>
       <c r="J103" t="n">
@@ -16474,9 +16466,13 @@
         </is>
       </c>
       <c r="Z103" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA103" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>Data Log Ingestion</t>
+        </is>
+      </c>
       <c r="AB103" t="b">
         <v>0</v>
       </c>
@@ -16546,7 +16542,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>threat data review, stakeholder engagement, risk reporting, data briefings, cyber security communication</t>
+          <t>stakeholder engagement, threat intelligence, data briefings, cyber security communication, threat data</t>
         </is>
       </c>
       <c r="J104" t="n">
@@ -16624,12 +16620,12 @@
         <v>0</v>
       </c>
       <c r="W104" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X104" t="inlineStr"/>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Threat Findings Communication":1</t>
         </is>
       </c>
       <c r="Z104" t="b">
@@ -16705,7 +16701,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>threat intelligence, log analysis, data ingestion, dataset creation, security monitoring</t>
+          <t>threat intelligence, log analysis, SIEM, data collection, security monitoring</t>
         </is>
       </c>
       <c r="J105" t="n">
@@ -16868,7 +16864,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>outlier analysis, root‑cause analysis, statistical process control, monitoring and diagnostics, anomaly detection</t>
+          <t>outlier analysis, root‑cause analysis, statistical process control, anomaly detection, context recognition</t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -16940,12 +16936,12 @@
         <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Anomaly Detection":1</t>
         </is>
       </c>
       <c r="Z106" t="b">
@@ -17016,12 +17012,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Implements additional protection plan requirements and asset management processes to safeguard assets.</t>
+          <t>Implements enhanced protection plan requirements and asset management processes to safeguard assets.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>asset management processes, protection plan requirements, additional protection methods, asset tracking, risk mitigation</t>
+          <t>asset management processes, additional protection plan, protection plan requirements, asset tracking, risk mitigation</t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -17093,7 +17089,7 @@
         <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X107" t="inlineStr"/>
       <c r="Y107" t="inlineStr">
@@ -17122,7 +17118,7 @@
         </is>
       </c>
       <c r="AH107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI107" t="inlineStr">
         <is>
@@ -17174,7 +17170,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>critical infrastructure protection, infrastructure protection, research findings, protection plan requirements, policy compliance</t>
+          <t>critical infrastructure protection, infrastructure protection, research findings, document findings, risk assessment</t>
         </is>
       </c>
       <c r="J108" t="n">
@@ -17475,12 +17471,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Secures devices in accordance with the protection plan and technical requirements.</t>
+          <t>Implements device security controls in accordance with protection plans and technical specifications.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>endpoint protection, device hardening, security policies, encryption, protection plan requirements</t>
+          <t>endpoint protection, device hardening, protection plan, technical requirements, encryption</t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -17581,7 +17577,7 @@
         </is>
       </c>
       <c r="AH110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI110" t="inlineStr">
         <is>
@@ -17628,12 +17624,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Submits protection plans to required personnel, seeks feedback, and incorporates stakeholder responses to improve outcomes.</t>
+          <t>Submits protection plans for review and incorporates stakeholder feedback to improve outcomes.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>protection plan, stakeholder communication, feedback loops, response management, compliance reporting</t>
+          <t>protection plan, feedback response, stakeholder communication, plan documentation, compliance reporting</t>
         </is>
       </c>
       <c r="J111" t="n">
@@ -17734,7 +17730,7 @@
         </is>
       </c>
       <c r="AH111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI111" t="inlineStr">
         <is>
@@ -17781,7 +17777,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Implements network segmentation to isolate security zones in line with approved protection plans.</t>
+          <t>Implements network segmentation to isolate security zones in line with approved protection plans and technical requirements.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -17887,7 +17883,7 @@
         </is>
       </c>
       <c r="AH112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI112" t="inlineStr">
         <is>
@@ -18011,7 +18007,7 @@
         <v>0</v>
       </c>
       <c r="W113" t="n">
-        <v>0.95</v>
+        <v>0.9524999999999999</v>
       </c>
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr">
@@ -18028,7 +18024,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>FS describes work style (planning and coordination) already embedded in PCs and other skills</t>
+          <t>FS describes work style (planning coordination) not a distinct task; capability already embedded in strategy development and implementation PCs</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -18091,12 +18087,12 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Analyzes the organisation’s existing critical infrastructure protection plan.</t>
+          <t>Analyses the organisation’s existing critical infrastructure protection plan to identify gaps and recommend improvements.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>critical infrastructure protection, protection plan, infrastructure protection plan, critical assets, vulnerability analysis</t>
+          <t>critical infrastructure protection, infrastructure protection plan, protection plan requirements, risk assessment, vulnerability analysis</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -18321,7 +18317,7 @@
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>0.95</v>
+        <v>0.9428571428571428</v>
       </c>
       <c r="X115" t="inlineStr"/>
       <c r="Y115" t="inlineStr">
@@ -18402,7 +18398,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>protection plan, deployment testing, security policies, compliance testing, vulnerability testing</t>
+          <t>protection plan, test deployment, security policies, compliance testing, vulnerability testing</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -18554,7 +18550,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Collects and analyses test results in accordance with organisational policies and procedures.</t>
+          <t>Obtains and analyses results according to organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -18707,12 +18703,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Determines the level of protection, vulnerability, risk and mitigation in line with organisational requirements.</t>
+          <t>Determines the level of protection, vulnerability, risk and mitigation in accordance with organisational requirements.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>vulnerability analysis, risk mitigation, protection plan, security governance, ISO 27001 compliance</t>
+          <t>vulnerability analysis, mitigation planning, risk matrices, protection plan requirements, security governance</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -18789,7 +18785,7 @@
       <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>keep:5, "Risk Evaluation":1, "Risk Assessment":1</t>
+          <t>keep:4, "Risk Assessment":2, "Risk Evaluation":1</t>
         </is>
       </c>
       <c r="Z118" t="b">
@@ -18865,7 +18861,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>patch management, vulnerability remediation, software patches, technical requirements, configuration management</t>
+          <t>patch management, vulnerability remediation, update deployment, configuration management, software patches</t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -19171,7 +19167,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>security architecture, data types, classification schemes, confidentiality levels, information security</t>
+          <t>information security, data inventories, data types, classification schemes, security architecture</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -19258,7 +19254,7 @@
       <c r="X121" t="inlineStr"/>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>keep:4, "Data Type Identification":3</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z121" t="b">
@@ -19493,7 +19489,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>security architecture, design methodologies, industry standards, security frameworks, security design</t>
+          <t>security architecture design, industry standard design, design methodologies, security frameworks, risk assessment</t>
         </is>
       </c>
       <c r="J123" t="n">
@@ -19739,7 +19735,7 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>keep:0, "Contextual Anomaly Identification":6, "Contextual Anomaly Detection":1</t>
+          <t>keep:0, "Contextual Anomaly Identification/Security Anomaly Identification":6, "Contextual Anomaly Detection":1</t>
         </is>
       </c>
       <c r="Z124" t="b">
@@ -19815,7 +19811,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>security architecture findings, security design documentation, cyber security requirements, compliance frameworks, ISO 27001</t>
+          <t>security architecture, security architecture findings, documentation detailing findings, cyber security requirements, compliance frameworks</t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -19978,7 +19974,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>security architecture, technical presentations, information security, enterprise architecture, risk assessment</t>
+          <t>security architecture, security design, technical presentations, enterprise architecture, risk assessment</t>
         </is>
       </c>
       <c r="J126" t="n">
@@ -20137,7 +20133,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>security architecture, threat modelling, NIST framework, ISO 27001, industry standard design methodologies</t>
+          <t>security architecture, threat modelling, NIST framework, ISO 27001, design methodologies</t>
         </is>
       </c>
       <c r="J127" t="n">
@@ -20459,7 +20455,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>phased implementation, performance monitoring, project scheduling, operational detail, priority review</t>
+          <t>phased implementation, performance monitoring, project scheduling tools, operational detail, priority review</t>
         </is>
       </c>
       <c r="J129" t="n">
@@ -20558,7 +20554,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>FS describes work style (planning and reviewing) not a distinct task; capability already embedded in PCs and other skills</t>
+          <t>FS describes work style (planning and reviewing) not a distinct task; capability is implicit in other skills and PCs</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -20626,7 +20622,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>cyber security requirements, security architecture, risk assessment, compliance standards, vulnerability analysis</t>
+          <t>security requirements, security architecture, risk assessment, threat modelling, compliance standards</t>
         </is>
       </c>
       <c r="J130" t="n">
@@ -20944,7 +20940,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>technical writing, documentation standards, findings and solutions, complex workplace documentation, knowledge management</t>
+          <t>technical writing, documentation standards, complex workplace documentation, findings and solutions, knowledge management</t>
         </is>
       </c>
       <c r="J132" t="n">
@@ -21102,7 +21098,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Interprets technical, manufacturer and organisational documentation to determine and confirm job requirements before commencing work.</t>
+          <t>Reviews technical, manufacturer and organisational documentation to confirm job requirements prior to work commencement.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -21222,7 +21218,7 @@
         </is>
       </c>
       <c r="AH133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI133" t="inlineStr">
         <is>
@@ -21626,7 +21622,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>security incident response, incident reporting, incident response plan, incident response team, compliance documentation</t>
+          <t>security incident response, incident reporting, incident response plan, incident documentation, compliance documentation</t>
         </is>
       </c>
       <c r="J136" t="n">
@@ -21885,16 +21881,16 @@
         <v>1</v>
       </c>
       <c r="W137" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>keep:0, "Incident Response Plan Evaluation":7</t>
+          <t>keep:3, "Incident Response Plan Evaluation":4</t>
         </is>
       </c>
       <c r="Z137" t="b">
@@ -21970,7 +21966,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>incident response plan, incident handling, NIST framework, playbook development, risk management</t>
+          <t>incident response plan, incident handling, playbook development, risk management, NIST framework</t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -22137,7 +22133,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Identifies and documents incident response team roles and services to support coordinated response.</t>
+          <t>Documents incident response team roles and services to support coordinated response.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -22229,7 +22225,7 @@
         <v>0</v>
       </c>
       <c r="W139" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr">
@@ -22258,7 +22254,7 @@
         </is>
       </c>
       <c r="AH139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI139" t="inlineStr">
         <is>
@@ -22305,12 +22301,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Designs incident response exercises, red‑team activities, and staffing and training plans.</t>
+          <t>Designs and conducts red‑team exercises and incident response simulations, including staffing and training plans.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>incident response exercises, red‑teaming activities, incident response planning, staffing and training, MITRE ATT&amp;CK framework</t>
+          <t>adversary simulation, incident response planning, threat modelling, security training programmes, MITRE ATT&amp;CK framework</t>
         </is>
       </c>
       <c r="J140" t="n">
@@ -22401,16 +22397,16 @@
         <v>1</v>
       </c>
       <c r="W140" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>keep:0, "Incident Response Exercise Design":7</t>
+          <t>keep:0, "Incident Response Exercise Design":5, "Incident Response Training":2</t>
         </is>
       </c>
       <c r="Z140" t="b">
@@ -22434,7 +22430,7 @@
         </is>
       </c>
       <c r="AH140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI140" t="inlineStr">
         <is>
@@ -22442,7 +22438,7 @@
         </is>
       </c>
       <c r="AJ140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -22653,12 +22649,12 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Interprets, analyses and documents numerical and technical system data to support risk assessment.</t>
+          <t>Interprets and documents numerical and technical system data to support risk assessment.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>technical system data, quantitative analysis, data documentation, risk assessment, system modelling</t>
+          <t>quantitative analysis, technical data interpretation, system modelling, data documentation, numerical data analysis</t>
         </is>
       </c>
       <c r="J142" t="n">
@@ -22753,22 +22749,18 @@
         <v>0</v>
       </c>
       <c r="W142" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>keep:6, "Technical Data Interpretation":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z142" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA142" t="inlineStr">
-        <is>
-          <t>Technical Data Interpretation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA142" t="inlineStr"/>
       <c r="AB142" t="b">
         <v>0</v>
       </c>
@@ -22786,7 +22778,7 @@
         </is>
       </c>
       <c r="AH142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI142" t="inlineStr">
         <is>
@@ -23190,7 +23182,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>quantitative analysis, technical system data, data documentation, engineering diagnostics, numeracy interpretation</t>
+          <t>quantitative analysis, technical system data, data documentation, engineering diagnostics, numeracy</t>
         </is>
       </c>
       <c r="J145" t="n">
@@ -23370,7 +23362,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>business continuity, impact analysis, business critical functions, risk assessment, resilience planning</t>
+          <t>business continuity, impact analysis, disaster recovery, resilience planning, system impact</t>
         </is>
       </c>
       <c r="J146" t="n">
@@ -23530,7 +23522,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Designs and implements compliance strategies to meet organisational, commercial and regulatory requirements.</t>
+          <t>Designs and implements compliance strategies to align organisational processes with regulatory requirements.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -23636,7 +23628,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>FS describes work style and compliance activity already implicit in other skills; not a distinct task for this unit</t>
+          <t>FS describes work style/strategic compliance activity already implicit in other skills and not a distinct task for this unit</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -23652,7 +23644,7 @@
         </is>
       </c>
       <c r="AH147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI147" t="inlineStr">
         <is>
@@ -23699,12 +23691,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Develops contingency plans by identifying threats.</t>
+          <t>Develops a contingency plan by identifying threats.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>contingency planning, threat identification, business continuity, mitigation strategies, disaster recovery plan</t>
+          <t>contingency planning, contingency plan, threat identification, business continuity, risk assessment</t>
         </is>
       </c>
       <c r="J148" t="n">
@@ -23868,12 +23860,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Evaluates and documents prevention and recovery options against business specifications and cost constraints.</t>
+          <t>Evaluates prevention and recovery options for compliance and cost effectiveness.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>cost constraints, business specifications, recovery options, disaster recovery plan, risk minimisation</t>
+          <t>cost‑benefit analysis, business specifications, cost constraints, disaster recovery, prevention and recovery options</t>
         </is>
       </c>
       <c r="J149" t="n">
@@ -23986,7 +23978,7 @@
         </is>
       </c>
       <c r="AH149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI149" t="inlineStr">
         <is>
@@ -24038,7 +24030,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>disaster recovery plan, business continuity, recovery time objectives, risk assessment, disaster recovery testing</t>
+          <t>disaster recovery plan, business continuity, backup and restore, recovery time objectives, risk assessment</t>
         </is>
       </c>
       <c r="J150" t="n">
@@ -24372,7 +24364,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>quantitative analysis, financial modelling, technical data interpretation, statistical methods, data reporting</t>
+          <t>quantitative analysis, financial modelling, technical data interpretation, statistical methods, data documentation</t>
         </is>
       </c>
       <c r="J152" t="n">
@@ -24497,7 +24489,7 @@
         </is>
       </c>
       <c r="AJ152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -24536,12 +24528,12 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Designs and implements prevention and recovery strategies to strengthen system resilience.</t>
+          <t>Formulates prevention and recovery strategies to strengthen system resilience.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>prevention strategy, recovery strategy, disaster recovery plan, contingency strategies, risk assessment</t>
+          <t>prevention strategy, recovery strategy, disaster recovery plan, mitigation planning, scenario analysis</t>
         </is>
       </c>
       <c r="J153" t="n">
@@ -24658,7 +24650,7 @@
         </is>
       </c>
       <c r="AH153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI153" t="inlineStr">
         <is>
@@ -24878,7 +24870,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Conducts comprehensive risk assessments and develops disaster recovery and contingency solutions.</t>
+          <t>Conducts comprehensive risk assessments and carries out disaster recovery and contingency planning.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -25000,7 +24992,7 @@
         </is>
       </c>
       <c r="AH155" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI155" t="inlineStr">
         <is>
@@ -25052,7 +25044,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>stakeholder engagement, feedback loops, document management, communication protocols, document disaster recovery</t>
+          <t>stakeholder engagement, feedback loops, document management, communication protocols, collaboration tools</t>
         </is>
       </c>
       <c r="J156" t="n">
@@ -25173,7 +25165,7 @@
         </is>
       </c>
       <c r="AJ156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -25217,7 +25209,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>priority alignment, outcome mapping, roadmap development, performance metrics, scenario analysis</t>
+          <t>priority alignment, outcome mapping, roadmap development, performance metrics, contingency planning</t>
         </is>
       </c>
       <c r="J157" t="n">
@@ -25306,7 +25298,7 @@
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>keep:4, "Strategy Prioritisation":3</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z157" t="b">
@@ -25318,7 +25310,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Foundation Skill describes a work style (strategic planning) that is already implicit in other skills and PCs</t>
+          <t>Foundation Skill describes a work style (strategic planning) that is already embedded in other skills and PCs</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -25342,7 +25334,7 @@
         </is>
       </c>
       <c r="AJ157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -25386,7 +25378,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>communication tools, relationship building, stakeholder engagement, collaboration platforms, interpersonal communication</t>
+          <t>communication tools, relationship building, stakeholder engagement, collaboration platforms, effective working relationships</t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -25507,7 +25499,7 @@
         </is>
       </c>
       <c r="AJ158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -25551,7 +25543,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>evaluation reporting, strategic articulation, document control, disaster strategy documentation, process documentation</t>
+          <t>specification drafting, process documentation, evaluation reporting, strategic articulation, document control</t>
         </is>
       </c>
       <c r="J159" t="n">
@@ -25672,7 +25664,7 @@
         </is>
       </c>
       <c r="AJ159" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -25878,12 +25870,12 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting decisions with relevant data and reasoning.</t>
+          <t>Provides clear, evidence‑based answers to queries, supporting each response with relevant data or rationale.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>evidence based answers, stakeholder queries, substantiated responses, data support, reasoning justification</t>
+          <t>evidence based answers, substantiated responses, query handling, data support, rationale provision</t>
         </is>
       </c>
       <c r="J161" t="n">
@@ -25974,7 +25966,7 @@
       </c>
       <c r="AG161" t="inlineStr">
         <is>
-          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting decisions with relevant data and reasoning.</t>
+          <t>Provides clear, evidence‑based answers to queries, supporting each response with relevant data or rationale.</t>
         </is>
       </c>
       <c r="AH161" t="b">
@@ -25982,7 +25974,7 @@
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>evidence based answers, stakeholder queries, substantiated responses, data support, reasoning justification</t>
+          <t>evidence based answers, substantiated responses, query handling, data support, rationale provision</t>
         </is>
       </c>
       <c r="AJ161" t="b">
@@ -26028,7 +26020,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, data mapping, asset documentation, storage verification</t>
+          <t>device data inventory, information classification, data mapping, asset documentation, registered devices</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -26127,11 +26119,11 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, data mapping, asset documentation, storage verification</t>
+          <t>device data inventory, information classification, data mapping, asset documentation, digital records</t>
         </is>
       </c>
       <c r="AJ162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -26148,7 +26140,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Sign‑off Coordination</t>
+          <t>Sign‑off Acquisition</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -26168,16 +26160,16 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
+          <t>Secures final approval from designated stakeholders by coordinating, presenting, and confirming sign‑off requirements.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>approval process, stakeholder engagement, compliance confirmation, sign‑off management, finalisation</t>
+          <t>approval coordination, stakeholder engagement, sign‑off confirmation, final authorization, approval documentation</t>
         </is>
       </c>
       <c r="J163" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -26234,14 +26226,14 @@
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>Sign‑off Coordination</t>
+          <t>Sign‑off Acquisition</t>
         </is>
       </c>
       <c r="V163" t="b">
         <v>0</v>
       </c>
       <c r="W163" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="X163" t="inlineStr">
         <is>
@@ -26266,7 +26258,7 @@
       </c>
       <c r="AG163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
+          <t>Secures final approval from designated stakeholders by coordinating, presenting, and confirming sign‑off requirements.</t>
         </is>
       </c>
       <c r="AH163" t="b">
@@ -26274,7 +26266,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>approval process, stakeholder engagement, compliance confirmation, sign‑off management, finalisation</t>
+          <t>approval coordination, stakeholder engagement, sign‑off confirmation, final authorization, approval documentation</t>
         </is>
       </c>
       <c r="AJ163" t="b">
@@ -26315,16 +26307,16 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Identifies organisational processes and transaction types suitable for blockchain, and determines relevant legislation, organisational policies and procedures and their impact on the blockchain solution.</t>
+          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation, considering relevant legislation and policies.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>blockchain suitability, transactional types, organisational processes, compliance impact, solution impact</t>
+          <t>process analysis, transaction evaluation, blockchain suitability, regulatory compliance, blockchain technology</t>
         </is>
       </c>
       <c r="J164" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -26396,7 +26388,7 @@
         <v>0</v>
       </c>
       <c r="W164" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="X164" t="inlineStr">
         <is>
@@ -26421,15 +26413,15 @@
       </c>
       <c r="AG164" t="inlineStr">
         <is>
-          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation.</t>
+          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation, considering relevant legislation and policies.</t>
         </is>
       </c>
       <c r="AH164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>process evaluation, transaction analysis, blockchain suitability, organisational assessment, compliance impact</t>
+          <t>process analysis, transaction evaluation, blockchain suitability, regulatory compliance, organisational policy</t>
         </is>
       </c>
       <c r="AJ164" t="b">
@@ -26450,7 +26442,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Log Requirement Consultation</t>
+          <t>Data Log Strategy Discussion</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -26470,16 +26462,16 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Facilitates discussion with relevant personnel to confirm data log requirements and processing strategy.</t>
+          <t>Facilitates discussions with relevant personnel to confirm data log requirements and processing strategies.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, collaborative discussion</t>
+          <t>data log requirements, processing strategy, personnel coordination, discussion facilitation, requirement confirmation</t>
         </is>
       </c>
       <c r="J165" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -26534,14 +26526,14 @@
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>Log Requirement Consultation</t>
+          <t>Data Log Strategy Discussion</t>
         </is>
       </c>
       <c r="V165" t="b">
         <v>0</v>
       </c>
       <c r="W165" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="X165" t="inlineStr">
         <is>
@@ -26566,7 +26558,7 @@
       </c>
       <c r="AG165" t="inlineStr">
         <is>
-          <t>Facilitates discussion with relevant personnel to confirm data log requirements and processing strategy.</t>
+          <t>Facilitates discussions with relevant personnel to confirm data log requirements and processing strategies.</t>
         </is>
       </c>
       <c r="AH165" t="b">
@@ -26574,7 +26566,7 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, collaborative discussion</t>
+          <t>data log requirements, processing strategy, personnel coordination, discussion facilitation, requirement confirmation</t>
         </is>
       </c>
       <c r="AJ165" t="b">
@@ -26615,12 +26607,12 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Evaluates gathered threat data results to ensure reliability and consistency before further processing.</t>
+          <t>Evaluates gathered threat data results to confirm reliability and consistency before further processing.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>reliability assessment, consistency verification, data validation, result evaluation, false negative analysis</t>
+          <t>reliability assessment, consistency verification, data validation, result evaluation, results analysis</t>
         </is>
       </c>
       <c r="J166" t="n">
@@ -26711,7 +26703,7 @@
       </c>
       <c r="AG166" t="inlineStr">
         <is>
-          <t>Evaluates gathered threat data results to ensure reliability and consistency before further processing.</t>
+          <t>Evaluates gathered threat data results to confirm reliability and consistency before further processing.</t>
         </is>
       </c>
       <c r="AH166" t="b">
@@ -26760,12 +26752,12 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Evaluates the effectiveness and alignment of the existing protection plan with organisational requirements, and identifies operational systems, critical assets, network segmentation and legislative requirements.</t>
+          <t>Determines the effectiveness and alignment of the existing protection plan with organisational requirements, and identifies operational systems, critical assets, network segmentation and legislative requirements.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>plan effectiveness, organisational requirements, critical assets, legislative compliance, operational systems</t>
+          <t>plan effectiveness, organisational alignment, regulatory compliance, critical assets, operational systems</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -26863,7 +26855,7 @@
       </c>
       <c r="AG167" t="inlineStr">
         <is>
-          <t>Evaluates how well the current protection plan meets organisational needs and regulatory standards.</t>
+          <t>Evaluates how well the current protection plan meets organisational needs and regulatory requirements.</t>
         </is>
       </c>
       <c r="AH167" t="b">
@@ -26871,11 +26863,11 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>plan effectiveness, organisational requirements, alignment assessment, critical assets, legislative compliance</t>
+          <t>plan effectiveness, organisational alignment, regulatory compliance, critical assets, operational systems</t>
         </is>
       </c>
       <c r="AJ167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -26912,12 +26904,12 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Determines and documents the alignment of the existing incident response plan against identified requirements, submits the documentation to required personnel, and seeks and responds to feedback.</t>
+          <t>The worker assesses the current incident response plan, documents its compliance with requirements, and submits it for feedback.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment, documentation, requirements, feedback</t>
+          <t>incident response plan, alignment assessment, documentation, compliance verification, feedback submission</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -27022,15 +27014,15 @@
       </c>
       <c r="AG168" t="inlineStr">
         <is>
-          <t>Aligns the current incident response plan with requirements and documents the comparison for stakeholders.</t>
+          <t>The worker assesses the current incident response plan, documents its compliance with requirements, and submits it for feedback.</t>
         </is>
       </c>
       <c r="AH168" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment, documentation, requirements, feedback</t>
+          <t>incident response plan, alignment assessment, documentation, compliance verification, feedback submission</t>
         </is>
       </c>
       <c r="AJ168" t="b">
@@ -27051,7 +27043,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Evidence Preservation Assistance</t>
+          <t>Evidence Preservation</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -27071,12 +27063,12 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing, and securely preserving evidence in line with established incident response requirements.</t>
+          <t>Assist in gathering, processing and securely preserving incident evidence in line with organisational requirements.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, forensic evidence, incident response</t>
+          <t>evidence collection, evidence processing, evidence preservation, incident response, legislative requirements</t>
         </is>
       </c>
       <c r="J169" t="n">
@@ -27148,7 +27140,7 @@
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>Evidence Preservation Assistance</t>
+          <t>Evidence Preservation</t>
         </is>
       </c>
       <c r="V169" t="b">
@@ -27180,7 +27172,7 @@
       </c>
       <c r="AG169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing, and securely preserving evidence in line with established incident response requirements.</t>
+          <t>Assist in gathering, processing and securely preserving incident evidence in line with organisational requirements.</t>
         </is>
       </c>
       <c r="AH169" t="b">
@@ -27188,7 +27180,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, incident response, assistance</t>
+          <t>evidence collection, evidence processing, evidence preservation, incident response, organisational requirements</t>
         </is>
       </c>
       <c r="AJ169" t="b">
@@ -27229,7 +27221,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Identify essential business critical functions, the required security environment, critical data and software, and assess the potential impact of business risk and threats on ICT systems.</t>
+          <t>Identify essential business functions, data, and software, and assess ICT risk impacts on them.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -27333,11 +27325,11 @@
       </c>
       <c r="AG170" t="inlineStr">
         <is>
-          <t>Identify essential business functions, critical data, and software, and assess ICT risk impacts on them.</t>
+          <t>Identify essential business functions, data, and software, and assess ICT risk impacts on them.</t>
         </is>
       </c>
       <c r="AH170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI170" t="inlineStr">
         <is>
@@ -27382,12 +27374,12 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Creates and records detailed disaster strategy processes, cut‑over criteria, and secures final task sign‑off.</t>
+          <t>The worker identifies, records, and finalises disaster strategy processes, cut‑over criteria, and obtains sign‑off.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>disaster strategy processes, cut‑over criteria plan, task sign‑off, disaster recovery plan, documentation</t>
+          <t>disaster strategy, process documentation, cut‑over criteria, task sign‑off, disaster recovery plan</t>
         </is>
       </c>
       <c r="J171" t="n">
@@ -27486,7 +27478,7 @@
       </c>
       <c r="AG171" t="inlineStr">
         <is>
-          <t>Creates and records detailed disaster strategy processes, cut‑over criteria, and secures final task sign‑off.</t>
+          <t>The worker identifies, records, and finalises disaster strategy processes, cut‑over criteria, and obtains sign‑off.</t>
         </is>
       </c>
       <c r="AH171" t="b">
@@ -27494,7 +27486,7 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>disaster strategy, process documentation, cut‑over criteria, task sign‑off, implementation</t>
+          <t>disaster strategy, process documentation, cut‑over criteria, task sign‑off, finalisation</t>
         </is>
       </c>
       <c r="AJ171" t="b">

--- a/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v7.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v7.xlsx
@@ -648,12 +648,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Elicits others’ views and integrates feedback to refine ideas during collaborative discussions.</t>
+          <t>Elicits others’ views and opinions to develop and refine ideas during collaborative discussions.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>stakeholder engagement, feedback, empathy, communication, ideas elicitation</t>
+          <t>communication, empathy, stakeholder engagement, elicitation, viewpoint</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="AH2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>benchmarking, best practice, best practice examples, similar products, industry standards</t>
+          <t>benchmarking, best practice, similar products, competitive analysis, industry standards</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -987,7 +987,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ideation, brainstorming, creative problem solving, mind mapping, group facilitation</t>
+          <t>ideation, creative problem solving, mind mapping, group facilitation, idea generation</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>systematic analytical processes, concept evaluation, feasibility analysis, design thinking, ideation processes</t>
+          <t>analytical methodology, systematic concept evaluation, ideation processes, feasibility analysis, concept gathering</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name uses 'Planning' but evidence describes gathering and evaluating concepts, not planning</t>
+          <t>MIS re-refinement: Skill name uses 'Planning' which is not present in evidence; evidence describes gathering and evaluating concepts, not planning</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Skill name uses 'Planning' but evidence describes gathering and evaluating concepts, not planning</t>
+          <t>Skill name uses 'Planning' which is not present in evidence; evidence describes gathering and evaluating concepts, not planning</t>
         </is>
       </c>
       <c r="AF5" t="b">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>creative thinking techniques, ideation, innovation, brainstorming, design thinking</t>
+          <t>creative thinking, ideation, innovation, brainstorming, design thinking</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>record‑keeping, compliance, audit trail, quality assurance, feedback documentation</t>
+          <t>record‑keeping, compliance, audit trail, feedback documentation, organisational standards</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Idea Viability Evaluation</t>
+          <t>Idea Viability Assessment</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>feasibility analysis, criteria weighting, business case evaluation, market viability, viability assessment</t>
+          <t>feasibility analysis, risk assessment, criteria weighting, idea viability, market viability</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -1721,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>keep:0, "Idea Viability Evaluation":4, "Solution Viability Assessment/Idea Viability Assessment":3</t>
+          <t>keep:0, "Idea Viability Assessment/Solution Viability Assessment":4, "Idea Viability Evaluation":3</t>
         </is>
       </c>
       <c r="Z8" t="b">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>stakeholder engagement, problem identification, needs assessment, consultation processes, issue selection</t>
+          <t>stakeholder engagement, problem identification, needs assessment, issue selection, decision‑making</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>stakeholder communication, business case development, grant and RFP responses, persuasive writing, proposal preparation</t>
+          <t>stakeholder communication, business case development, grant and RFP responses, persuasive writing, proposal</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>literature review, data collection, search strategies, online databases, evidence‑based analysis</t>
+          <t>literature review, data collection, search strategies, online databases, research information</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="AJ11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>solution presentation, stakeholder communication, visual presentation tools, format selection, solution pitching</t>
+          <t>stakeholder communication, visual presentation tools, solution pitching, format selection, solution presentation</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -2369,16 +2369,16 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>keep:3, "Solution Presentation":4</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z12" t="b">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>requirements analysis, design optimisation, prototype testing, validation feedback, solution finalisation</t>
+          <t>requirements analysis, design optimisation, prototype testing, solution refinement, validation feedback</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -2536,7 +2536,7 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>keep:5, "Solution Refinement":2</t>
+          <t>keep:6, "Solution Refinement":1</t>
         </is>
       </c>
       <c r="Z13" t="b">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>feasibility analysis, constraint identification, business issue evaluation, viability assessment, solution evaluation</t>
+          <t>feasibility analysis, constraint identification, solution viability, risk assessment, decision matrices</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>stakeholder engagement, feedback collection, surveys, interviews, stakeholder feedback</t>
+          <t>stakeholder engagement, feedback collection, surveys, interviews, stakeholder solicitation</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -2858,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Group Interaction Facilitation</t>
+          <t>Discussion Facilitation</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>group dynamics, meeting facilitation, conflict resolution, consensus building, active listening</t>
+          <t>group dynamics, meeting facilitation, conflict resolution, consensus building, discussion</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>keep:0, "Group Interaction Facilitation":4, "Discussion Facilitation":3</t>
+          <t>keep:0, "Discussion Facilitation":6, "Group Interaction Facilitation":1</t>
         </is>
       </c>
       <c r="Z16" t="b">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Creates and updates cyber security awareness program that reflects organisation-wide best practice.</t>
+          <t>Creates and updates cyber security awareness program reflecting organisation-wide best practice.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>cyber security awareness, security awareness program, organisation-wide best practice, phishing simulations, compliance governance</t>
+          <t>cyber security, security awareness training, phishing simulations, compliance governance, security awareness program</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>cyber security terminology, technical documentation, information security policies, industry standards (ISO 27001, NIST), risk assessment reporting</t>
+          <t>cyber security terminology, technical documentation, clear technical writing, industry standards (ISO 27001, NIST), risk assessment reporting</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="AJ18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>cyber security awareness, security awareness program, level of awareness, cyber security, risk awareness</t>
+          <t>cyber security awareness, risk awareness, security posture, threat intelligence, security metrics</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>cyber security, security improvement, review outcomes, policy compliance, stakeholder reporting</t>
+          <t>cyber security, policy compliance, risk communication, improvement requirements, stakeholder reporting</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>stakeholder communication, knowledge transfer, visual storytelling, presentation tools, review outcomes</t>
+          <t>stakeholder communication, knowledge transfer, visual storytelling, presentation tools, insight</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Notifiable Data Breach, Australian Privacy Act, data breach legislation, privacy law interpretation, data protection implications</t>
+          <t>Notifiable Data Breach, Australian Privacy Act, data protection compliance, privacy law interpretation, legislation</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>review outcomes, improvement recommendations, stakeholder communication, record‑keeping, document outcomes</t>
+          <t>reporting, review outcomes, improvement recommendations, outcome documentation, stakeholder communication</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>cyber security governance, policy development, risk management, compliance frameworks, stakeholder communication</t>
+          <t>cyber security governance, policy development, drafting, stakeholder communication, compliance frameworks</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -4330,7 +4330,7 @@
         </is>
       </c>
       <c r="AJ24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>cyber security practices, policy compliance, risk assessment, security governance, audit controls</t>
+          <t>cyber security, policy compliance, security governance, audit controls, cyber security practices</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>cyber security documentation, information security records, compliance logging, data governance, records and documentation</t>
+          <t>cyber security documentation, information security records, compliance logging, data governance, record maintenance</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>stakeholder engagement, consultation workshops, decision support, needs analysis, facilitation</t>
+          <t>stakeholder engagement, consultation workshops, decision support, stakeholder consultation, needs analysis</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -4769,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr">
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="AJ27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>interdisciplinary teamwork, cyber security coordination, cross‑functional communication, stakeholder engagement, cyber security awareness</t>
+          <t>interdisciplinary teamwork, cyber security coordination, cross‑functional communication, stakeholder engagement, team collaboration</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>technology platforms, cyber security awareness, security platforms, SIEM, threat monitoring</t>
+          <t>cyber security, security platforms, technology platforms, SIEM, threat monitoring</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Reviews latest cyber security threats and trends impacting organisations.</t>
+          <t>Analyses current cyber threat reports to assess organisational impacts and advise on security measures.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>cyber security threats, threat intelligence, trend monitoring, security analytics, trends impacting organisations</t>
+          <t>cyber security, threat intelligence, trend monitoring, security analytics, trends impacting organisations</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -5249,7 +5249,7 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="AH30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>risk assessment, incident tracking, business impact analysis, breach review, security metrics</t>
+          <t>risk assessment, incident tracking, business impact analysis, breach, security metrics</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Device Configuration</t>
+          <t>Device Configuration Setup</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>device provisioning, firmware updates, configuration management, hardware initialisation, system onboarding</t>
+          <t>device provisioning, firmware updates, configuration management, hardware initialisation, device setup</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -5999,19 +5999,15 @@
         </is>
       </c>
       <c r="V36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 4/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>keep:3, "Device Configuration":4</t>
+          <t>keep:5, "Device Configuration":2</t>
         </is>
       </c>
       <c r="Z36" t="b">
@@ -6043,7 +6039,7 @@
         </is>
       </c>
       <c r="AJ36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -6087,7 +6083,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>encryption, device security, endpoint encryption, mobile device management, mobile devices</t>
+          <t>encryption, device security, endpoint encryption, mobile device management, implementation</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -6242,7 +6238,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>IT asset tracking, hardware registers, network inventories, CMDB, digital devices</t>
+          <t>IT asset tracking, hardware registers, network inventories, device register, asset management software</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -6417,7 +6413,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>gap analysis, best practice strategies, effectiveness evaluation, performance metrics, process improvement</t>
+          <t>gap analysis, benchmarking, performance metrics, best‑practice assessment, effectiveness evaluation</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -6580,7 +6576,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>authentication, password complexity, entropy, cyber security, password managers</t>
+          <t>authentication, password complexity, password strength, cyber security, password managers</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -6654,12 +6650,12 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>keep:6, "Password Creation":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z40" t="b">
@@ -6691,7 +6687,7 @@
         </is>
       </c>
       <c r="AJ40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -6735,7 +6731,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>physical security plan, access control systems, facility protection, stakeholder communication, risk assessment</t>
+          <t>risk assessment, access control systems, security policy development, facility protection, physical security plan</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -6898,7 +6894,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>risk assessment, information sensitivity, device classification, risk matrices, level of risk</t>
+          <t>risk assessment, information sensitivity, device classification, risk categorisation, cyber security</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -6980,12 +6976,12 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>keep:1, "Data Risk Categorisation":6</t>
+          <t>keep:3, "Data Risk Categorisation":4</t>
         </is>
       </c>
       <c r="Z42" t="b">
@@ -7036,7 +7032,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Physical Security Plan Communication</t>
+          <t>Security Plan Communication</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -7061,7 +7057,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>physical security, risk assessment, security policy, stakeholder communication, access control</t>
+          <t>physical security, security policy, stakeholder communication, access control, security plan</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -7140,19 +7136,15 @@
         </is>
       </c>
       <c r="V43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 4/7: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>keep:1, "Physical Security Plan Communication":4, "Physical Security Planning":2</t>
+          <t>keep:3, "Physical Security Planning":2, "Physical Security Plan Communication":2</t>
         </is>
       </c>
       <c r="Z43" t="b">
@@ -7188,7 +7180,7 @@
         </is>
       </c>
       <c r="AJ43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -7232,7 +7224,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>risk assessment, security protocol, device hardening, cyber security governance, protocol compliance</t>
+          <t>risk assessment, encryption standards, device hardening, security protocol, cyber security governance</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -7395,7 +7387,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>security strategies, security frameworks, risk assessment, cyber security governance, ISO 27001</t>
+          <t>cyber security governance, risk assessment, security frameworks, threat modelling, security strategies</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -7558,7 +7550,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>digital security, cyber security, threat intelligence, vulnerability tracking, security intelligence feeds</t>
+          <t>cyber security, threat intelligence, vulnerability tracking, digital security, security monitoring</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -7640,12 +7632,12 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>keep:3, "Security Development Monitoring":4</t>
+          <t>keep:2, "Security Development Monitoring":5</t>
         </is>
       </c>
       <c r="Z46" t="b">
@@ -7859,7 +7851,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Two-factor Authentication Enablement</t>
+          <t>Multi-factor Authentication Enablement</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -7884,7 +7876,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>multi‑factor authentication, MFA, OTP, access control, cyber security</t>
+          <t>multi‑factor authentication, MFA, two-factor authentication, access control, cyber security</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -7966,16 +7958,16 @@
         <v>1</v>
       </c>
       <c r="W48" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>keep:4, "Multi-factor Authentication Enablement":3</t>
+          <t>keep:1, "Multi-factor Authentication Enablement":6</t>
         </is>
       </c>
       <c r="Z48" t="b">
@@ -8007,7 +7999,7 @@
         </is>
       </c>
       <c r="AJ48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -8051,7 +8043,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>project scheduling, prioritisation, policy compliance, change management, implementation planning</t>
+          <t>action plan, project scheduling, prioritisation, policy compliance, change management</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -8153,7 +8145,7 @@
         </is>
       </c>
       <c r="AJ49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -8192,12 +8184,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Prioritises proposed changes to refine opportunities and assist in scheduling implementation.</t>
+          <t>Ranks proposed changes to clarify improvement opportunities and inform implementation scheduling.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>change management, prioritisation, opportunity assessment, implementation scheduling, project planning</t>
+          <t>change management, prioritisation, opportunity assessment, implementation scheduling, proposed changes</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -8295,15 +8287,15 @@
         </is>
       </c>
       <c r="AH50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>change management, prioritisation, opportunity assessment, implementation scheduling, project planning</t>
+        </is>
+      </c>
+      <c r="AJ50" t="b">
         <v>1</v>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>change management, prioritisation, opportunity assessment, implementation scheduling, project planning</t>
-        </is>
-      </c>
-      <c r="AJ50" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -8347,7 +8339,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data management, digital collaboration tools, emerging technologies, cloud computing, data visualisation</t>
+          <t>data management, digital collaboration tools, emerging technologies, cloud computing, digital technology utilisation</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -8453,7 +8445,7 @@
         </is>
       </c>
       <c r="AJ51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -8492,12 +8484,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Prepares evaluation documents, organises findings and submits them to a supervisor for review.</t>
+          <t>Documents the evaluation process and provides it to a superior for feedback.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>technical writing, document review, quality assurance, document control, evaluation process</t>
+          <t>technical writing, document review, quality assurance, reporting standards, evaluation documentation</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -8566,18 +8558,22 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>keep:0, "Evaluation Documentation":6, "Evaluation Documentation Preparation":1</t>
+          <t>keep:1, "Evaluation Documentation":5, "Evaluation Documentation Preparation":1</t>
         </is>
       </c>
       <c r="Z52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Strategic Plan Analysis</t>
+        </is>
+      </c>
       <c r="AB52" t="b">
         <v>0</v>
       </c>
@@ -8595,7 +8591,7 @@
         </is>
       </c>
       <c r="AH52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
@@ -8622,7 +8618,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ICT Gap Identification</t>
+          <t>Ict Gap Identification</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -8642,12 +8638,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Compares strategic objectives with current ICT capability to identify gaps, improvement opportunities, and propose changes.</t>
+          <t>Analyses strategic objectives against current ICT capability in hybrid environments to identify gaps and propose improvements.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>gap analysis, strategic alignment, ICT governance, digital transformation, ICT gaps</t>
+          <t>gap analysis, strategic alignment, ICT governance, digital transformation, improvement opportunities</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -8721,19 +8717,15 @@
         </is>
       </c>
       <c r="V53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 5/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>keep:2, "ICT Gap Identification":5</t>
+          <t>keep:4, "ICT Gap Identification":3</t>
         </is>
       </c>
       <c r="Z53" t="b">
@@ -8757,7 +8749,7 @@
         </is>
       </c>
       <c r="AH53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
@@ -8804,12 +8796,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Assesses the impact of proposed ICT system and product changes in hybrid environments against organisational strategic objectives.</t>
+          <t>Assesses proposed ICT system changes in hybrid environments for alignment with organisational strategic objectives.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>impact assessment, ICT systems, strategic objectives, change management, performance metrics</t>
+          <t>impact assessment, ICT systems, strategic alignment, change management, proposed changes</t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -8890,7 +8882,7 @@
         <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr">
@@ -8919,7 +8911,7 @@
         </is>
       </c>
       <c r="AH54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
@@ -8966,12 +8958,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Investigates innovative ideas and applies findings to refine work practices and processes.</t>
+          <t>Researches and tests innovative ideas, applying findings to refine work practices and processes.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>continuous improvement, process optimisation, ideation techniques, innovative ideas, innovation management</t>
+          <t>continuous improvement, process optimisation, ideation techniques, innovative ideas, creative problem solving</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -9065,7 +9057,7 @@
         </is>
       </c>
       <c r="AH55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
@@ -9117,7 +9109,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>financial analysis, quantitative modelling, cost‑benefit assessment, numerical data, mathematical calculations</t>
+          <t>financial analysis, quantitative modelling, cost‑benefit assessment, Excel, numerical data interpretation</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -9182,12 +9174,12 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0.952</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>keep:5, "Financial Impact Interpretation":1, "Financial Impact Assessment":1</t>
+          <t>keep:6, "Financial Impact Interpretation":1</t>
         </is>
       </c>
       <c r="Z56" t="b">
@@ -9263,7 +9255,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>regulatory standards, compliance frameworks, risk assessment, policy implementation planning, action plan</t>
+          <t>regulatory standards, compliance frameworks, risk assessment, policy implementation planning, implementation methods</t>
         </is>
       </c>
       <c r="J57" t="n">
@@ -9409,7 +9401,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>action planning, prioritised schedules, timeline management, resource allocation, critical path</t>
+          <t>action planning, prioritised schedules, timeline management, resource allocation, project scheduling</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -9511,7 +9503,7 @@
         </is>
       </c>
       <c r="AJ58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -9530,7 +9522,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Implementation Difficulty Evaluation</t>
+          <t>Difficulty Evaluation</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -9550,12 +9542,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Evaluates the difficulty of implementing proposed changes to ICT systems and products.</t>
+          <t>Assesses the difficulty of implementing proposed changes to ICT systems and products.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ICT systems, change management, implementation difficulty, proposed changes, impact assessment</t>
+          <t>ICT systems, change management, difficulty evaluation, implementation complexity, risk analysis</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -9620,16 +9612,16 @@
         <v>1</v>
       </c>
       <c r="W59" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name uses 'Planning' but evidence describes evaluating difficulty, not planning</t>
+          <t>MIS re-refinement: Skill name includes 'Planning' which is not present in the evidence; evidence only involves evaluating difficulty</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:3, "Change Difficulty Assessment/Implementation Difficulty Assessment":3, "Change Implementation Planning":1</t>
         </is>
       </c>
       <c r="Z59" t="b">
@@ -9645,7 +9637,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>Skill name uses 'Planning' but evidence describes evaluating difficulty, not planning</t>
+          <t>Skill name includes 'Planning' which is not present in the evidence; evidence only involves evaluating difficulty</t>
         </is>
       </c>
       <c r="AF59" t="b">
@@ -9709,7 +9701,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>executive communication, gap analysis, improvement recommendations, business reporting, proposed changes</t>
+          <t>executive communication, gap analysis, change management, improvement recommendations, proposed changes</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -9867,7 +9859,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>strategic plan, industry environment, organisational objectives, SWOT analysis, gap analysis</t>
+          <t>strategic alignment, SWOT analysis, organisational objectives, gap analysis, current strategic plan</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -10094,7 +10086,7 @@
         <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr">
@@ -10175,7 +10167,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>plain language, jargon translation, stakeholder communication, technical writing, audience adaptation</t>
+          <t>plain language, jargon translation, stakeholder communication, technical writing, range of personnel</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -10277,7 +10269,7 @@
         </is>
       </c>
       <c r="AJ63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -10321,7 +10313,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>legislative compliance, policy analysis, regulatory standards, qualitative analysis, legislative standards</t>
+          <t>legislative compliance, policy analysis, regulatory standards, text analysis, qualitative analysis</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -10474,7 +10466,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>privacy policy, industry standard requirements, compliance assessment, regulatory standards, data protection</t>
+          <t>privacy policy, regulatory standards, compliance, industry standards, data protection</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -10623,7 +10615,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>professional ethics, codes of conduct, ethical frameworks, ethical work practices, organisational governance</t>
+          <t>professional ethics, codes of conduct, compliance, organisational governance, ethical decision making</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -10772,7 +10764,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>grievance procedures, review processes, stakeholder communication, document management, complaint handling</t>
+          <t>grievance procedures, stakeholder communication, document management, complaint handling, feedback</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -10840,12 +10832,12 @@
         <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>keep:6, "Feedback Management":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z67" t="b">
@@ -10877,7 +10869,7 @@
         </is>
       </c>
       <c r="AJ67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -11070,7 +11062,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>literature review, source integration, technical writing, citation management, knowledge synthesis</t>
+          <t>literature review, source integration, technical writing, citation management, range of sources</t>
         </is>
       </c>
       <c r="J69" t="n">
@@ -11175,7 +11167,7 @@
         </is>
       </c>
       <c r="AJ69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -11219,7 +11211,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>intellectual property law, copyright legislation, industry standard legislation, policy compliance, regulatory analysis</t>
+          <t>intellectual property law, copyright legislation, legislative analysis, policy compliance, regulatory analysis</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -11492,7 +11484,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Policy Documentation</t>
+          <t>Privacy Policy Documentation</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -11517,7 +11509,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>privacy legislation, policy management, codes of ethics, privacy policy, regulatory documentation</t>
+          <t>privacy legislation, policy management, codes of ethics, regulatory documentation, update privacy policy</t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -11582,15 +11574,19 @@
         </is>
       </c>
       <c r="V72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W72" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X72" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/7: </t>
+        </is>
+      </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>keep:4, "Privacy Policy Documentation":3</t>
+          <t>keep:2, "Privacy Policy Documentation":5</t>
         </is>
       </c>
       <c r="Z72" t="b">
@@ -11666,7 +11662,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>grievance procedure, policy drafting, standard operating procedures, process documentation, compliance workflows</t>
+          <t>policy drafting, grievance management, standard operating procedures, document review, compliance workflows</t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -11734,7 +11730,7 @@
         <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr">
@@ -11815,7 +11811,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>scheduling, stakeholder communication, project monitoring, Gantt charts, sequences and schedules</t>
+          <t>scheduling, resource allocation, stakeholder communication, project monitoring, sequences</t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -11883,12 +11879,12 @@
         <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>keep:6, "Project Sequencing":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z74" t="b">
@@ -11968,7 +11964,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>legislation monitoring, regulatory analysis, policy tracking, legal research, rights and responsibilities</t>
+          <t>compliance, regulatory analysis, policy tracking, legal research, regulations</t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -12185,12 +12181,12 @@
         <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>0.9516666666666667</v>
+        <v>0.95</v>
       </c>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>keep:6, "Digital Information Security":1</t>
+          <t>keep:5, "Digital Information Security":2</t>
         </is>
       </c>
       <c r="Z76" t="b">
@@ -12266,7 +12262,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>policy dissemination, stakeholder engagement, communication protocols, change management, policy distribution</t>
+          <t>policy dissemination, stakeholder engagement, communication protocols, distribution, organisational compliance</t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -12334,16 +12330,16 @@
         <v>1</v>
       </c>
       <c r="W77" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>keep:0, "Policy Distribution":7</t>
+          <t>keep:2, "Policy Distribution":5</t>
         </is>
       </c>
       <c r="Z77" t="b">
@@ -12423,7 +12419,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>active listening, questioning techniques, verbal exchange, stakeholder engagement, interpersonal communication</t>
+          <t>active listening, questioning techniques, verbal communication, dialogue facilitation, interpersonal communication</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -12572,7 +12568,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>distributed ledger, node deployment, consensus configuration, Ethereum, platform for blockchain</t>
+          <t>distributed ledger, node deployment, consensus configuration, Ethereum, blockchain platform</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -12647,12 +12643,12 @@
         <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>keep:6, "Blockchain Platform Installation":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z79" t="b">
@@ -12728,7 +12724,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>anomaly detection, blockchain analytics, smart contract debugging, cryptographic forensics, nuanced understanding</t>
+          <t>anomaly detection, blockchain analytics, smart contract debugging, cryptographic forensics, resolution</t>
         </is>
       </c>
       <c r="J80" t="n">
@@ -12803,16 +12799,16 @@
         <v>1</v>
       </c>
       <c r="W80" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>keep:0, "Blockchain Anomaly Resolution":5, "Blockchain Anomaly Problem Solving":2</t>
+          <t>keep:0, "Blockchain Anomaly Resolution":7</t>
         </is>
       </c>
       <c r="Z80" t="b">
@@ -12820,9 +12816,13 @@
       </c>
       <c r="AA80" t="inlineStr"/>
       <c r="AB80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC80" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Foundation Skill describes problem‑solving capability already embedded in other skills and PCs; it does not represent a distinct task for this unit</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -12883,7 +12883,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Establishes blockchain objectives, purpose and requirements aligned with organisational needs, including consideration of hybrid environments.</t>
+          <t>Defines blockchain objectives and requirements aligned with organisational needs in hybrid environments.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -12992,7 +12992,7 @@
         </is>
       </c>
       <c r="AH81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI81" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>blockchain, consensus algorithms, peer-to-peer networking, Byzantine fault tolerance, consensus portal</t>
+          <t>blockchain, distributed ledger, consensus algorithms, consensus portal, Byzantine fault tolerance</t>
         </is>
       </c>
       <c r="J82" t="n">
@@ -13200,7 +13200,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>design plan, organisational requirements, engineering documentation, technical specifications, design standards</t>
+          <t>technical specifications, design standards, engineering documentation, organisational requirements, design documentation</t>
         </is>
       </c>
       <c r="J83" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>documentation submission, feedback response, record‑keeping, workflow approvals, electronic filing</t>
+          <t>record‑keeping, feedback loops, compliance, documentation submission, workflow approvals</t>
         </is>
       </c>
       <c r="J84" t="n">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>systems integration, workflow orchestration, process automation, integration workflow, design integration</t>
+          <t>systems integration, workflow orchestration, process automation, ETL, design integration workflow</t>
         </is>
       </c>
       <c r="J85" t="n">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>preventive maintenance, asset management, CMMS, work order scheduling, reliability engineering</t>
+          <t>preventive maintenance, asset management, CMMS, work order scheduling, maintenance schedule</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -13780,7 +13780,7 @@
         </is>
       </c>
       <c r="AJ86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Maintenance Testing Execution</t>
+          <t>Maintenance Testing</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -13824,7 +13824,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>preventive maintenance, maintenance tests, test procedures, equipment inspection, reliability testing</t>
+          <t>preventive maintenance, test procedures, equipment inspection, maintenance tests, reliability testing</t>
         </is>
       </c>
       <c r="J87" t="n">
@@ -13896,15 +13896,19 @@
         </is>
       </c>
       <c r="V87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W87" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X87" t="inlineStr"/>
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 7/7: </t>
+        </is>
+      </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>keep:4, "Maintenance Testing":3</t>
+          <t>keep:0, "Maintenance Testing":7</t>
         </is>
       </c>
       <c r="Z87" t="b">
@@ -13980,7 +13984,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>blockchain, security architecture, platform evaluation, security and platform, risk assessment</t>
+          <t>blockchain, security architecture, platform selection, cryptography, risk assessment</t>
         </is>
       </c>
       <c r="J88" t="n">
@@ -14131,12 +14135,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Executes smart commands on the required blockchain platform in accordance with the blockchain solution specifications.</t>
+          <t>Executes smart commands on the required blockchain platform in accordance with the solution specifications.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>blockchain, Ethereum, Solidity, decentralised applications, smart command</t>
+          <t>blockchain, Ethereum, Solidity, smart contract, Web3</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -14292,7 +14296,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>blockchain, smart contracts, Solidity, distributed ledger, debug</t>
+          <t>blockchain, smart contracts, Solidity, debugging, performance scaling</t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -14443,12 +14447,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Tests solution performance against organisational needs and requirements.</t>
+          <t>Tests and evaluates solutions against organisational requirements to confirm suitability.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>benchmarking, load testing, service level agreements, performance metrics, organisational requirements</t>
+          <t>benchmarking, load testing, service level agreements, performance metrics, solution</t>
         </is>
       </c>
       <c r="J91" t="n">
@@ -14552,7 +14556,7 @@
         </is>
       </c>
       <c r="AH91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
@@ -14604,7 +14608,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>stakeholder engagement, requirements gathering, industry terminology, verbal communication, active listening</t>
+          <t>stakeholder engagement, requirements gathering, industry terminology, oral communication, active listening</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -14716,7 +14720,7 @@
         </is>
       </c>
       <c r="AJ92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -14755,12 +14759,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Identifies organisational use cases aligned with business needs.</t>
+          <t>Analyses hybrid environments to identify organisational use cases aligned with business needs.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>requirements analysis, business analysis, stakeholder mapping, use‑case modelling, business needs</t>
+          <t>requirements analysis, business analysis, stakeholder mapping, use‑case modelling, use case identification</t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -14864,7 +14868,7 @@
         </is>
       </c>
       <c r="AH93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI93" t="inlineStr">
         <is>
@@ -14911,12 +14915,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Ingests data logs into analytics platforms as instructed to support monitoring and analysis.</t>
+          <t>Ingests data logs into analytic platform according to user instructions.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>data ingestion, log analytics, ETL pipelines, analytic platform, data logs</t>
+          <t>data ingestion, log analytics, ETL pipelines, analytic platform, user instructions</t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -15031,7 +15035,7 @@
         </is>
       </c>
       <c r="AH94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI94" t="inlineStr">
         <is>
@@ -15083,7 +15087,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>legislative requirements, organisational policies, threat data, data analysis, regulatory compliance</t>
+          <t>regulatory compliance, legislative requirements, policy analysis, threat intelligence, risk assessment</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -15246,7 +15250,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>data validation, anomaly detection, data quality, data auditing, data discrepancy</t>
+          <t>data validation, anomaly detection, data quality, data discrepancy, data auditing</t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -15405,7 +15409,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>log analysis, data ingestion, dataset creation, alerts, reported events</t>
+          <t>log analysis, data ingestion, dataset creation, data governance, ETL processes</t>
         </is>
       </c>
       <c r="J97" t="n">
@@ -15483,16 +15487,16 @@
         <v>1</v>
       </c>
       <c r="W97" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>keep:1, "Dataset Creation":6</t>
+          <t>keep:4, "Dataset Creation":3</t>
         </is>
       </c>
       <c r="Z97" t="b">
@@ -15572,7 +15576,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>false positives, false negatives, type I error, anomaly detection, precision‑recall analysis</t>
+          <t>type I error, false positives, false negatives, anomaly detection, precision‑recall analysis</t>
         </is>
       </c>
       <c r="J98" t="n">
@@ -15739,7 +15743,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>incident reporting, root‑cause analysis, procedural compliance, report writing, safety management</t>
+          <t>incident reporting, report writing, documentation, findings, safety management</t>
         </is>
       </c>
       <c r="J99" t="n">
@@ -15850,7 +15854,7 @@
         </is>
       </c>
       <c r="AJ99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -15894,7 +15898,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>lessons learned, action steps, recommendations, mitigation strategies, stakeholder engagement</t>
+          <t>risk management, lessons learned, action planning, mitigation planning, recommendations</t>
         </is>
       </c>
       <c r="J100" t="n">
@@ -16057,7 +16061,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>risk assessment, threat modelling, likelihood of occurrence, impact evaluation, cyber threats</t>
+          <t>risk assessment, threat modelling, impact evaluation, likelihood of occurrence, risk matrices</t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -16220,7 +16224,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>security equipment, network security, asset inventories, data sources, IDS</t>
+          <t>cyber security, network security, asset inventories, security equipment, data sources</t>
         </is>
       </c>
       <c r="J102" t="n">
@@ -16374,12 +16378,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Imports security logs into analytics platforms to support monitoring and threat detection.</t>
+          <t>Imports security logs into analytics platforms.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>log aggregation, SIEM, data ingestion, security analytics, analytic platform</t>
+          <t>log aggregation, SIEM, data ingestion, security analytics, user instructions</t>
         </is>
       </c>
       <c r="J103" t="n">
@@ -16490,7 +16494,7 @@
         </is>
       </c>
       <c r="AH103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI103" t="inlineStr">
         <is>
@@ -16542,7 +16546,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>stakeholder engagement, threat intelligence, data briefings, cyber security communication, threat data</t>
+          <t>stakeholder engagement, threat intelligence, risk reporting, findings communication, cyber security communication</t>
         </is>
       </c>
       <c r="J104" t="n">
@@ -16620,12 +16624,12 @@
         <v>0</v>
       </c>
       <c r="W104" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X104" t="inlineStr"/>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>keep:6, "Threat Findings Communication":1</t>
+          <t>keep:4, "Threat Findings Communication":3</t>
         </is>
       </c>
       <c r="Z104" t="b">
@@ -16701,7 +16705,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>threat intelligence, log analysis, SIEM, data collection, security monitoring</t>
+          <t>threat intelligence, log analysis, SIEM, dataset, security monitoring</t>
         </is>
       </c>
       <c r="J105" t="n">
@@ -16864,7 +16868,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>outlier analysis, root‑cause analysis, statistical process control, anomaly detection, context recognition</t>
+          <t>outlier analysis, root‑cause analysis, statistical process control, monitoring and diagnostics, anomaly detection</t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -16941,7 +16945,7 @@
       <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>keep:6, "Anomaly Detection":1</t>
+          <t>keep:6, "Anomaly Troubleshooting":1</t>
         </is>
       </c>
       <c r="Z106" t="b">
@@ -17017,7 +17021,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>asset management processes, additional protection plan, protection plan requirements, asset tracking, risk mitigation</t>
+          <t>asset tracking, risk mitigation, protection plans, asset management processes, implementation</t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -17165,12 +17169,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Conducts critical infrastructure research to support protection planning and documentation requirements.</t>
+          <t>Researches the organisation’s need for critical infrastructure protection and documents findings in accordance with organisational requirements.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>critical infrastructure protection, infrastructure protection, research findings, document findings, risk assessment</t>
+          <t>critical infrastructure protection, infrastructure protection, risk assessment, threat modelling, resilience analysis</t>
         </is>
       </c>
       <c r="J108" t="n">
@@ -17271,7 +17275,7 @@
         </is>
       </c>
       <c r="AH108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI108" t="inlineStr">
         <is>
@@ -17323,7 +17327,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>backup software, data retention policies, storage replication, disaster recovery, backup data</t>
+          <t>disaster recovery, backup software, data retention policies, storage replication, backup execution</t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -17476,7 +17480,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>endpoint protection, device hardening, protection plan, technical requirements, encryption</t>
+          <t>endpoint protection, device hardening, encryption, mobile device management, technical requirements</t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -17624,12 +17628,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Submits protection plans for review and incorporates stakeholder feedback to improve outcomes.</t>
+          <t>Submits the protection plan to required personnel, seeks feedback, and responds to that feedback.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>protection plan, feedback response, stakeholder communication, plan documentation, compliance reporting</t>
+          <t>stakeholder communication, feedback loops, response management, submit protection plan, compliance reporting</t>
         </is>
       </c>
       <c r="J111" t="n">
@@ -17730,7 +17734,7 @@
         </is>
       </c>
       <c r="AH111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI111" t="inlineStr">
         <is>
@@ -17777,12 +17781,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Implements network segmentation to isolate security zones in line with approved protection plans and technical requirements.</t>
+          <t>Implements network segmentation to isolate security zones in line with approved protection plans.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>network segmentation, VLANs, firewall policies, micro‑segmentation, zero‑trust architecture</t>
+          <t>VLANs, firewall policies, micro‑segmentation, network segmentation, zero‑trust architecture</t>
         </is>
       </c>
       <c r="J112" t="n">
@@ -17883,7 +17887,7 @@
         </is>
       </c>
       <c r="AH112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI112" t="inlineStr">
         <is>
@@ -17935,7 +17939,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>operational planning, performance monitoring, resource allocation, timeline management, strategy development</t>
+          <t>operational planning, performance monitoring, resource allocation, timeline management, project coordination</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -18007,12 +18011,12 @@
         <v>0</v>
       </c>
       <c r="W113" t="n">
-        <v>0.9524999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>keep:4, "Protection Strategy Coordination":3</t>
+          <t>keep:5, "Protection Strategy Coordination":2</t>
         </is>
       </c>
       <c r="Z113" t="b">
@@ -18024,7 +18028,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>FS describes work style (planning coordination) not a distinct task; capability already embedded in strategy development and implementation PCs</t>
+          <t>FS describes work style (planning and coordinating) rather than a distinct task; capability already embedded in strategy development and implementation PCs</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -18087,12 +18091,12 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Analyses the organisation’s existing critical infrastructure protection plan to identify gaps and recommend improvements.</t>
+          <t>Evaluates current critical infrastructure protection plans to identify gaps and recommend improvements.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>critical infrastructure protection, infrastructure protection plan, protection plan requirements, risk assessment, vulnerability analysis</t>
+          <t>critical infrastructure, protection plan, risk assessment, cyber security resilience, vulnerability analysis</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -18169,7 +18173,7 @@
       <c r="X114" t="inlineStr"/>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:5, "Critical Infrastructure Protection Analysis":2</t>
         </is>
       </c>
       <c r="Z114" t="b">
@@ -18193,7 +18197,7 @@
         </is>
       </c>
       <c r="AH114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
@@ -18245,7 +18249,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>critical infrastructure protection, protection plan, security policy compliance, business continuity planning, incident response frameworks</t>
+          <t>critical infrastructure, protection plan, security policy compliance, business continuity planning, incident response frameworks</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -18317,7 +18321,7 @@
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>0.9428571428571428</v>
+        <v>0.95</v>
       </c>
       <c r="X115" t="inlineStr"/>
       <c r="Y115" t="inlineStr">
@@ -18393,7 +18397,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Conducts protection plan testing to validate safeguards in line with organisational requirements.</t>
+          <t>Tests deployment of protection plan in line with organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -18503,7 +18507,7 @@
         </is>
       </c>
       <c r="AH116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI116" t="inlineStr">
         <is>
@@ -18555,7 +18559,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>data interpretation, performance metrics, compliance reporting, organisational standards, business intelligence</t>
+          <t>data interpretation, performance metrics, compliance reporting, results analysis, business intelligence</t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -18664,7 +18668,7 @@
         </is>
       </c>
       <c r="AJ117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -18683,7 +18687,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Risk Assessment Evaluation</t>
+          <t>Risk Evaluation</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -18703,12 +18707,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Determines the level of protection, vulnerability, risk and mitigation in accordance with organisational requirements.</t>
+          <t>Determines protection, vulnerability, risk and mitigation levels in line with organisational requirements.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>vulnerability analysis, mitigation planning, risk matrices, protection plan requirements, security governance</t>
+          <t>vulnerability analysis, mitigation planning, risk matrices, protection, security governance</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -18777,15 +18781,19 @@
         </is>
       </c>
       <c r="V118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W118" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X118" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 4/7: </t>
+        </is>
+      </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>keep:4, "Risk Assessment":2, "Risk Evaluation":1</t>
+          <t>keep:3, "Risk Evaluation":4</t>
         </is>
       </c>
       <c r="Z118" t="b">
@@ -19014,7 +19022,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>technical writing, process documentation, standard operating procedures, document formatting, complex workplace documentation</t>
+          <t>technical writing, process documentation, standard operating procedures, document formatting, structure layout</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -19167,7 +19175,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>information security, data inventories, data types, classification schemes, security architecture</t>
+          <t>information security, data inventories, classification schemes, data types, security architecture</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -19330,7 +19338,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>documentation, stakeholder communication, feedback loops, record‑keeping, initial feedback</t>
+          <t>documentation, stakeholder communication, feedback loops, response, internal reporting</t>
         </is>
       </c>
       <c r="J122" t="n">
@@ -19489,7 +19497,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>security architecture design, industry standard design, design methodologies, security frameworks, risk assessment</t>
+          <t>security architecture, design methodologies, industry standards, security frameworks, methodology</t>
         </is>
       </c>
       <c r="J123" t="n">
@@ -19619,7 +19627,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Contextual Anomaly Identification</t>
+          <t>Problem Solving in Security</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -19644,7 +19652,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>anomaly detection, pattern recognition, situational awareness, contextual analysis, subtle deviations</t>
+          <t>anomaly detection, threat analysis, pattern recognition, situational awareness, problem solving</t>
         </is>
       </c>
       <c r="J124" t="n">
@@ -19726,16 +19734,16 @@
         <v>1</v>
       </c>
       <c r="W124" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>keep:0, "Contextual Anomaly Identification/Security Anomaly Identification":6, "Contextual Anomaly Detection":1</t>
+          <t>keep:0, "Security Contextual Problem Solving":3, "Contextual Anomaly Identification":2, "Contextual Anomaly Detection/Security Anomaly Detection":2</t>
         </is>
       </c>
       <c r="Z124" t="b">
@@ -19743,9 +19751,13 @@
       </c>
       <c r="AA124" t="inlineStr"/>
       <c r="AB124" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC124" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Foundation Skill describes a work style (problem solving) that is already embedded in multiple performance criteria and other skills</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
@@ -19811,7 +19823,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>security architecture, security architecture findings, documentation detailing findings, cyber security requirements, compliance frameworks</t>
+          <t>security architecture, risk assessment, compliance frameworks, ISO 27001, documentation</t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -19898,7 +19910,7 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>keep:0, "Security Requirements Documentation":7</t>
+          <t>keep:0, "Security Requirements Documentation/Security Findings Documentation":7</t>
         </is>
       </c>
       <c r="Z125" t="b">
@@ -19974,7 +19986,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>security architecture, security design, technical presentations, enterprise architecture, risk assessment</t>
+          <t>information security, enterprise architecture, security frameworks, technical presentations, document form</t>
         </is>
       </c>
       <c r="J126" t="n">
@@ -20128,12 +20140,12 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Validates security designs using industry‑recognised methodologies.</t>
+          <t>Demonstrates security design using major industry‑standard design methodologies.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>security architecture, threat modelling, NIST framework, ISO 27001, design methodologies</t>
+          <t>security architecture, threat modelling, NIST framework, ISO 27001, validation</t>
         </is>
       </c>
       <c r="J127" t="n">
@@ -20240,7 +20252,7 @@
         </is>
       </c>
       <c r="AH127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
@@ -20292,7 +20304,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>security level, security features, security mode, perimeter security, security architecture</t>
+          <t>risk assessment, access control, security architecture, security level, security mode</t>
         </is>
       </c>
       <c r="J128" t="n">
@@ -20455,7 +20467,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>phased implementation, performance monitoring, project scheduling tools, operational detail, priority review</t>
+          <t>cyber security governance, risk assessment, phased implementation, performance monitoring, operational detail</t>
         </is>
       </c>
       <c r="J129" t="n">
@@ -20554,7 +20566,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>FS describes work style (planning and reviewing) not a distinct task; capability is implicit in other skills and PCs</t>
+          <t>FS describes work style (planning and reviewing) not a distinct task; capability already embedded in PCs and other skills</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -20622,7 +20634,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>security requirements, security architecture, risk assessment, threat modelling, compliance standards</t>
+          <t>risk assessment, security architecture, compliance standards, vulnerability analysis, operation and infrastructure</t>
         </is>
       </c>
       <c r="J130" t="n">
@@ -20696,7 +20708,7 @@
         <v>0</v>
       </c>
       <c r="W130" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X130" t="inlineStr"/>
       <c r="Y130" t="inlineStr">
@@ -20777,7 +20789,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>security solution design, security architecture, security requirements, solution documentation, threat modelling</t>
+          <t>cyber security architecture, security solution, design, solution documentation, threat modelling</t>
         </is>
       </c>
       <c r="J131" t="n">
@@ -20940,7 +20952,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>technical writing, documentation standards, complex workplace documentation, findings and solutions, knowledge management</t>
+          <t>technical writing, documentation standards, findings, solutions, knowledge management</t>
         </is>
       </c>
       <c r="J132" t="n">
@@ -21103,7 +21115,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>technical documentation, manufacturer manuals, job requirement analysis, engineering drawings, certification requirements</t>
+          <t>technical documentation, manufacturer manuals, job requirement analysis, reading, interpretation</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -21270,7 +21282,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>autonomy, strategic decision‑making, self‑management, high‑level decisions, organisational performance</t>
+          <t>autonomy, strategic decision‑making, self‑management, autonomous decision‑making, organisational performance</t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -21445,7 +21457,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Designs and implements forensic evidence collection processes to preserve data during incident response.</t>
+          <t>Creates and protects forensic evidence collection procedures to preserve data during incident response.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -21570,7 +21582,7 @@
         </is>
       </c>
       <c r="AH135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI135" t="inlineStr">
         <is>
@@ -21622,7 +21634,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>security incident response, incident reporting, incident response plan, incident documentation, compliance documentation</t>
+          <t>security incident response, incident reporting, document incident response, SIEM, compliance documentation</t>
         </is>
       </c>
       <c r="J136" t="n">
@@ -21765,7 +21777,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Incident Response Plan Evaluation</t>
+          <t>Incident Response Evaluation</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -21790,7 +21802,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>incident response plan, post‑incident analysis, efficiency metrics, response plan documentation, security operations</t>
+          <t>security operations, post‑incident analysis, efficiency metrics, incident response evaluation, SOC tools</t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -21878,19 +21890,15 @@
         </is>
       </c>
       <c r="V137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W137" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 4/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X137" t="inlineStr"/>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>keep:3, "Incident Response Plan Evaluation":4</t>
+          <t>keep:5, "Incident Response Plan Evaluation":2</t>
         </is>
       </c>
       <c r="Z137" t="b">
@@ -21966,7 +21974,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>incident response plan, incident handling, playbook development, risk management, NIST framework</t>
+          <t>incident response, incident handling, incident response plan, playbook development, risk management</t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -22138,7 +22146,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>incident response, incident response team, response team services, service documentation, organisational compliance</t>
+          <t>incident response, service documentation, team coordination, organisational compliance, incident response team</t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -22225,7 +22233,7 @@
         <v>0</v>
       </c>
       <c r="W139" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr">
@@ -22281,7 +22289,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Incident Response Exercise Design</t>
+          <t>Incident Response Exercise Development</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -22301,12 +22309,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Designs and conducts red‑team exercises and incident response simulations, including staffing and training plans.</t>
+          <t>Creates incident response exercises, red‑team activities, and associated staffing and training requirements.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>adversary simulation, incident response planning, threat modelling, security training programmes, MITRE ATT&amp;CK framework</t>
+          <t>adversary simulation, incident response planning, red‑teaming activities, security training programmes, MITRE ATT&amp;CK framework</t>
         </is>
       </c>
       <c r="J140" t="n">
@@ -22401,12 +22409,12 @@
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t>MIS re-refinement: Skill name implies delivering training, but evidence is about creating exercises and training requirements</t>
         </is>
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>keep:0, "Incident Response Exercise Design":5, "Incident Response Training":2</t>
+          <t>keep:0, "Incident Response Training":4, "Incident Response Exercise Design":3</t>
         </is>
       </c>
       <c r="Z140" t="b">
@@ -22418,9 +22426,13 @@
       </c>
       <c r="AC140" t="inlineStr"/>
       <c r="AD140" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE140" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>Skill name implies delivering training, but evidence is about creating exercises and training requirements</t>
+        </is>
+      </c>
       <c r="AF140" t="b">
         <v>0</v>
       </c>
@@ -22430,7 +22442,7 @@
         </is>
       </c>
       <c r="AH140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI140" t="inlineStr">
         <is>
@@ -22438,7 +22450,7 @@
         </is>
       </c>
       <c r="AJ140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -22654,7 +22666,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>quantitative analysis, technical data interpretation, system modelling, data documentation, numerical data analysis</t>
+          <t>quantitative analysis, technical data interpretation, risk assessment, document numerical, system modelling</t>
         </is>
       </c>
       <c r="J142" t="n">
@@ -22749,18 +22761,22 @@
         <v>0</v>
       </c>
       <c r="W142" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Technical Data Interpretation":1</t>
         </is>
       </c>
       <c r="Z142" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA142" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>Technical Data Interpretation</t>
+        </is>
+      </c>
       <c r="AB142" t="b">
         <v>0</v>
       </c>
@@ -22830,7 +22846,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>incident response, incident response plan, security incident, response actions, security operations centre</t>
+          <t>incident response, security operations centres, SIEM, playbook execution, security incident handling</t>
         </is>
       </c>
       <c r="J143" t="n">
@@ -22925,7 +22941,7 @@
         <v>0</v>
       </c>
       <c r="W143" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X143" t="inlineStr"/>
       <c r="Y143" t="inlineStr">
@@ -23006,7 +23022,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>incident management policy, incident response, security incident, governance, ISO 27001</t>
+          <t>incident management, policy development, governance, compliance, ISO 27001</t>
         </is>
       </c>
       <c r="J144" t="n">
@@ -23182,7 +23198,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>quantitative analysis, technical system data, data documentation, engineering diagnostics, numeracy</t>
+          <t>quantitative analysis, technical system data, measurement instrumentation, data documentation, numerical interpretation</t>
         </is>
       </c>
       <c r="J145" t="n">
@@ -23362,7 +23378,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>business continuity, impact analysis, disaster recovery, resilience planning, system impact</t>
+          <t>business continuity, risk assessment, impact analysis, disaster recovery, evaluation</t>
         </is>
       </c>
       <c r="J146" t="n">
@@ -23522,12 +23538,12 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Designs and implements compliance strategies to align organisational processes with regulatory requirements.</t>
+          <t>Develops and implements strategies to ensure organisational policies, procedures and regulatory requirements are met.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>regulatory compliance, policy enforcement, risk management, governance, legislative requirements</t>
+          <t>regulatory compliance, policy enforcement, risk management, governance, implementation</t>
         </is>
       </c>
       <c r="J147" t="n">
@@ -23628,7 +23644,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>FS describes work style/strategic compliance activity already implicit in other skills and not a distinct task for this unit</t>
+          <t>FS describes work style (ensuring compliance) rather than a distinct unit task; capability is implicit in other skills like Risk Analysis and Business Continuity Evaluation</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -23644,7 +23660,7 @@
         </is>
       </c>
       <c r="AH147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI147" t="inlineStr">
         <is>
@@ -23691,12 +23707,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Develops a contingency plan by identifying threats.</t>
+          <t>Develops contingency plans by identifying threats.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>contingency planning, contingency plan, threat identification, business continuity, risk assessment</t>
+          <t>contingency plan, risk assessment, business continuity, threat identification, mitigation strategies</t>
         </is>
       </c>
       <c r="J148" t="n">
@@ -23793,9 +23809,13 @@
         </is>
       </c>
       <c r="Z148" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA148" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>Disaster Recovery Planning</t>
+        </is>
+      </c>
       <c r="AB148" t="b">
         <v>0</v>
       </c>
@@ -23865,7 +23885,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>cost‑benefit analysis, business specifications, cost constraints, disaster recovery, prevention and recovery options</t>
+          <t>cost‑benefit analysis, budgeting, risk assessment, business case evaluation, cost constraints</t>
         </is>
       </c>
       <c r="J149" t="n">
@@ -24030,7 +24050,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>disaster recovery plan, business continuity, backup and restore, recovery time objectives, risk assessment</t>
+          <t>business continuity, backup and restore, recovery time objectives, risk assessment, disaster recovery testing</t>
         </is>
       </c>
       <c r="J150" t="n">
@@ -24155,7 +24175,7 @@
         </is>
       </c>
       <c r="AJ150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -24199,7 +24219,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>industry standard operational, risk safeguards, standard operating procedures, compliance, risk management</t>
+          <t>compliance, risk management, standard operating procedures, regulatory guidance, safeguards</t>
         </is>
       </c>
       <c r="J151" t="n">
@@ -24364,7 +24384,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>quantitative analysis, financial modelling, technical data interpretation, statistical methods, data documentation</t>
+          <t>quantitative analysis, financial modelling, technical data interpretation, statistical methods, business data analysis</t>
         </is>
       </c>
       <c r="J152" t="n">
@@ -24533,7 +24553,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>prevention strategy, recovery strategy, disaster recovery plan, mitigation planning, scenario analysis</t>
+          <t>risk assessment, mitigation planning, prevention strategy, recovery planning, scenario analysis</t>
         </is>
       </c>
       <c r="J153" t="n">
@@ -24702,7 +24722,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>data analysis, feedback loops, process improvement, root‑cause analysis, continuous improvement</t>
+          <t>data analysis, feedback loops, process improvement, root‑cause analysis, problem solving</t>
         </is>
       </c>
       <c r="J154" t="n">
@@ -24790,7 +24810,7 @@
         <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>0.9428571428571428</v>
+        <v>0.95</v>
       </c>
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="inlineStr">
@@ -24831,7 +24851,7 @@
         </is>
       </c>
       <c r="AJ154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -24870,12 +24890,12 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Conducts comprehensive risk assessments and carries out disaster recovery and contingency planning.</t>
+          <t>Conducts comprehensive risk assessments and develops disaster recovery and contingency solutions.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>risk assessment, disaster recovery, contingency planning, business continuity, threat modelling</t>
+          <t>risk assessment, disaster recovery, contingency planning, business continuity, risk analysis</t>
         </is>
       </c>
       <c r="J155" t="n">
@@ -24992,15 +25012,15 @@
         </is>
       </c>
       <c r="AH155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>risk assessment, disaster recovery, contingency planning, business continuity, threat modelling</t>
+        </is>
+      </c>
+      <c r="AJ155" t="b">
         <v>1</v>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>risk assessment, disaster recovery, contingency planning, business continuity, threat modelling</t>
-        </is>
-      </c>
-      <c r="AJ155" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -25044,7 +25064,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>stakeholder engagement, feedback loops, document management, communication protocols, collaboration tools</t>
+          <t>stakeholder engagement, feedback loops, document management, communication protocols, submit document</t>
         </is>
       </c>
       <c r="J156" t="n">
@@ -25165,7 +25185,7 @@
         </is>
       </c>
       <c r="AJ156" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -25209,7 +25229,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>priority alignment, outcome mapping, roadmap development, performance metrics, contingency planning</t>
+          <t>priority alignment, outcome mapping, strategic planning, performance metrics, scenario analysis</t>
         </is>
       </c>
       <c r="J157" t="n">
@@ -25298,7 +25318,7 @@
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:5, "Strategy Prioritisation":2</t>
         </is>
       </c>
       <c r="Z157" t="b">
@@ -25306,13 +25326,9 @@
       </c>
       <c r="AA157" t="inlineStr"/>
       <c r="AB157" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Foundation Skill describes a work style (strategic planning) that is already embedded in other skills and PCs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC157" t="inlineStr"/>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
@@ -25378,7 +25394,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>communication tools, relationship building, stakeholder engagement, collaboration platforms, effective working relationships</t>
+          <t>communication tools, relationship building, stakeholder engagement, collaboration platforms, team collaboration</t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -25543,7 +25559,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>specification drafting, process documentation, evaluation reporting, strategic articulation, document control</t>
+          <t>specification drafting, process documentation, evaluation reporting, strategic articulation, technical writing</t>
         </is>
       </c>
       <c r="J159" t="n">
@@ -25664,7 +25680,7 @@
         </is>
       </c>
       <c r="AJ159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
@@ -25708,7 +25724,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>risk analysis, vulnerability assessment, threat modelling, cyber security, intelligence gathering</t>
+          <t>risk analysis, vulnerability assessment, threat modelling, cyber security, evaluate</t>
         </is>
       </c>
       <c r="J160" t="n">
@@ -25833,7 +25849,7 @@
         </is>
       </c>
       <c r="AJ160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -25870,16 +25886,16 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Provides clear, evidence‑based answers to queries, supporting each response with relevant data or rationale.</t>
+          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting decisions with relevant data and reasoning.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>evidence based answers, substantiated responses, query handling, data support, rationale provision</t>
+          <t>evidence based answers, stakeholder queries, data support, reasoning justification, clear communication</t>
         </is>
       </c>
       <c r="J161" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -25941,7 +25957,7 @@
         <v>0</v>
       </c>
       <c r="W161" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="X161" t="inlineStr">
         <is>
@@ -25966,7 +25982,7 @@
       </c>
       <c r="AG161" t="inlineStr">
         <is>
-          <t>Provides clear, evidence‑based answers to queries, supporting each response with relevant data or rationale.</t>
+          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting decisions with relevant data and reasoning.</t>
         </is>
       </c>
       <c r="AH161" t="b">
@@ -25974,7 +25990,7 @@
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>evidence based answers, substantiated responses, query handling, data support, rationale provision</t>
+          <t>evidence based answers, stakeholder queries, data support, reasoning justification, clear communication</t>
         </is>
       </c>
       <c r="AJ161" t="b">
@@ -26015,12 +26031,12 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Assists in confirming and documenting the types of information stored on each registered digital device.</t>
+          <t>Assists in identifying and confirming the types of information stored on each registered digital device.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, data mapping, asset documentation, registered devices</t>
+          <t>device data inventory, information classification, data mapping, asset documentation, device identification</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -26111,7 +26127,7 @@
       </c>
       <c r="AG162" t="inlineStr">
         <is>
-          <t>Assists in confirming and documenting the types of information stored on each registered digital device.</t>
+          <t>Assists in identifying and confirming the types of information stored on each registered digital device.</t>
         </is>
       </c>
       <c r="AH162" t="b">
@@ -26119,7 +26135,7 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, data mapping, asset documentation, digital records</t>
+          <t>device data inventory, information classification, data mapping, asset documentation, storage verification</t>
         </is>
       </c>
       <c r="AJ162" t="b">
@@ -26140,7 +26156,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Sign‑off Acquisition</t>
+          <t>Sign‑off Coordination</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -26160,12 +26176,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated stakeholders by coordinating, presenting, and confirming sign‑off requirements.</t>
+          <t>Secures final approval from designated personnel by organising, presenting, and confirming sign‑off requirements.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>approval coordination, stakeholder engagement, sign‑off confirmation, final authorization, approval documentation</t>
+          <t>approval process, stakeholder engagement, sign‑off management, final sign‑off, coordination</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -26226,7 +26242,7 @@
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>Sign‑off Acquisition</t>
+          <t>Sign‑off Coordination</t>
         </is>
       </c>
       <c r="V163" t="b">
@@ -26258,7 +26274,7 @@
       </c>
       <c r="AG163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated stakeholders by coordinating, presenting, and confirming sign‑off requirements.</t>
+          <t>Secures final approval from designated personnel by organising, presenting, and confirming sign‑off requirements.</t>
         </is>
       </c>
       <c r="AH163" t="b">
@@ -26266,11 +26282,11 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>approval coordination, stakeholder engagement, sign‑off confirmation, final authorization, approval documentation</t>
+          <t>approval process, stakeholder engagement, documentation finalisation, authority confirmation, sign‑off management</t>
         </is>
       </c>
       <c r="AJ163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -26307,16 +26323,16 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation, considering relevant legislation and policies.</t>
+          <t>Identifies organisational processes and transaction types suitable for blockchain implementation and determines relevant legislation, organisational policies and procedures, as well as their impact on the solution.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>process analysis, transaction evaluation, blockchain suitability, regulatory compliance, blockchain technology</t>
+          <t>organisational processes, transaction types, blockchain suitability, legislative impact, blockchain technology</t>
         </is>
       </c>
       <c r="J164" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -26388,7 +26404,7 @@
         <v>0</v>
       </c>
       <c r="W164" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="X164" t="inlineStr">
         <is>
@@ -26413,15 +26429,15 @@
       </c>
       <c r="AG164" t="inlineStr">
         <is>
-          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation, considering relevant legislation and policies.</t>
+          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation.</t>
         </is>
       </c>
       <c r="AH164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>process analysis, transaction evaluation, blockchain suitability, regulatory compliance, organisational policy</t>
+          <t>organisational processes, transaction types, blockchain suitability, legislative impact, policy compliance</t>
         </is>
       </c>
       <c r="AJ164" t="b">
@@ -26442,7 +26458,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Data Log Strategy Discussion</t>
+          <t>Log Requirement Consultation</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -26462,16 +26478,16 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Facilitates discussions with relevant personnel to confirm data log requirements and processing strategies.</t>
+          <t>Collaborates with relevant personnel to discuss and confirm data log requirements and processing strategy.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel coordination, discussion facilitation, requirement confirmation</t>
+          <t>data log requirements, processing strategy, personnel consultation, requirement discussion, confirm data log</t>
         </is>
       </c>
       <c r="J165" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -26526,14 +26542,14 @@
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>Data Log Strategy Discussion</t>
+          <t>Log Requirement Consultation</t>
         </is>
       </c>
       <c r="V165" t="b">
         <v>0</v>
       </c>
       <c r="W165" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="X165" t="inlineStr">
         <is>
@@ -26558,7 +26574,7 @@
       </c>
       <c r="AG165" t="inlineStr">
         <is>
-          <t>Facilitates discussions with relevant personnel to confirm data log requirements and processing strategies.</t>
+          <t>Collaborates with relevant personnel to discuss and confirm data log requirements and processing strategy.</t>
         </is>
       </c>
       <c r="AH165" t="b">
@@ -26566,11 +26582,11 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel coordination, discussion facilitation, requirement confirmation</t>
+          <t>data log requirements, processing strategy, personnel consultation, requirement discussion, log strategy confirmation</t>
         </is>
       </c>
       <c r="AJ165" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -26607,7 +26623,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Evaluates gathered threat data results to confirm reliability and consistency before further processing.</t>
+          <t>The worker evaluates gathered threat data results to confirm reliability and consistency before further processing.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -26703,7 +26719,7 @@
       </c>
       <c r="AG166" t="inlineStr">
         <is>
-          <t>Evaluates gathered threat data results to confirm reliability and consistency before further processing.</t>
+          <t>The worker evaluates gathered threat data results to confirm reliability and consistency before further processing.</t>
         </is>
       </c>
       <c r="AH166" t="b">
@@ -26752,12 +26768,12 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Determines the effectiveness and alignment of the existing protection plan with organisational requirements, and identifies operational systems, critical assets, network segmentation and legislative requirements.</t>
+          <t>Assess the current protection plan's effectiveness and ensure it aligns with organisational and legislative requirements.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>plan effectiveness, organisational alignment, regulatory compliance, critical assets, operational systems</t>
+          <t>protection plan assessment, effectiveness analysis, organisational alignment, critical asset identification, operational systems</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -26855,19 +26871,19 @@
       </c>
       <c r="AG167" t="inlineStr">
         <is>
-          <t>Evaluates how well the current protection plan meets organisational needs and regulatory requirements.</t>
+          <t>Assess the current protection plan's effectiveness and ensure it aligns with organisational and legislative requirements.</t>
         </is>
       </c>
       <c r="AH167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>protection plan assessment, effectiveness analysis, organisational alignment, legislative compliance, critical asset identification</t>
+        </is>
+      </c>
+      <c r="AJ167" t="b">
         <v>1</v>
-      </c>
-      <c r="AI167" t="inlineStr">
-        <is>
-          <t>plan effectiveness, organisational alignment, regulatory compliance, critical assets, operational systems</t>
-        </is>
-      </c>
-      <c r="AJ167" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -26884,7 +26900,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Incident Plan Alignment</t>
+          <t>Plan Alignment Documentation</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -26904,12 +26920,12 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>The worker assesses the current incident response plan, documents its compliance with requirements, and submits it for feedback.</t>
+          <t>The worker determines and documents how the existing incident response plan aligns with identified requirements, then submits the documentation to the required personnel and addresses any feedback received.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment assessment, documentation, compliance verification, feedback submission</t>
+          <t>incident response plan, alignment, documentation, requirements, submit</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -26982,7 +26998,7 @@
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>Incident Plan Alignment</t>
+          <t>Plan Alignment Documentation</t>
         </is>
       </c>
       <c r="V168" t="b">
@@ -27014,19 +27030,19 @@
       </c>
       <c r="AG168" t="inlineStr">
         <is>
-          <t>The worker assesses the current incident response plan, documents its compliance with requirements, and submits it for feedback.</t>
+          <t>The worker aligns the current incident response plan with requirements and records the findings for review.</t>
         </is>
       </c>
       <c r="AH168" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment assessment, documentation, compliance verification, feedback submission</t>
+          <t>incident response plan, alignment, documentation, requirements, feedback</t>
         </is>
       </c>
       <c r="AJ168" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -27063,16 +27079,16 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing and securely preserving incident evidence in line with organisational requirements.</t>
+          <t>Assist in gathering, processing, and securely preserving evidence in line with organisational requirements.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, incident response, legislative requirements</t>
+          <t>evidence collection, evidence processing, evidence preservation, security requirements, incident response</t>
         </is>
       </c>
       <c r="J169" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -27147,7 +27163,7 @@
         <v>0</v>
       </c>
       <c r="W169" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="X169" t="inlineStr">
         <is>
@@ -27172,7 +27188,7 @@
       </c>
       <c r="AG169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing and securely preserving incident evidence in line with organisational requirements.</t>
+          <t>Assist in gathering, processing, and securely preserving evidence in line with organisational requirements.</t>
         </is>
       </c>
       <c r="AH169" t="b">
@@ -27180,11 +27196,11 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, incident response, organisational requirements</t>
+          <t>evidence collection, evidence processing, evidence preservation, security requirements, incident response</t>
         </is>
       </c>
       <c r="AJ169" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -27221,12 +27237,12 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Identify essential business functions, data, and software, and assess ICT risk impacts on them.</t>
+          <t>Identifies essential business functions, critical data, and software, and evaluates risk impacts on ICT systems.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>business critical functions, security environment, critical data, software assets, ICT risk assessment</t>
+          <t>business critical functions, security environment, critical data, software assets, threat assessment</t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -27325,7 +27341,7 @@
       </c>
       <c r="AG170" t="inlineStr">
         <is>
-          <t>Identify essential business functions, data, and software, and assess ICT risk impacts on them.</t>
+          <t>Identifies essential business functions, critical data, and software, and evaluates risk impacts on ICT systems.</t>
         </is>
       </c>
       <c r="AH170" t="b">
@@ -27333,11 +27349,11 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>business critical functions, security environment, critical data, software assets, ICT risk assessment</t>
+          <t>business critical functions, security environment, critical data, software assets, risk impact assessment</t>
         </is>
       </c>
       <c r="AJ170" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
@@ -27374,12 +27390,12 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>The worker identifies, records, and finalises disaster strategy processes, cut‑over criteria, and obtains sign‑off.</t>
+          <t>Creates and records detailed disaster strategy processes, cut‑over criteria, and secures final task sign‑off.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>disaster strategy, process documentation, cut‑over criteria, task sign‑off, disaster recovery plan</t>
+          <t>disaster strategy, cut‑over criteria, task sign‑off, document disaster strategy, final task sign‑off</t>
         </is>
       </c>
       <c r="J171" t="n">
@@ -27478,7 +27494,7 @@
       </c>
       <c r="AG171" t="inlineStr">
         <is>
-          <t>The worker identifies, records, and finalises disaster strategy processes, cut‑over criteria, and obtains sign‑off.</t>
+          <t>Creates and records detailed disaster strategy processes, cut‑over criteria, and secures final task sign‑off.</t>
         </is>
       </c>
       <c r="AH171" t="b">
@@ -27486,7 +27502,7 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>disaster strategy, process documentation, cut‑over criteria, task sign‑off, finalisation</t>
+          <t>disaster strategy, process documentation, cut‑over criteria, task sign‑off, implementation</t>
         </is>
       </c>
       <c r="AJ171" t="b">

--- a/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v7.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v7.xlsx
@@ -648,12 +648,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Elicits others’ views and opinions to develop and refine ideas during collaborative discussions.</t>
+          <t>Elicits others’ views and integrates feedback to refine ideas during collaborative discussions.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>communication, empathy, stakeholder engagement, elicitation, viewpoint</t>
+          <t>stakeholder engagement, feedback, communication, empathy, viewpoint elicitation</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="AH2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>benchmarking, best practice, similar products, competitive analysis, industry standards</t>
+          <t>benchmarking, best practice, performance metrics, competitive analysis, industry standards</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="AJ3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -987,7 +987,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ideation, creative problem solving, mind mapping, group facilitation, idea generation</t>
+          <t>ideation, brainstorming, idea generation, creative problem solving, group facilitation</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>analytical methodology, systematic concept evaluation, ideation processes, feasibility analysis, concept gathering</t>
+          <t>systematic analytical processes, concept evaluation, analytical methodology, feasibility analysis, design thinking</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name uses 'Planning' which is not present in evidence; evidence describes gathering and evaluating concepts, not planning</t>
+          <t>MIS re-refinement: Skill name uses 'Planning' but evidence describes gathering and evaluating concepts, not planning</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Skill name uses 'Planning' which is not present in evidence; evidence describes gathering and evaluating concepts, not planning</t>
+          <t>Skill name uses 'Planning' but evidence describes gathering and evaluating concepts, not planning</t>
         </is>
       </c>
       <c r="AF5" t="b">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>creative thinking, ideation, innovation, brainstorming, design thinking</t>
+          <t>ideation, innovation, brainstorming, design thinking, problem solving</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="AJ6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>record‑keeping, compliance, audit trail, feedback documentation, organisational standards</t>
+          <t>record‑keeping, compliance, audit trail, quality assurance, organisational standards</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="AJ7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Idea Viability Assessment</t>
+          <t>Idea Viability Evaluation</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>feasibility analysis, risk assessment, criteria weighting, idea viability, market viability</t>
+          <t>feasibility analysis, criteria weighting, business case evaluation, market viability, idea viability</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>keep:0, "Idea Viability Assessment/Solution Viability Assessment":4, "Idea Viability Evaluation":3</t>
+          <t>keep:0, "Idea Viability Evaluation":4, "Idea Viability Assessment":3</t>
         </is>
       </c>
       <c r="Z8" t="b">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Collaborates with relevant personnel to identify and select consultation issues for focused analysis.</t>
+          <t>Selects an issue to be explored, consulting relevant personnel to ensure relevance.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>stakeholder engagement, problem identification, needs assessment, issue selection, decision‑making</t>
+          <t>stakeholder engagement, problem identification, needs assessment, consultation processes, decision‑making</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="AH9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         </is>
       </c>
       <c r="AJ9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Drafts detailed proposals and plans using sector‑specific terminology for stakeholder review.</t>
+          <t>Prepares proposals and plans for relevant stakeholders incorporating appropriate vocabulary</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>stakeholder communication, business case development, grant and RFP responses, persuasive writing, proposal</t>
+          <t>stakeholder communication, business case development, grant and RFP responses, technical documentation, persuasive writing</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="AH10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="AJ10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Gathers and evaluates relevant data to identify viable solutions to the identified issue.</t>
+          <t>Researches information on possible solutions to the identified issue.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>literature review, data collection, search strategies, online databases, research information</t>
+          <t>literature review, data collection, search strategies, online databases, information research</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="AH11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>stakeholder communication, visual presentation tools, solution pitching, format selection, solution presentation</t>
+          <t>solution presentation, stakeholder communication, visual presentation tools, format selection, solution pitching</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>requirements analysis, design optimisation, prototype testing, solution refinement, validation feedback</t>
+          <t>requirements analysis, design optimisation, prototype testing, solution finalisation, validation feedback</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -2536,7 +2536,7 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>keep:6, "Solution Refinement":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z13" t="b">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>feasibility analysis, constraint identification, solution viability, risk assessment, decision matrices</t>
+          <t>feasibility analysis, constraint identification, business issue evaluation, risk assessment, decision matrices</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="AJ14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Proactively seeks stakeholder input on ideas to refine concepts and align expectations.</t>
+          <t>Seeks feedback from stakeholders on ideas to refine concepts and align expectations.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>stakeholder engagement, feedback collection, surveys, interviews, stakeholder solicitation</t>
+          <t>stakeholder engagement, feedback collection, surveys, interviews, communication</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="AH15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="AJ15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Discussion Facilitation</t>
+          <t>Group Interaction Facilitation</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>group dynamics, meeting facilitation, conflict resolution, consensus building, discussion</t>
+          <t>group dynamics, meeting facilitation, conflict resolution, consensus building, group interaction</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>keep:0, "Discussion Facilitation":6, "Group Interaction Facilitation":1</t>
+          <t>keep:2, "Group Interaction Facilitation":4, "Discussion Facilitation":1</t>
         </is>
       </c>
       <c r="Z16" t="b">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Creates and updates cyber security awareness program reflecting organisation-wide best practice.</t>
+          <t>Creates and maintains a cyber security awareness program that reflects organisation-wide best practice.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>cyber security, security awareness training, phishing simulations, compliance governance, security awareness program</t>
+          <t>cyber security, security awareness training, risk management, phishing simulations, compliance governance</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="AJ17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>cyber security terminology, technical documentation, clear technical writing, industry standards (ISO 27001, NIST), risk assessment reporting</t>
+          <t>cyber security terminology, technical documentation, information security policies, industry standards (ISO 27001, NIST), risk assessment reporting</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="AJ18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>cyber security awareness, risk awareness, security posture, threat intelligence, security metrics</t>
+          <t>cyber security, risk awareness, security posture, threat intelligence, security metrics</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c r="AJ19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>cyber security, policy compliance, risk communication, improvement requirements, stakeholder reporting</t>
+          <t>cyber security, policy compliance, risk communication, security standards, stakeholder reporting</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="AJ20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>stakeholder communication, knowledge transfer, visual storytelling, presentation tools, insight</t>
+          <t>insights presentation, stakeholder communication, knowledge transfer, visual storytelling, presentation tools</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Notifiable Data Breach, Australian Privacy Act, data protection compliance, privacy law interpretation, legislation</t>
+          <t>Notifiable Data Breach, Australian Privacy Act, data protection compliance, privacy law interpretation, regulatory risk assessment</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="AJ22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Prepares detailed review outcome reports outlining improvement recommendations for relevant personnel.</t>
+          <t>Documents outcomes of the review and suggested improvements for consideration by required personnel.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>reporting, review outcomes, improvement recommendations, outcome documentation, stakeholder communication</t>
+          <t>reporting, review outcomes, improvement recommendations, stakeholder communication, record‑keeping</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="AH23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="AJ23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>cyber security governance, policy development, drafting, stakeholder communication, compliance frameworks</t>
+          <t>cyber security governance, policy development, cyber security policies, stakeholder communication, compliance frameworks</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>cyber security documentation, information security records, compliance logging, data governance, record maintenance</t>
+          <t>cyber security documentation, information security records, compliance logging, data governance, audit trail management</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -4654,7 +4654,7 @@
         </is>
       </c>
       <c r="AJ26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -4693,12 +4693,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Engages relevant stakeholders through meetings and surveys to gather input that informs decision‑making.</t>
+          <t>Consults with stakeholders to inform decision making</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>stakeholder engagement, consultation workshops, decision support, stakeholder consultation, needs analysis</t>
+          <t>stakeholder engagement, consultation workshops, decision support, needs analysis, facilitation</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -4769,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr">
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="AH27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="AJ27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -4845,12 +4845,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Collaborates with interdisciplinary teams to promote cyber security.</t>
+          <t>Works collaboratively with interdisciplinary teams to promote cyber security.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>interdisciplinary teamwork, cyber security coordination, cross‑functional communication, stakeholder engagement, team collaboration</t>
+          <t>interdisciplinary teamwork, cyber security coordination, cross‑functional communication, stakeholder engagement, collaboration tools</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="AJ28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>cyber security, security platforms, technology platforms, SIEM, threat monitoring</t>
+          <t>technology platforms, cyber security, security platforms, SIEM, threat monitoring</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -5085,7 +5085,7 @@
         <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Analyses current cyber threat reports to assess organisational impacts and advise on security measures.</t>
+          <t>Reviews latest cyber security threats and trends impacting organisations.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>cyber security, threat intelligence, trend monitoring, security analytics, trends impacting organisations</t>
+          <t>cyber security, threat intelligence, trend monitoring, vulnerability assessment, security analytics</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -5249,7 +5249,7 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.9528571428571428</v>
       </c>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="AH30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="AJ30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Coordinates training sessions and information updates by scheduling, delivering and recording activities.</t>
+          <t>Arranges training and information updates as required, maintaining related records.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>training schedules, learning management systems, record management, information updates, training coordination</t>
+          <t>training coordination, training schedules, learning management systems, record management, information updates</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="AH31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Installs and configures up‑to‑date anti‑malware on all workstations to ensure continuous protection.</t>
+          <t>Installs and runs latest anti‑malware on each device.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="AH34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
@@ -5764,12 +5764,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Analyses breach volumes and assesses business impacts across review periods to inform risk mitigation.</t>
+          <t>Reviews number of breaches and business impact over the review period.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>risk assessment, incident tracking, business impact analysis, breach, security metrics</t>
+          <t>risk assessment, incident tracking, business impact analysis, compliance reporting, security metrics</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="AH35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="AJ35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Performs initial device set‑up by updating firmware and configuring settings on new devices.</t>
+          <t>Ensures new devices are updated and configured correctly as part of the initial start‑up procedure.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>device provisioning, firmware updates, configuration management, hardware initialisation, device setup</t>
+          <t>device provisioning, firmware updates, configuration management, hardware initialisation, system onboarding</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="AH36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="AJ36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>encryption, device security, endpoint encryption, mobile device management, implementation</t>
+          <t>encryption, device security, endpoint encryption, mobile device management, cryptography</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="AJ37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>IT asset tracking, hardware registers, network inventories, device register, asset management software</t>
+          <t>digital device register, IT asset tracking, hardware registers, network inventories, CMDB</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Conducts gap analyses to assess and benchmark best‑practice implementation effectiveness.</t>
+          <t>Conducts gap analyses to evaluate best‑practice implementation effectiveness.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>gap analysis, benchmarking, performance metrics, best‑practice assessment, effectiveness evaluation</t>
+          <t>benchmarking, performance metrics, best‑practice assessment, process improvement, effectiveness evaluation</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -6524,7 +6524,7 @@
         </is>
       </c>
       <c r="AH39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         </is>
       </c>
       <c r="AJ39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>authentication, password complexity, password strength, cyber security, password managers</t>
+          <t>authentication, password complexity, entropy, cyber security, password managers</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -6687,7 +6687,7 @@
         </is>
       </c>
       <c r="AJ40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Develops comprehensive physical security plans and disseminates them organisation‑wide to ensure coordinated protection.</t>
+          <t>Develops physical security plan and communicates it to the whole organisation.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>risk assessment, access control systems, security policy development, facility protection, physical security plan</t>
+          <t>risk assessment, access control systems, security policy development, facility protection, stakeholder communication</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="AH41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="AJ41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Assesses device data sensitivity to assign appropriate risk categories for security management.</t>
+          <t>Categorises level of risk associated with each device based on sensitivity of information stored.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="AH42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Security Plan Communication</t>
+          <t>Physical Security Plan Communication</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>physical security, security policy, stakeholder communication, access control, security plan</t>
+          <t>physical security, physical security plan, security policy, stakeholder communication, access control</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -7136,15 +7136,19 @@
         </is>
       </c>
       <c r="V43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W43" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="X43" t="inlineStr"/>
+        <v>0.91</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 4/7: </t>
+        </is>
+      </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>keep:3, "Physical Security Planning":2, "Physical Security Plan Communication":2</t>
+          <t>keep:2, "Physical Security Plan Communication":4, "Physical Security Planning":1</t>
         </is>
       </c>
       <c r="Z43" t="b">
@@ -7224,7 +7228,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>risk assessment, encryption standards, device hardening, security protocol, cyber security governance</t>
+          <t>risk assessment, encryption standards, device hardening, cyber security governance, protocol compliance</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -7306,7 +7310,7 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr">
@@ -7343,7 +7347,7 @@
         </is>
       </c>
       <c r="AJ44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -7382,12 +7386,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Advises the organisation by evaluating options and recommending optimal security strategies.</t>
+          <t>Supports the organisation in selecting the most appropriate security strategies.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>cyber security governance, risk assessment, security frameworks, threat modelling, security strategies</t>
+          <t>cyber security governance, risk assessment, security frameworks, threat modelling, ISO 27001</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -7498,7 +7502,7 @@
         </is>
       </c>
       <c r="AH45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
@@ -7506,7 +7510,7 @@
         </is>
       </c>
       <c r="AJ45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -7545,12 +7549,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Monitors emerging digital security developments to inform risk assessments and protective measures.</t>
+          <t>Monitors latest developments in digital security.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>cyber security, threat intelligence, vulnerability tracking, digital security, security monitoring</t>
+          <t>digital security, cyber security, threat intelligence, vulnerability tracking, security intelligence feeds</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -7632,12 +7636,12 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>keep:2, "Security Development Monitoring":5</t>
+          <t>keep:3, "Security Development Monitoring":4</t>
         </is>
       </c>
       <c r="Z46" t="b">
@@ -7661,7 +7665,7 @@
         </is>
       </c>
       <c r="AH46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
@@ -7708,12 +7712,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Installs and configures software patches on desktop and mobile devices to maintain system security.</t>
+          <t>Installs software patches on desktop and mobile devices to maintain system security.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>patch management, software updates, endpoint management, mobile device management, desktop devices</t>
+          <t>patch management, software updates, endpoint management, mobile device management, security patches</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -7824,7 +7828,7 @@
         </is>
       </c>
       <c r="AH47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
@@ -7832,7 +7836,7 @@
         </is>
       </c>
       <c r="AJ47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -7851,7 +7855,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Multi-factor Authentication Enablement</t>
+          <t>Two-factor Authentication Enablement</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -7876,7 +7880,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>multi‑factor authentication, MFA, two-factor authentication, access control, cyber security</t>
+          <t>two-factor authentication, multi-factor authentication, OTP, access control, cyber security</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -7958,16 +7962,16 @@
         <v>1</v>
       </c>
       <c r="W48" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>keep:1, "Multi-factor Authentication Enablement":6</t>
+          <t>keep:5, "Multi-factor Authentication Enablement":2</t>
         </is>
       </c>
       <c r="Z48" t="b">
@@ -8038,12 +8042,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Develops detailed action plans aligned with policies, prioritising tasks and scheduling implementation.</t>
+          <t>Develops action plans to implement proposed changes, ensuring a prioritised schedule and alignment with organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>action plan, project scheduling, prioritisation, policy compliance, change management</t>
+          <t>project scheduling, prioritisation, policy compliance, change management, implementation planning</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -8108,7 +8112,7 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr">
@@ -8137,7 +8141,7 @@
         </is>
       </c>
       <c r="AH49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
@@ -8145,7 +8149,7 @@
         </is>
       </c>
       <c r="AJ49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -8184,12 +8188,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Ranks proposed changes to clarify improvement opportunities and inform implementation scheduling.</t>
+          <t>Prioritises proposed changes to refine opportunities and assist in scheduling implementation.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>change management, prioritisation, opportunity assessment, implementation scheduling, proposed changes</t>
+          <t>change management, prioritisation, opportunity assessment, implementation scheduling, project planning</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -8287,7 +8291,7 @@
         </is>
       </c>
       <c r="AH50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
@@ -8295,7 +8299,7 @@
         </is>
       </c>
       <c r="AJ50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -8339,7 +8343,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data management, digital collaboration tools, emerging technologies, cloud computing, digital technology utilisation</t>
+          <t>digital technologies, emerging technologies, data management, cloud computing, data visualisation</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -8484,12 +8488,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Documents the evaluation process and provides it to a superior for feedback.</t>
+          <t>Documents evaluation process and provides it to a supervisor for feedback.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>technical writing, document review, quality assurance, reporting standards, evaluation documentation</t>
+          <t>technical writing, document review, quality assurance, reporting standards, document evaluation</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -8558,22 +8562,18 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>keep:1, "Evaluation Documentation":5, "Evaluation Documentation Preparation":1</t>
+          <t>keep:1, "Evaluation Documentation":6</t>
         </is>
       </c>
       <c r="Z52" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>Strategic Plan Analysis</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA52" t="inlineStr"/>
       <c r="AB52" t="b">
         <v>0</v>
       </c>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ict Gap Identification</t>
+          <t>ICT Gap Identification</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>gap analysis, strategic alignment, ICT governance, digital transformation, improvement opportunities</t>
+          <t>gap analysis, strategic alignment, ICT gaps, improvement opportunities, proposed changes</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -8717,15 +8717,19 @@
         </is>
       </c>
       <c r="V53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W53" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X53" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 6/7: </t>
+        </is>
+      </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>keep:4, "ICT Gap Identification":3</t>
+          <t>keep:1, "ICT Gap Identification":6</t>
         </is>
       </c>
       <c r="Z53" t="b">
@@ -8796,12 +8800,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Assesses proposed ICT system changes in hybrid environments for alignment with organisational strategic objectives.</t>
+          <t>Evaluates impact of proposed ICT system changes against the organisation's strategic objectives.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>impact assessment, ICT systems, strategic alignment, change management, proposed changes</t>
+          <t>impact assessment, ICT systems, strategic alignment, change management, performance metrics</t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -8911,7 +8915,7 @@
         </is>
       </c>
       <c r="AH54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
@@ -8919,7 +8923,7 @@
         </is>
       </c>
       <c r="AJ54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -8958,12 +8962,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Researches and tests innovative ideas, applying findings to refine work practices and processes.</t>
+          <t>Investigates new and innovative ideas to continuously improve work practices and processes.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>continuous improvement, process optimisation, ideation techniques, innovative ideas, creative problem solving</t>
+          <t>continuous improvement, process optimisation, ideation techniques, creative problem solving, innovation management</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -9028,12 +9032,12 @@
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Innovative Idea Investigation":1</t>
         </is>
       </c>
       <c r="Z55" t="b">
@@ -9057,7 +9061,7 @@
         </is>
       </c>
       <c r="AH55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
@@ -9065,7 +9069,7 @@
         </is>
       </c>
       <c r="AJ55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -9104,12 +9108,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Analyses numerical data and calculates financial impacts of proposed changes in hybrid environments.</t>
+          <t>Interprets numerical data and applies mathematical calculations to assess the financial implications of introducing changes.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>financial analysis, quantitative modelling, cost‑benefit assessment, Excel, numerical data interpretation</t>
+          <t>financial analysis, quantitative modelling, cost‑benefit assessment, Excel, statistical calculations</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -9179,7 +9183,7 @@
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>keep:6, "Financial Impact Interpretation":1</t>
+          <t>keep:3, "Financial Impact Interpretation":3, "Financial Impact Assessment":1</t>
         </is>
       </c>
       <c r="Z56" t="b">
@@ -9203,7 +9207,7 @@
         </is>
       </c>
       <c r="AH56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
@@ -9211,7 +9215,7 @@
         </is>
       </c>
       <c r="AJ56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -9250,12 +9254,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Assesses policy compliance by documenting standards, targets and implementation approaches within action plans.</t>
+          <t>Details standards, targets and implementation methods in action plans to assess policy compliance.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>regulatory standards, compliance frameworks, risk assessment, policy implementation planning, implementation methods</t>
+          <t>regulatory standards, compliance frameworks, risk assessment, governance risk and compliance, policy implementation planning</t>
         </is>
       </c>
       <c r="J57" t="n">
@@ -9349,7 +9353,7 @@
         </is>
       </c>
       <c r="AH57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
@@ -9357,7 +9361,7 @@
         </is>
       </c>
       <c r="AJ57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -9401,7 +9405,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>action planning, prioritised schedules, timeline management, resource allocation, project scheduling</t>
+          <t>action planning, prioritised schedules, timeline management, resource allocation, critical path</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -9503,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -9522,7 +9526,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Difficulty Evaluation</t>
+          <t>Implementation Difficulty Evaluation</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -9542,12 +9546,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Assesses the difficulty of implementing proposed changes to ICT systems and products.</t>
+          <t>Evaluates the difficulty of implementing proposed changes to ICT systems and products.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ICT systems, change management, difficulty evaluation, implementation complexity, risk analysis</t>
+          <t>ICT systems, change management, implementation difficulty, risk analysis, impact assessment</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -9616,12 +9620,12 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name includes 'Planning' which is not present in the evidence; evidence only involves evaluating difficulty</t>
+          <t>MIS re-refinement: Skill name uses 'Planning' but evidence describes evaluating difficulty, not planning</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>keep:3, "Change Difficulty Assessment/Implementation Difficulty Assessment":3, "Change Implementation Planning":1</t>
+          <t>keep:6, "Change Implementation Planning":1</t>
         </is>
       </c>
       <c r="Z59" t="b">
@@ -9637,7 +9641,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>Skill name includes 'Planning' which is not present in the evidence; evidence only involves evaluating difficulty</t>
+          <t>Skill name uses 'Planning' but evidence describes evaluating difficulty, not planning</t>
         </is>
       </c>
       <c r="AF59" t="b">
@@ -9696,12 +9700,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Prepares concise reports outlining changes, gaps and improvement opportunities for senior staff.</t>
+          <t>Reports on proposed changes, gaps and improvement opportunities to senior staff.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>executive communication, gap analysis, change management, improvement recommendations, proposed changes</t>
+          <t>executive communication, gap analysis, change management, improvement recommendations, business reporting</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -9807,7 +9811,7 @@
         </is>
       </c>
       <c r="AH60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI60" t="inlineStr">
         <is>
@@ -9815,7 +9819,7 @@
         </is>
       </c>
       <c r="AJ60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -9859,7 +9863,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>strategic alignment, SWOT analysis, organisational objectives, gap analysis, current strategic plan</t>
+          <t>strategic alignment, industry benchmarking, SWOT analysis, organisational objectives, gap analysis</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -9977,7 +9981,7 @@
         </is>
       </c>
       <c r="AJ61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -10021,7 +10025,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>decision analysis, analytical reasoning, systematic decision making, risk assessment, scenario modelling</t>
+          <t>decision analysis, analytical reasoning, structured methodologies, risk assessment, scenario modelling</t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -10086,7 +10090,7 @@
         <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr">
@@ -10123,7 +10127,7 @@
         </is>
       </c>
       <c r="AJ62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -10167,7 +10171,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>plain language, jargon translation, stakeholder communication, technical writing, range of personnel</t>
+          <t>plain language, jargon translation, stakeholder communication, technical writing, audience adaptation</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -10269,7 +10273,7 @@
         </is>
       </c>
       <c r="AJ63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -10313,7 +10317,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>legislative compliance, policy analysis, regulatory standards, text analysis, qualitative analysis</t>
+          <t>legislative compliance, policy analysis, regulatory standards, legislative text, qualitative analysis</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -10461,12 +10465,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Evaluates organisational privacy policies against industry standards to ensure compliance in hybrid environments.</t>
+          <t>Reviews organisational privacy policy and procedures to determine compliance with industry standard requirements.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>privacy policy, regulatory standards, compliance, industry standards, data protection</t>
+          <t>privacy policy, regulatory standards, risk assessment, audit, data protection</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -10563,7 +10567,7 @@
         </is>
       </c>
       <c r="AH65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
@@ -10571,7 +10575,7 @@
         </is>
       </c>
       <c r="AJ65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -10610,12 +10614,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Reviews ethical practices and feedback and applies the organisational code of ethics to guide decisions.</t>
+          <t>Reviews ethical work practices and feedback and determines application of the organisational code of ethics according to organisational requirements.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>professional ethics, codes of conduct, compliance, organisational governance, ethical decision making</t>
+          <t>professional ethics, codes of conduct, compliance, organisational governance, ethical frameworks</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -10712,7 +10716,7 @@
         </is>
       </c>
       <c r="AH66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
@@ -10720,7 +10724,7 @@
         </is>
       </c>
       <c r="AJ66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -10764,7 +10768,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>grievance procedures, stakeholder communication, document management, complaint handling, feedback</t>
+          <t>grievance procedures, review processes, stakeholder communication, document management, complaint handling</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -10832,12 +10836,12 @@
         <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Feedback Management":1</t>
         </is>
       </c>
       <c r="Z67" t="b">
@@ -10869,7 +10873,7 @@
         </is>
       </c>
       <c r="AJ67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -10913,7 +10917,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>penetration testing, vulnerability assessment, ISO 27001, CIA triad, industry standards</t>
+          <t>penetration testing, vulnerability assessment, ISO 27001, CIA triad, security controls</t>
         </is>
       </c>
       <c r="J68" t="n">
@@ -11018,7 +11022,7 @@
         </is>
       </c>
       <c r="AJ68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -11062,7 +11066,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>literature review, source integration, technical writing, citation management, range of sources</t>
+          <t>literature review, source integration, technical writing, citation management, knowledge synthesis</t>
         </is>
       </c>
       <c r="J69" t="n">
@@ -11167,7 +11171,7 @@
         </is>
       </c>
       <c r="AJ69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -11206,12 +11210,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Analyses and interprets intellectual property and copyright legislation to ensure organisational compliance.</t>
+          <t>Identifies industry standard intellectual property (IP) and copyright legislation, policies and procedures.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>intellectual property law, copyright legislation, legislative analysis, policy compliance, regulatory analysis</t>
+          <t>intellectual property law, copyright legislation, policy compliance, legal research, regulatory analysis</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -11308,7 +11312,7 @@
         </is>
       </c>
       <c r="AH70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI70" t="inlineStr">
         <is>
@@ -11316,7 +11320,7 @@
         </is>
       </c>
       <c r="AJ70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -11360,7 +11364,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>policy distribution, document dissemination, compliance communication, stakeholder engagement, ethics training</t>
+          <t>document dissemination, compliance communication, stakeholder engagement, internal governance, ethics training</t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -11465,7 +11469,7 @@
         </is>
       </c>
       <c r="AJ71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -11509,7 +11513,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>privacy legislation, policy management, codes of ethics, regulatory documentation, update privacy policy</t>
+          <t>privacy legislation, privacy policy, code of ethics, policy management, regulatory documentation</t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -11581,12 +11585,12 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>keep:2, "Privacy Policy Documentation":5</t>
+          <t>keep:1, "Privacy Policy Documentation":6</t>
         </is>
       </c>
       <c r="Z72" t="b">
@@ -11662,7 +11666,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>policy drafting, grievance management, standard operating procedures, document review, compliance workflows</t>
+          <t>policy drafting, grievance management, standard operating procedures, process documentation, compliance workflows</t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -11767,7 +11771,7 @@
         </is>
       </c>
       <c r="AJ73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -11806,12 +11810,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Sequences and schedules complex activities, monitors progress and coordinates communication to maintain delivery momentum.</t>
+          <t>Sequences and schedules complex activities, monitors implementation and manages communication.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>scheduling, resource allocation, stakeholder communication, project monitoring, sequences</t>
+          <t>scheduling, resource allocation, stakeholder communication, project monitoring, Gantt charts</t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -11912,7 +11916,7 @@
         </is>
       </c>
       <c r="AH74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI74" t="inlineStr">
         <is>
@@ -11920,7 +11924,7 @@
         </is>
       </c>
       <c r="AJ74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -11964,7 +11968,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>compliance, regulatory analysis, policy tracking, legal research, regulations</t>
+          <t>compliance, legislation monitoring, regulatory analysis, policy tracking, legal research</t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -12069,7 +12073,7 @@
         </is>
       </c>
       <c r="AJ75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -12113,7 +12117,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>cyber security, data protection, information governance, privacy compliance, digital technologies</t>
+          <t>cyber security, data protection, information governance, privacy compliance, access control</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -12181,12 +12185,12 @@
         <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>keep:5, "Digital Information Security":2</t>
+          <t>keep:3, "Digital Information Handling":3, "Digital Information Security":1</t>
         </is>
       </c>
       <c r="Z76" t="b">
@@ -12218,7 +12222,7 @@
         </is>
       </c>
       <c r="AJ76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -12262,7 +12266,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>policy dissemination, stakeholder engagement, communication protocols, distribution, organisational compliance</t>
+          <t>policy dissemination, stakeholder engagement, communication protocols, policy distribution, change management</t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -12334,12 +12338,12 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>keep:2, "Policy Distribution":5</t>
+          <t>keep:1, "Policy Distribution":6</t>
         </is>
       </c>
       <c r="Z77" t="b">
@@ -12419,7 +12423,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>active listening, questioning techniques, verbal communication, dialogue facilitation, interpersonal communication</t>
+          <t>active listening, questioning techniques, stakeholder engagement, dialogue facilitation, interpersonal communication</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -12487,7 +12491,7 @@
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>0.95</v>
+        <v>0.9528571428571428</v>
       </c>
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr">
@@ -12524,7 +12528,7 @@
         </is>
       </c>
       <c r="AJ78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -12568,7 +12572,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>distributed ledger, node deployment, consensus configuration, Ethereum, blockchain platform</t>
+          <t>distributed ledger, node deployment, consensus configuration, Ethereum, Docker</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -12643,12 +12647,12 @@
         <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Blockchain Platform Installation":1</t>
         </is>
       </c>
       <c r="Z79" t="b">
@@ -12680,7 +12684,7 @@
         </is>
       </c>
       <c r="AJ79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -12724,7 +12728,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>anomaly detection, blockchain analytics, smart contract debugging, cryptographic forensics, resolution</t>
+          <t>anomaly detection, blockchain analytics, smart contract debugging, cryptographic forensics, pattern recognition</t>
         </is>
       </c>
       <c r="J80" t="n">
@@ -12799,16 +12803,16 @@
         <v>1</v>
       </c>
       <c r="W80" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>keep:0, "Blockchain Anomaly Resolution":7</t>
+          <t>keep:1, "Blockchain Anomaly Resolution":4, "Blockchain Anomaly Problem Solving":2</t>
         </is>
       </c>
       <c r="Z80" t="b">
@@ -12820,7 +12824,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Foundation Skill describes problem‑solving capability already embedded in other skills and PCs; it does not represent a distinct task for this unit</t>
+          <t>Foundation Skill describes problem‑solving capability already embedded in other skills and PCs; it is a work style rather than a distinct task</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -12844,7 +12848,7 @@
         </is>
       </c>
       <c r="AJ80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -12883,12 +12887,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Defines blockchain objectives and requirements aligned with organisational needs in hybrid environments.</t>
+          <t>Establishes blockchain objectives, purpose and requirements according to organisational needs.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>distributed ledger, blockchain objectives, stakeholder analysis, smart contract design, governance frameworks</t>
+          <t>distributed ledger, use‑case definition, stakeholder analysis, smart contract design, governance frameworks</t>
         </is>
       </c>
       <c r="J81" t="n">
@@ -12992,7 +12996,7 @@
         </is>
       </c>
       <c r="AH81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI81" t="inlineStr">
         <is>
@@ -13000,7 +13004,7 @@
         </is>
       </c>
       <c r="AJ81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -13044,7 +13048,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>blockchain, distributed ledger, consensus algorithms, consensus portal, Byzantine fault tolerance</t>
+          <t>blockchain, distributed ledger, consensus algorithms, peer‑to‑peer networking, Byzantine fault tolerance</t>
         </is>
       </c>
       <c r="J82" t="n">
@@ -13156,7 +13160,7 @@
         </is>
       </c>
       <c r="AJ82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -13200,7 +13204,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>technical specifications, design standards, engineering documentation, organisational requirements, design documentation</t>
+          <t>technical specifications, design standards, engineering documentation, organisational requirements</t>
         </is>
       </c>
       <c r="J83" t="n">
@@ -13312,7 +13316,7 @@
         </is>
       </c>
       <c r="AJ83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -13356,7 +13360,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>record‑keeping, feedback loops, compliance, documentation submission, workflow approvals</t>
+          <t>record‑keeping, feedback loops, compliance, workflow approvals, electronic filing</t>
         </is>
       </c>
       <c r="J84" t="n">
@@ -13468,7 +13472,7 @@
         </is>
       </c>
       <c r="AJ84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -13507,12 +13511,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Designs integration workflows by mapping data flows and configuring tools to meet organisational needs.</t>
+          <t>Designs integration workflow according to organisational need.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>systems integration, workflow orchestration, process automation, ETL, design integration workflow</t>
+          <t>systems integration, workflow orchestration, process automation, ETL, API middleware</t>
         </is>
       </c>
       <c r="J85" t="n">
@@ -13616,7 +13620,7 @@
         </is>
       </c>
       <c r="AH85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI85" t="inlineStr">
         <is>
@@ -13624,7 +13628,7 @@
         </is>
       </c>
       <c r="AJ85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -13668,7 +13672,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>preventive maintenance, asset management, CMMS, work order scheduling, maintenance schedule</t>
+          <t>preventive maintenance, asset management, CMMS, work order scheduling, reliability engineering</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -13780,7 +13784,7 @@
         </is>
       </c>
       <c r="AJ86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -13824,7 +13828,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>preventive maintenance, test procedures, equipment inspection, maintenance tests, reliability testing</t>
+          <t>preventive maintenance, maintenance tests, equipment inspection, reliability testing, compliance standards</t>
         </is>
       </c>
       <c r="J87" t="n">
@@ -13899,16 +13903,16 @@
         <v>1</v>
       </c>
       <c r="W87" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>keep:0, "Maintenance Testing":7</t>
+          <t>keep:2, "Maintenance Testing":5</t>
         </is>
       </c>
       <c r="Z87" t="b">
@@ -13979,12 +13983,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Selects and configures security platforms for blockchain solutions based on risk assessments.</t>
+          <t>Selects security platforms for blockchain solutions based on risk assessments.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>blockchain, security architecture, platform selection, cryptography, risk assessment</t>
+          <t>blockchain, security architecture, platform evaluation, cryptography, risk assessment</t>
         </is>
       </c>
       <c r="J88" t="n">
@@ -14088,7 +14092,7 @@
         </is>
       </c>
       <c r="AH88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
@@ -14096,7 +14100,7 @@
         </is>
       </c>
       <c r="AJ88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -14135,12 +14139,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Executes smart commands on the required blockchain platform in accordance with the solution specifications.</t>
+          <t>Executes smart command in required platform according to blockchain solution.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>blockchain, Ethereum, Solidity, smart contract, Web3</t>
+          <t>blockchain, Ethereum, Solidity, decentralised applications, Web3</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -14252,7 +14256,7 @@
         </is>
       </c>
       <c r="AJ89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -14296,7 +14300,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>blockchain, smart contracts, Solidity, debugging, performance scaling</t>
+          <t>blockchain, smart contracts, Solidity, distributed ledger, performance scaling</t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -14408,7 +14412,7 @@
         </is>
       </c>
       <c r="AJ90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -14447,12 +14451,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Tests and evaluates solutions against organisational requirements to confirm suitability.</t>
+          <t>Tests solutions against organisational requirements to confirm suitability.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>benchmarking, load testing, service level agreements, performance metrics, solution</t>
+          <t>benchmarking, requirements compliance, load testing, service level agreements, performance metrics</t>
         </is>
       </c>
       <c r="J91" t="n">
@@ -14556,7 +14560,7 @@
         </is>
       </c>
       <c r="AH91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
@@ -14564,7 +14568,7 @@
         </is>
       </c>
       <c r="AJ91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -14608,7 +14612,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>stakeholder engagement, requirements gathering, industry terminology, oral communication, active listening</t>
+          <t>stakeholder engagement, requirements gathering, industry terminology, verbal communication, active listening</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -14720,7 +14724,7 @@
         </is>
       </c>
       <c r="AJ92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -14759,12 +14763,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Analyses hybrid environments to identify organisational use cases aligned with business needs.</t>
+          <t>Identifies organisational use case according to organisational needs.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>requirements analysis, business analysis, stakeholder mapping, use‑case modelling, use case identification</t>
+          <t>requirements analysis, business analysis, stakeholder mapping, use‑case modelling, functional requirements</t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -14868,7 +14872,7 @@
         </is>
       </c>
       <c r="AH93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI93" t="inlineStr">
         <is>
@@ -14876,7 +14880,7 @@
         </is>
       </c>
       <c r="AJ93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -14915,12 +14919,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Ingests data logs into analytic platform according to user instructions.</t>
+          <t>Ingests data logs into analytics platforms as instructed to support monitoring and analysis.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>data ingestion, log analytics, ETL pipelines, analytic platform, user instructions</t>
+          <t>data ingestion, log analytics, ETL pipelines, analytic platform, data logs</t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -15035,7 +15039,7 @@
         </is>
       </c>
       <c r="AH94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI94" t="inlineStr">
         <is>
@@ -15087,7 +15091,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>regulatory compliance, legislative requirements, policy analysis, threat intelligence, risk assessment</t>
+          <t>regulatory compliance, legislation, policy analysis, threat intelligence, risk assessment</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -15206,7 +15210,7 @@
         </is>
       </c>
       <c r="AJ95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -15250,7 +15254,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>data validation, anomaly detection, data quality, data discrepancy, data auditing</t>
+          <t>data validation, anomaly detection, data quality, data auditing, profiling</t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -15365,7 +15369,7 @@
         </is>
       </c>
       <c r="AJ96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -15409,7 +15413,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>log analysis, data ingestion, dataset creation, data governance, ETL processes</t>
+          <t>log analysis, data ingestion, dataset creation, security monitoring, data governance</t>
         </is>
       </c>
       <c r="J97" t="n">
@@ -15487,16 +15491,16 @@
         <v>1</v>
       </c>
       <c r="W97" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>keep:4, "Dataset Creation":3</t>
+          <t>keep:1, "Dataset Creation":6</t>
         </is>
       </c>
       <c r="Z97" t="b">
@@ -15576,7 +15580,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>type I error, false positives, false negatives, anomaly detection, precision‑recall analysis</t>
+          <t>false positives, false negatives, type I error, anomaly detection, precision‑recall analysis</t>
         </is>
       </c>
       <c r="J98" t="n">
@@ -15743,7 +15747,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>incident reporting, report writing, documentation, findings, safety management</t>
+          <t>incident reporting, root‑cause analysis, procedural compliance, report writing, safety management</t>
         </is>
       </c>
       <c r="J99" t="n">
@@ -15817,7 +15821,7 @@
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X99" t="inlineStr"/>
       <c r="Y99" t="inlineStr">
@@ -15854,7 +15858,7 @@
         </is>
       </c>
       <c r="AJ99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -15898,7 +15902,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>risk management, lessons learned, action planning, mitigation planning, recommendations</t>
+          <t>risk management, lessons learned, action planning, stakeholder engagement, mitigation planning</t>
         </is>
       </c>
       <c r="J100" t="n">
@@ -16017,7 +16021,7 @@
         </is>
       </c>
       <c r="AJ100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -16061,7 +16065,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>risk assessment, threat modelling, impact evaluation, likelihood of occurrence, risk matrices</t>
+          <t>risk assessment, threat modelling, likelihood of occurrence, impact evaluation, cyber threats</t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -16224,7 +16228,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>cyber security, network security, asset inventories, security equipment, data sources</t>
+          <t>cyber security, network security, asset inventories, IDS, firewalls</t>
         </is>
       </c>
       <c r="J102" t="n">
@@ -16339,7 +16343,7 @@
         </is>
       </c>
       <c r="AJ102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -16378,12 +16382,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Imports security logs into analytics platforms.</t>
+          <t>Ingests data logs into an analytic platform according to user instructions.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>log aggregation, SIEM, data ingestion, security analytics, user instructions</t>
+          <t>log aggregation, SIEM, data ingestion, security analytics, ELK stack</t>
         </is>
       </c>
       <c r="J103" t="n">
@@ -16502,7 +16506,7 @@
         </is>
       </c>
       <c r="AJ103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -16546,7 +16550,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>stakeholder engagement, threat intelligence, risk reporting, findings communication, cyber security communication</t>
+          <t>stakeholder engagement, threat intelligence, risk reporting, data briefings, cyber security communication</t>
         </is>
       </c>
       <c r="J104" t="n">
@@ -16661,7 +16665,7 @@
         </is>
       </c>
       <c r="AJ104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -16700,12 +16704,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Collects and structures alerts, logs and event data in accordance with organisational data policies.</t>
+          <t>Collects alerts, logs and event data and creates a dataset in accordance with organisational data policies.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>threat intelligence, log analysis, SIEM, dataset, security monitoring</t>
+          <t>threat intelligence, log analysis, SIEM, incident response, security monitoring</t>
         </is>
       </c>
       <c r="J105" t="n">
@@ -16816,7 +16820,7 @@
         </is>
       </c>
       <c r="AH105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI105" t="inlineStr">
         <is>
@@ -16824,7 +16828,7 @@
         </is>
       </c>
       <c r="AJ105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -16868,7 +16872,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>outlier analysis, root‑cause analysis, statistical process control, monitoring and diagnostics, anomaly detection</t>
+          <t>outlier analysis, root‑cause analysis, statistical process control, monitoring and diagnostics</t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -16940,12 +16944,12 @@
         <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>keep:6, "Anomaly Troubleshooting":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z106" t="b">
@@ -16977,7 +16981,7 @@
         </is>
       </c>
       <c r="AJ106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -17016,12 +17020,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Implements enhanced protection plan requirements and asset management processes to safeguard assets.</t>
+          <t>Implements additional protection plan requirements and asset management processes to safeguard assets.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>asset tracking, risk mitigation, protection plans, asset management processes, implementation</t>
+          <t>asset tracking, risk mitigation, protection plans, maintenance scheduling, capital budgeting</t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -17122,7 +17126,7 @@
         </is>
       </c>
       <c r="AH107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI107" t="inlineStr">
         <is>
@@ -17130,7 +17134,7 @@
         </is>
       </c>
       <c r="AJ107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -17169,12 +17173,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Researches the organisation’s need for critical infrastructure protection and documents findings in accordance with organisational requirements.</t>
+          <t>Researches the organisation's need for critical infrastructure protection and documents findings according to organisational requirements.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>critical infrastructure protection, infrastructure protection, risk assessment, threat modelling, resilience analysis</t>
+          <t>infrastructure protection, risk assessment, threat modelling, resilience analysis, policy compliance</t>
         </is>
       </c>
       <c r="J108" t="n">
@@ -17283,7 +17287,7 @@
         </is>
       </c>
       <c r="AJ108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -17327,7 +17331,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>disaster recovery, backup software, data retention policies, storage replication, backup execution</t>
+          <t>disaster recovery, backup software, data retention policies, storage replication, ICT compliance</t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -17436,7 +17440,7 @@
         </is>
       </c>
       <c r="AJ109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -17480,7 +17484,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>endpoint protection, device hardening, encryption, mobile device management, technical requirements</t>
+          <t>endpoint protection, device hardening, security policies, encryption, mobile device management</t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -17589,7 +17593,7 @@
         </is>
       </c>
       <c r="AJ110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -17628,12 +17632,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Submits the protection plan to required personnel, seeks feedback, and responds to that feedback.</t>
+          <t>Submits protection plan to required personnel and seeks and responds to feedback.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>stakeholder communication, feedback loops, response management, submit protection plan, compliance reporting</t>
+          <t>stakeholder communication, feedback loops, response management, plan documentation, compliance reporting</t>
         </is>
       </c>
       <c r="J111" t="n">
@@ -17742,7 +17746,7 @@
         </is>
       </c>
       <c r="AJ111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -17781,12 +17785,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Implements network segmentation to isolate security zones in line with approved protection plans.</t>
+          <t>Implements network segmentation according to the protection plan and technical requirements.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>VLANs, firewall policies, micro‑segmentation, network segmentation, zero‑trust architecture</t>
+          <t>VLANs, firewall policies, micro‑segmentation, zero‑trust architecture, network security zones</t>
         </is>
       </c>
       <c r="J112" t="n">
@@ -17887,7 +17891,7 @@
         </is>
       </c>
       <c r="AH112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI112" t="inlineStr">
         <is>
@@ -17895,7 +17899,7 @@
         </is>
       </c>
       <c r="AJ112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -17939,7 +17943,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>operational planning, performance monitoring, resource allocation, timeline management, project coordination</t>
+          <t>operational planning, performance monitoring, resource allocation, timeline management, Gantt charts</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -18028,7 +18032,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>FS describes work style (planning and coordinating) rather than a distinct task; capability already embedded in strategy development and implementation PCs</t>
+          <t>FS describes work style (planning and coordinating) rather than a distinct task; capability already embedded in strategy development PCs</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -18052,7 +18056,7 @@
         </is>
       </c>
       <c r="AJ113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -18091,12 +18095,12 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Evaluates current critical infrastructure protection plans to identify gaps and recommend improvements.</t>
+          <t>Analyses existing critical infrastructure protection plan to identify gaps and recommend improvements.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>critical infrastructure, protection plan, risk assessment, cyber security resilience, vulnerability analysis</t>
+          <t>critical infrastructure, risk assessment, cyber security resilience, ISO 27001, vulnerability analysis</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -18168,12 +18172,12 @@
         <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>0.95</v>
+        <v>0.9428571428571428</v>
       </c>
       <c r="X114" t="inlineStr"/>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>keep:5, "Critical Infrastructure Protection Analysis":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z114" t="b">
@@ -18197,7 +18201,7 @@
         </is>
       </c>
       <c r="AH114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
@@ -18205,7 +18209,7 @@
         </is>
       </c>
       <c r="AJ114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -18249,7 +18253,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>critical infrastructure, protection plan, security policy compliance, business continuity planning, incident response frameworks</t>
+          <t>critical infrastructure, risk assessment, security policy compliance, business continuity planning, incident response frameworks</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -18358,7 +18362,7 @@
         </is>
       </c>
       <c r="AJ115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -18397,7 +18401,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Tests deployment of protection plan in line with organisational policies and procedures.</t>
+          <t>Tests deployment of protection plan according to organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -18554,12 +18558,12 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Obtains and analyses results according to organisational policies and procedures.</t>
+          <t>Collects and analyses test results according to organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>data interpretation, performance metrics, compliance reporting, results analysis, business intelligence</t>
+          <t>data interpretation, performance metrics, compliance reporting, organisational standards, business intelligence</t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -18668,7 +18672,7 @@
         </is>
       </c>
       <c r="AJ117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -18687,7 +18691,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Risk Evaluation</t>
+          <t>Risk Assessment Evaluation</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -18707,12 +18711,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Determines protection, vulnerability, risk and mitigation levels in line with organisational requirements.</t>
+          <t>Evaluates protection, vulnerability, risk and mitigation levels aligned with organisational requirements.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>vulnerability analysis, mitigation planning, risk matrices, protection, security governance</t>
+          <t>vulnerability analysis, mitigation planning, risk matrices, security governance, ISO 27001 compliance</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -18781,19 +18785,15 @@
         </is>
       </c>
       <c r="V118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W118" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 4/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>keep:3, "Risk Evaluation":4</t>
+          <t>keep:4, "Risk Assessment":2, "Risk Evaluation":1</t>
         </is>
       </c>
       <c r="Z118" t="b">
@@ -18825,7 +18825,7 @@
         </is>
       </c>
       <c r="AJ118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -18864,12 +18864,12 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Installs and configures software updates in line with documented technical specifications.</t>
+          <t>Installs software updates in line with documented technical specifications.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>patch management, vulnerability remediation, update deployment, configuration management, software patches</t>
+          <t>patch management, vulnerability remediation, update deployment, configuration management, WSUS</t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -18970,7 +18970,7 @@
         </is>
       </c>
       <c r="AH119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI119" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         </is>
       </c>
       <c r="AJ119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -19022,7 +19022,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>technical writing, process documentation, standard operating procedures, document formatting, structure layout</t>
+          <t>technical writing, process documentation, standard operating procedures, document formatting</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -19131,7 +19131,7 @@
         </is>
       </c>
       <c r="AJ120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -19170,12 +19170,12 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Identifies and categorises data types to inform security architecture requirements.</t>
+          <t>Establishes all data types to be included in security architecture.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>information security, data inventories, classification schemes, data types, security architecture</t>
+          <t>information security, data inventories, classification schemes, confidentiality levels, security architecture</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -19286,7 +19286,7 @@
         </is>
       </c>
       <c r="AH121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI121" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         </is>
       </c>
       <c r="AJ121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>documentation, stakeholder communication, feedback loops, response, internal reporting</t>
+          <t>documentation, stakeholder communication, feedback loops, record‑keeping, internal reporting</t>
         </is>
       </c>
       <c r="J122" t="n">
@@ -19453,7 +19453,7 @@
         </is>
       </c>
       <c r="AJ122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -19492,12 +19492,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Researches and documents industry‑standard design methodologies to inform security architecture planning.</t>
+          <t>Researches industry‑standard design methodologies to inform security architecture planning.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>security architecture, design methodologies, industry standards, security frameworks, methodology</t>
+          <t>security architecture, design methodologies, industry standards, security frameworks, risk assessment</t>
         </is>
       </c>
       <c r="J123" t="n">
@@ -19600,7 +19600,7 @@
         </is>
       </c>
       <c r="AH123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI123" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         </is>
       </c>
       <c r="AJ123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -19627,7 +19627,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Problem Solving in Security</t>
+          <t>Contextual Anomaly Identification</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -19652,7 +19652,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>anomaly detection, threat analysis, pattern recognition, situational awareness, problem solving</t>
+          <t>anomaly detection, pattern recognition, situational awareness, context analysis, subtle deviations</t>
         </is>
       </c>
       <c r="J124" t="n">
@@ -19734,16 +19734,16 @@
         <v>1</v>
       </c>
       <c r="W124" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>keep:0, "Security Contextual Problem Solving":3, "Contextual Anomaly Identification":2, "Contextual Anomaly Detection/Security Anomaly Detection":2</t>
+          <t>keep:0, "Contextual Anomaly Identification/Security Anomaly Identification":6, "Security Contextual Problem Solving":1</t>
         </is>
       </c>
       <c r="Z124" t="b">
@@ -19751,13 +19751,9 @@
       </c>
       <c r="AA124" t="inlineStr"/>
       <c r="AB124" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Foundation Skill describes a work style (problem solving) that is already embedded in multiple performance criteria and other skills</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC124" t="inlineStr"/>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
@@ -19818,12 +19814,12 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Documents and validates security architecture findings with relevant personnel.</t>
+          <t>Documents security architecture findings and confirms them with relevant personnel.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>security architecture, risk assessment, compliance frameworks, ISO 27001, documentation</t>
+          <t>security architecture, security requirements, documentation, compliance frameworks, ISO 27001</t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -19910,7 +19906,7 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>keep:0, "Security Requirements Documentation/Security Findings Documentation":7</t>
+          <t>keep:0, "Security Requirements Documentation":7</t>
         </is>
       </c>
       <c r="Z125" t="b">
@@ -19934,7 +19930,7 @@
         </is>
       </c>
       <c r="AH125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI125" t="inlineStr">
         <is>
@@ -19981,12 +19977,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Prepares and delivers documented security architecture presentations for stakeholder engagement.</t>
+          <t>Delivers documented security architecture presentations for stakeholder engagement.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>information security, enterprise architecture, security frameworks, technical presentations, document form</t>
+          <t>information security, enterprise architecture, risk assessment, security frameworks, technical presentations</t>
         </is>
       </c>
       <c r="J126" t="n">
@@ -20093,7 +20089,7 @@
         </is>
       </c>
       <c r="AH126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI126" t="inlineStr">
         <is>
@@ -20101,7 +20097,7 @@
         </is>
       </c>
       <c r="AJ126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -20140,12 +20136,12 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Demonstrates security design using major industry‑standard design methodologies.</t>
+          <t>Demonstrates security design utilising major industry‑standard design methodologies.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>security architecture, threat modelling, NIST framework, ISO 27001, validation</t>
+          <t>security architecture, threat modelling, NIST framework, ISO 27001, risk assessment</t>
         </is>
       </c>
       <c r="J127" t="n">
@@ -20260,7 +20256,7 @@
         </is>
       </c>
       <c r="AJ127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -20299,12 +20295,12 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Assesses assets to determine required security levels, perimeters, features and protection modes.</t>
+          <t>Determines required security level, perimeters, features and protection mode.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>risk assessment, access control, security architecture, security level, security mode</t>
+          <t>risk assessment, access control, security architecture, perimeter security, security policy</t>
         </is>
       </c>
       <c r="J128" t="n">
@@ -20415,7 +20411,7 @@
         </is>
       </c>
       <c r="AH128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI128" t="inlineStr">
         <is>
@@ -20423,7 +20419,7 @@
         </is>
       </c>
       <c r="AJ128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -20467,7 +20463,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>cyber security governance, risk assessment, phased implementation, performance monitoring, operational detail</t>
+          <t>cyber security governance, risk assessment, phased implementation, performance monitoring, project scheduling tools</t>
         </is>
       </c>
       <c r="J129" t="n">
@@ -20549,7 +20545,7 @@
         <v>0</v>
       </c>
       <c r="W129" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X129" t="inlineStr"/>
       <c r="Y129" t="inlineStr">
@@ -20590,7 +20586,7 @@
         </is>
       </c>
       <c r="AJ129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -20634,7 +20630,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>risk assessment, security architecture, compliance standards, vulnerability analysis, operation and infrastructure</t>
+          <t>risk assessment, threat modelling, security architecture, compliance standards, vulnerability analysis</t>
         </is>
       </c>
       <c r="J130" t="n">
@@ -20708,7 +20704,7 @@
         <v>0</v>
       </c>
       <c r="W130" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X130" t="inlineStr"/>
       <c r="Y130" t="inlineStr">
@@ -20745,7 +20741,7 @@
         </is>
       </c>
       <c r="AJ130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -20784,12 +20780,12 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Designs and documents security solutions aligned with organisational standards and requirements.</t>
+          <t>Designs and documents security solutions according to organisational requirements.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>cyber security architecture, security solution, design, solution documentation, threat modelling</t>
+          <t>cyber security architecture, risk assessment, security compliance, solution documentation, threat modelling</t>
         </is>
       </c>
       <c r="J131" t="n">
@@ -20900,7 +20896,7 @@
         </is>
       </c>
       <c r="AH131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI131" t="inlineStr">
         <is>
@@ -20908,7 +20904,7 @@
         </is>
       </c>
       <c r="AJ131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -20952,7 +20948,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>technical writing, documentation standards, findings, solutions, knowledge management</t>
+          <t>technical writing, documentation standards, reporting and analysis, knowledge management</t>
         </is>
       </c>
       <c r="J132" t="n">
@@ -21071,7 +21067,7 @@
         </is>
       </c>
       <c r="AJ132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -21115,7 +21111,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>technical documentation, manufacturer manuals, job requirement analysis, reading, interpretation</t>
+          <t>technical documentation, manufacturer manuals, job requirement analysis, engineering drawings, documentation reading</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -21277,12 +21273,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Makes independent strategic decisions to align actions with organisational objectives and improve performance.</t>
+          <t>Works autonomously, making high‑level decisions to achieve and improve organisational goals.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>autonomy, strategic decision‑making, self‑management, autonomous decision‑making, organisational performance</t>
+          <t>autonomy, strategic decision‑making, self‑management, leadership, organisational performance</t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -21410,7 +21406,7 @@
         </is>
       </c>
       <c r="AH134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI134" t="inlineStr">
         <is>
@@ -21418,7 +21414,7 @@
         </is>
       </c>
       <c r="AJ134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -21457,12 +21453,12 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Creates and protects forensic evidence collection procedures to preserve data during incident response.</t>
+          <t>Develops procedures for collecting and protecting forensic evidence during incident response.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>chain of custody, evidence preservation, incident response, forensic evidence, crime scene documentation</t>
+          <t>chain of custody, evidence preservation, incident response, digital forensics tools, crime scene documentation</t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -21590,7 +21586,7 @@
         </is>
       </c>
       <c r="AJ135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -21629,12 +21625,12 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Prepares detailed incident reports documenting response actions against task requirements.</t>
+          <t>Documents security incident response and actions according to task requirements.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>security incident response, incident reporting, document incident response, SIEM, compliance documentation</t>
+          <t>security incident response, incident reporting, ITIL, SIEM, compliance documentation</t>
         </is>
       </c>
       <c r="J136" t="n">
@@ -21750,7 +21746,7 @@
         </is>
       </c>
       <c r="AH136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI136" t="inlineStr">
         <is>
@@ -21758,7 +21754,7 @@
         </is>
       </c>
       <c r="AJ136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -21777,7 +21773,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Incident Response Evaluation</t>
+          <t>Incident Response Plan Evaluation</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -21802,7 +21798,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>security operations, post‑incident analysis, efficiency metrics, incident response evaluation, SOC tools</t>
+          <t>incident response plan, post‑incident analysis, efficiency metrics, response plan documentation, security operations</t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -21890,15 +21886,19 @@
         </is>
       </c>
       <c r="V137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W137" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X137" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/7: </t>
+        </is>
+      </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>keep:5, "Incident Response Plan Evaluation":2</t>
+          <t>keep:2, "Incident Response Plan Evaluation":5</t>
         </is>
       </c>
       <c r="Z137" t="b">
@@ -21974,7 +21974,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>incident response, incident handling, incident response plan, playbook development, risk management</t>
+          <t>cyber security, incident handling, NIST framework, playbook development, risk management</t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="AJ138" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -22141,12 +22141,12 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Documents incident response team roles and services to support coordinated response.</t>
+          <t>Identifies and documents incident response team services according to organisational requirements.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>incident response, service documentation, team coordination, organisational compliance, incident response team</t>
+          <t>incident response, service documentation, team coordination, organisational compliance, ticketing systems</t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -22233,7 +22233,7 @@
         <v>0</v>
       </c>
       <c r="W139" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr">
@@ -22262,7 +22262,7 @@
         </is>
       </c>
       <c r="AH139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI139" t="inlineStr">
         <is>
@@ -22270,7 +22270,7 @@
         </is>
       </c>
       <c r="AJ139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -22289,7 +22289,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Incident Response Exercise Development</t>
+          <t>Incident Response Exercise Design</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -22309,12 +22309,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Creates incident response exercises, red‑team activities, and associated staffing and training requirements.</t>
+          <t>Creates incident response exercises, red‑team activities, and defines staffing and training requirements.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>adversary simulation, incident response planning, red‑teaming activities, security training programmes, MITRE ATT&amp;CK framework</t>
+          <t>incident response exercises, red-teaming activities, incident response planning, security training programmes, MITRE ATT&amp;CK framework</t>
         </is>
       </c>
       <c r="J140" t="n">
@@ -22409,12 +22409,12 @@
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name implies delivering training, but evidence is about creating exercises and training requirements</t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>keep:0, "Incident Response Training":4, "Incident Response Exercise Design":3</t>
+          <t>keep:0, "Incident Response Exercise Design":5, "Incident Response Training":2</t>
         </is>
       </c>
       <c r="Z140" t="b">
@@ -22426,13 +22426,9 @@
       </c>
       <c r="AC140" t="inlineStr"/>
       <c r="AD140" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE140" t="inlineStr">
-        <is>
-          <t>Skill name implies delivering training, but evidence is about creating exercises and training requirements</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AE140" t="inlineStr"/>
       <c r="AF140" t="b">
         <v>0</v>
       </c>
@@ -22641,7 +22637,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Risk Analysis</t>
+          <t>Technical Data Interpretation</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -22666,7 +22662,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>quantitative analysis, technical data interpretation, risk assessment, document numerical, system modelling</t>
+          <t>technical data interpretation, quantitative analysis, system modelling, data documentation, numerical data</t>
         </is>
       </c>
       <c r="J142" t="n">
@@ -22758,15 +22754,19 @@
         </is>
       </c>
       <c r="V142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W142" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="X142" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 6/7: </t>
+        </is>
+      </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>keep:6, "Technical Data Interpretation":1</t>
+          <t>keep:1, "Technical Data Interpretation/Data Interpretation":6</t>
         </is>
       </c>
       <c r="Z142" t="b">
@@ -22846,7 +22846,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>incident response, security operations centres, SIEM, playbook execution, security incident handling</t>
+          <t>incident response, security operations centres, SIEM, playbook execution, forensic analysis</t>
         </is>
       </c>
       <c r="J143" t="n">
@@ -22941,7 +22941,7 @@
         <v>0</v>
       </c>
       <c r="W143" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X143" t="inlineStr"/>
       <c r="Y143" t="inlineStr">
@@ -22978,7 +22978,7 @@
         </is>
       </c>
       <c r="AJ143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -23022,7 +23022,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>incident management, policy development, governance, compliance, ISO 27001</t>
+          <t>incident management, risk assessment, governance, compliance, ISO 27001</t>
         </is>
       </c>
       <c r="J144" t="n">
@@ -23154,7 +23154,7 @@
         </is>
       </c>
       <c r="AJ144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -23193,12 +23193,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Analyses and records numerical system data to inform technical decision‑making.</t>
+          <t>Interprets, analyses and documents numerical and technical system data</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>quantitative analysis, technical system data, measurement instrumentation, data documentation, numerical interpretation</t>
+          <t>quantitative analysis, technical system data, measurement instrumentation, data documentation, engineering diagnostics</t>
         </is>
       </c>
       <c r="J145" t="n">
@@ -23326,7 +23326,7 @@
         </is>
       </c>
       <c r="AH145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI145" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         </is>
       </c>
       <c r="AJ145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -23378,7 +23378,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>business continuity, risk assessment, impact analysis, disaster recovery, evaluation</t>
+          <t>business continuity, risk assessment, impact analysis, disaster recovery, resilience planning</t>
         </is>
       </c>
       <c r="J146" t="n">
@@ -23499,7 +23499,7 @@
         </is>
       </c>
       <c r="AJ146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -23538,12 +23538,12 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Develops and implements strategies to ensure organisational policies, procedures and regulatory requirements are met.</t>
+          <t>Develops and implements strategies to ensure organisational policies, procedures and regulatory requirements are met</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>regulatory compliance, policy enforcement, risk management, governance, implementation</t>
+          <t>regulatory compliance, policy enforcement, risk management, governance, audit</t>
         </is>
       </c>
       <c r="J147" t="n">
@@ -23644,7 +23644,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>FS describes work style (ensuring compliance) rather than a distinct unit task; capability is implicit in other skills like Risk Analysis and Business Continuity Evaluation</t>
+          <t>FS describes work style/strategic compliance activity already implicit in other skills and not a distinct task for this unit</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -23668,7 +23668,7 @@
         </is>
       </c>
       <c r="AJ147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -23707,12 +23707,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Develops contingency plans by identifying threats.</t>
+          <t>Develops contingency plans that identify threats.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>contingency plan, risk assessment, business continuity, threat identification, mitigation strategies</t>
+          <t>risk assessment, business continuity, threat identification, mitigation strategies, scenario analysis</t>
         </is>
       </c>
       <c r="J148" t="n">
@@ -23841,7 +23841,7 @@
         </is>
       </c>
       <c r="AJ148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -23880,12 +23880,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Evaluates prevention and recovery options for compliance and cost effectiveness.</t>
+          <t>Evaluates prevention and recovery options against business specifications and cost constraints.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>cost‑benefit analysis, budgeting, risk assessment, business case evaluation, cost constraints</t>
+          <t>cost‑benefit analysis, budgeting, risk assessment, business case evaluation, financial modelling</t>
         </is>
       </c>
       <c r="J149" t="n">
@@ -23998,7 +23998,7 @@
         </is>
       </c>
       <c r="AH149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI149" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         </is>
       </c>
       <c r="AJ149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -24045,7 +24045,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Develops comprehensive disaster recovery plans detailing procedures, resources and recovery timeframes.</t>
+          <t>Develops disaster recovery plan.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -24134,7 +24134,7 @@
         <v>0</v>
       </c>
       <c r="W150" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X150" t="inlineStr"/>
       <c r="Y150" t="inlineStr">
@@ -24167,7 +24167,7 @@
         </is>
       </c>
       <c r="AH150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI150" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>compliance, risk management, standard operating procedures, regulatory guidance, safeguards</t>
+          <t>compliance, risk management, standard operating procedures, regulatory guidance, audit</t>
         </is>
       </c>
       <c r="J151" t="n">
@@ -24340,7 +24340,7 @@
         </is>
       </c>
       <c r="AJ151" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -24384,7 +24384,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>quantitative analysis, financial modelling, technical data interpretation, statistical methods, business data analysis</t>
+          <t>quantitative analysis, financial modelling, technical data interpretation, data reporting, business data analysis</t>
         </is>
       </c>
       <c r="J152" t="n">
@@ -24548,12 +24548,12 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Formulates prevention and recovery strategies to strengthen system resilience.</t>
+          <t>Formulates prevention and recovery strategy to strengthen system resilience.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>risk assessment, mitigation planning, prevention strategy, recovery planning, scenario analysis</t>
+          <t>risk assessment, mitigation planning, contingency strategies, recovery planning, scenario analysis</t>
         </is>
       </c>
       <c r="J153" t="n">
@@ -24678,7 +24678,7 @@
         </is>
       </c>
       <c r="AJ153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -24722,7 +24722,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>data analysis, feedback loops, process improvement, root‑cause analysis, problem solving</t>
+          <t>data analysis, feedback loops, process improvement, root‑cause analysis, continuous improvement</t>
         </is>
       </c>
       <c r="J154" t="n">
@@ -24810,7 +24810,7 @@
         <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>0.95</v>
+        <v>0.9142857142857144</v>
       </c>
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="inlineStr">
@@ -24851,7 +24851,7 @@
         </is>
       </c>
       <c r="AJ154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Conducts comprehensive risk assessments and develops disaster recovery and contingency solutions.</t>
+          <t>Conducts risk analysis and develops disaster recovery and contingency solutions.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>risk assessment, disaster recovery, contingency planning, business continuity, risk analysis</t>
+          <t>risk assessment, disaster recovery, contingency planning, business continuity, threat modelling</t>
         </is>
       </c>
       <c r="J155" t="n">
@@ -24988,13 +24988,9 @@
         </is>
       </c>
       <c r="Z155" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>Disaster Recovery Planning</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA155" t="inlineStr"/>
       <c r="AB155" t="b">
         <v>0</v>
       </c>
@@ -25012,7 +25008,7 @@
         </is>
       </c>
       <c r="AH155" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI155" t="inlineStr">
         <is>
@@ -25020,7 +25016,7 @@
         </is>
       </c>
       <c r="AJ155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -25064,7 +25060,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>stakeholder engagement, feedback loops, document management, communication protocols, submit document</t>
+          <t>stakeholder engagement, feedback loops, document management, communication protocols, collaboration tools</t>
         </is>
       </c>
       <c r="J156" t="n">
@@ -25185,7 +25181,7 @@
         </is>
       </c>
       <c r="AJ156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -25229,7 +25225,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>priority alignment, outcome mapping, strategic planning, performance metrics, scenario analysis</t>
+          <t>priority alignment, outcome mapping, roadmap development, performance metrics, scenario analysis</t>
         </is>
       </c>
       <c r="J157" t="n">
@@ -25318,7 +25314,7 @@
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>keep:5, "Strategy Prioritisation":2</t>
+          <t>keep:4, "Priority Planning":2, "Strategy Prioritisation":1</t>
         </is>
       </c>
       <c r="Z157" t="b">
@@ -25326,9 +25322,13 @@
       </c>
       <c r="AA157" t="inlineStr"/>
       <c r="AB157" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC157" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Foundation Skill describes a work style (strategic planning) that is already embedded in other skills and PCs</t>
+        </is>
+      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
@@ -25350,7 +25350,7 @@
         </is>
       </c>
       <c r="AJ157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -25394,7 +25394,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>communication tools, relationship building, stakeholder engagement, collaboration platforms, team collaboration</t>
+          <t>communication tools, relationship building, stakeholder engagement, collaboration platforms, interpersonal communication</t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -25515,7 +25515,7 @@
         </is>
       </c>
       <c r="AJ158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -25559,7 +25559,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>specification drafting, process documentation, evaluation reporting, strategic articulation, technical writing</t>
+          <t>specification drafting, process documentation, evaluation reporting, strategic articulation, document control</t>
         </is>
       </c>
       <c r="J159" t="n">
@@ -25680,7 +25680,7 @@
         </is>
       </c>
       <c r="AJ159" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -25719,12 +25719,12 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Assesses system vulnerabilities through structured threat identification and analysis to support mitigation planning.</t>
+          <t>Evaluates system threats.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>risk analysis, vulnerability assessment, threat modelling, cyber security, evaluate</t>
+          <t>risk analysis, vulnerability assessment, threat modelling, cyber security, intelligence gathering</t>
         </is>
       </c>
       <c r="J160" t="n">
@@ -25808,7 +25808,7 @@
         <v>0</v>
       </c>
       <c r="W160" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X160" t="inlineStr"/>
       <c r="Y160" t="inlineStr">
@@ -25841,7 +25841,7 @@
         </is>
       </c>
       <c r="AH160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI160" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         </is>
       </c>
       <c r="AJ160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -25886,16 +25886,16 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting decisions with relevant data and reasoning.</t>
+          <t>Provides clear, evidence‑based answers to queries, supporting statements with relevant data and reasoning.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>evidence based answers, stakeholder queries, data support, reasoning justification, clear communication</t>
+          <t>evidence based answers, substantiated responses, query handling, data support, reasoning justification</t>
         </is>
       </c>
       <c r="J161" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>0</v>
       </c>
       <c r="W161" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="X161" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
       </c>
       <c r="AG161" t="inlineStr">
         <is>
-          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting decisions with relevant data and reasoning.</t>
+          <t>Provides clear, evidence‑based answers to queries, supporting statements with relevant data and reasoning.</t>
         </is>
       </c>
       <c r="AH161" t="b">
@@ -25990,7 +25990,7 @@
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>evidence based answers, stakeholder queries, data support, reasoning justification, clear communication</t>
+          <t>evidence based answers, substantiated responses, query handling, data support, reasoning justification</t>
         </is>
       </c>
       <c r="AJ161" t="b">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Assists in identifying and confirming the types of information stored on each registered digital device.</t>
+          <t>Confirms and documents the types of information stored on each registered digital device.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, data mapping, asset documentation, device identification</t>
+          <t>device data inventory, information classification, registered devices, data mapping, asset documentation</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -26127,15 +26127,15 @@
       </c>
       <c r="AG162" t="inlineStr">
         <is>
-          <t>Assists in identifying and confirming the types of information stored on each registered digital device.</t>
+          <t>Assists in confirming and documenting the types of information stored on each registered digital device.</t>
         </is>
       </c>
       <c r="AH162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, data mapping, asset documentation, storage verification</t>
+          <t>device data inventory, information classification, data mapping, asset documentation, digital records</t>
         </is>
       </c>
       <c r="AJ162" t="b">
@@ -26176,16 +26176,16 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated personnel by organising, presenting, and confirming sign‑off requirements.</t>
+          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>approval process, stakeholder engagement, sign‑off management, final sign‑off, coordination</t>
+          <t>sign‑off management, approval process, stakeholder engagement, compliance confirmation, final sign‑off</t>
         </is>
       </c>
       <c r="J163" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -26249,7 +26249,7 @@
         <v>0</v>
       </c>
       <c r="W163" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="X163" t="inlineStr">
         <is>
@@ -26274,7 +26274,7 @@
       </c>
       <c r="AG163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated personnel by organising, presenting, and confirming sign‑off requirements.</t>
+          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
         </is>
       </c>
       <c r="AH163" t="b">
@@ -26282,7 +26282,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>approval process, stakeholder engagement, documentation finalisation, authority confirmation, sign‑off management</t>
+          <t>approval process, stakeholder engagement, compliance confirmation, sign‑off management, finalisation</t>
         </is>
       </c>
       <c r="AJ163" t="b">
@@ -26323,12 +26323,12 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Identifies organisational processes and transaction types suitable for blockchain implementation and determines relevant legislation, organisational policies and procedures, as well as their impact on the solution.</t>
+          <t>Identifies organisational processes and transaction types suitable for blockchain technology and determines relevant legislation, policies and procedures and their impact on the solution.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>organisational processes, transaction types, blockchain suitability, legislative impact, blockchain technology</t>
+          <t>process evaluation, transaction analysis, blockchain suitability, organisational assessment, compliance impact</t>
         </is>
       </c>
       <c r="J164" t="n">
@@ -26437,11 +26437,11 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>organisational processes, transaction types, blockchain suitability, legislative impact, policy compliance</t>
+          <t>process evaluation, transaction analysis, blockchain suitability, organisational assessment, compliance impact</t>
         </is>
       </c>
       <c r="AJ164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -26458,7 +26458,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Log Requirement Consultation</t>
+          <t>Data Log Strategy Discussion</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -26478,12 +26478,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Collaborates with relevant personnel to discuss and confirm data log requirements and processing strategy.</t>
+          <t>Discusses and confirms data log requirements and processing strategies with relevant personnel.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel consultation, requirement discussion, confirm data log</t>
+          <t>data log requirements, data log strategy, personnel coordination, discussion facilitation, requirement confirmation</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -26542,7 +26542,7 @@
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>Log Requirement Consultation</t>
+          <t>Data Log Strategy Discussion</t>
         </is>
       </c>
       <c r="V165" t="b">
@@ -26574,15 +26574,15 @@
       </c>
       <c r="AG165" t="inlineStr">
         <is>
-          <t>Collaborates with relevant personnel to discuss and confirm data log requirements and processing strategy.</t>
+          <t>Facilitates discussions with relevant personnel to confirm data log requirements and processing strategies.</t>
         </is>
       </c>
       <c r="AH165" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel consultation, requirement discussion, log strategy confirmation</t>
+          <t>data log requirements, processing strategy, personnel coordination, discussion facilitation, requirement confirmation</t>
         </is>
       </c>
       <c r="AJ165" t="b">
@@ -26623,12 +26623,12 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>The worker evaluates gathered threat data results to confirm reliability and consistency before further processing.</t>
+          <t>Obtains and analyses results to ensure reliability and consistency across multiple sources and tools.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>reliability assessment, consistency verification, data validation, result evaluation, results analysis</t>
+          <t>reliability assessment, consistency verification, data validation, result evaluation, reliability analysis</t>
         </is>
       </c>
       <c r="J166" t="n">
@@ -26719,11 +26719,11 @@
       </c>
       <c r="AG166" t="inlineStr">
         <is>
-          <t>The worker evaluates gathered threat data results to confirm reliability and consistency before further processing.</t>
+          <t>Evaluates gathered threat data results to ensure reliability and consistency across multiple sources and tools.</t>
         </is>
       </c>
       <c r="AH166" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI166" t="inlineStr">
         <is>
@@ -26768,12 +26768,12 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Assess the current protection plan's effectiveness and ensure it aligns with organisational and legislative requirements.</t>
+          <t>Evaluates how well the current protection plan meets organisational needs and regulatory standards.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>protection plan assessment, effectiveness analysis, organisational alignment, critical asset identification, operational systems</t>
+          <t>plan effectiveness, organisational requirements, critical assets, legislative compliance, operational systems</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -26871,7 +26871,7 @@
       </c>
       <c r="AG167" t="inlineStr">
         <is>
-          <t>Assess the current protection plan's effectiveness and ensure it aligns with organisational and legislative requirements.</t>
+          <t>Evaluates how well the current protection plan meets organisational needs and regulatory standards.</t>
         </is>
       </c>
       <c r="AH167" t="b">
@@ -26879,7 +26879,7 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>protection plan assessment, effectiveness analysis, organisational alignment, legislative compliance, critical asset identification</t>
+          <t>plan effectiveness, organisational requirements, alignment assessment, critical assets, legislative compliance</t>
         </is>
       </c>
       <c r="AJ167" t="b">
@@ -26900,12 +26900,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Plan Alignment Documentation</t>
+          <t>Incident Plan Alignment</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>DOMAIN_KNOWLEDGE</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -26915,17 +26915,17 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>PRACTICAL</t>
+          <t>THEORETICAL</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>The worker determines and documents how the existing incident response plan aligns with identified requirements, then submits the documentation to the required personnel and addresses any feedback received.</t>
+          <t>Determines the alignment of the current incident response plan with identified requirements, documents the findings, submits the documentation to required personnel, and seeks and responds to feedback.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment, documentation, requirements, submit</t>
+          <t>incident response plan, alignment analysis, documentation, requirements mapping, feedback response</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -26998,7 +26998,7 @@
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>Plan Alignment Documentation</t>
+          <t>Incident Plan Alignment</t>
         </is>
       </c>
       <c r="V168" t="b">
@@ -27030,7 +27030,7 @@
       </c>
       <c r="AG168" t="inlineStr">
         <is>
-          <t>The worker aligns the current incident response plan with requirements and records the findings for review.</t>
+          <t>Analyzes the current incident response plan, documents its alignment with requirements, and submits it for feedback.</t>
         </is>
       </c>
       <c r="AH168" t="b">
@@ -27038,7 +27038,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment, documentation, requirements, feedback</t>
+          <t>incident response plan, alignment analysis, documentation, requirements mapping, feedback submission</t>
         </is>
       </c>
       <c r="AJ168" t="b">
@@ -27059,7 +27059,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Evidence Preservation</t>
+          <t>Evidence Preservation Assistance</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -27079,12 +27079,12 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing, and securely preserving evidence in line with organisational requirements.</t>
+          <t>Assist in gathering, processing, and preserving evidence in line with organisational and legal requirements.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, security requirements, incident response</t>
+          <t>evidence collection, evidence processing, evidence preservation, forensic evidence, legislative requirements</t>
         </is>
       </c>
       <c r="J169" t="n">
@@ -27156,7 +27156,7 @@
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>Evidence Preservation</t>
+          <t>Evidence Preservation Assistance</t>
         </is>
       </c>
       <c r="V169" t="b">
@@ -27188,7 +27188,7 @@
       </c>
       <c r="AG169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing, and securely preserving evidence in line with organisational requirements.</t>
+          <t>Assist in gathering, processing, and preserving evidence in line with organisational and legal requirements.</t>
         </is>
       </c>
       <c r="AH169" t="b">
@@ -27196,11 +27196,11 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, security requirements, incident response</t>
+          <t>evidence collection, evidence processing, evidence preservation, incident response, legal compliance</t>
         </is>
       </c>
       <c r="AJ169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
@@ -27237,12 +27237,12 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Identifies essential business functions, critical data, and software, and evaluates risk impacts on ICT systems.</t>
+          <t>Identify essential business functions, data, and software, and assess ICT risk impacts on them.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>business critical functions, security environment, critical data, software assets, threat assessment</t>
+          <t>business critical functions, security environment, critical data, software assets, business risk</t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -27341,7 +27341,7 @@
       </c>
       <c r="AG170" t="inlineStr">
         <is>
-          <t>Identifies essential business functions, critical data, and software, and evaluates risk impacts on ICT systems.</t>
+          <t>Identify essential business functions, data, and software, and assess ICT risk impacts on them.</t>
         </is>
       </c>
       <c r="AH170" t="b">
@@ -27349,7 +27349,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>business critical functions, security environment, critical data, software assets, risk impact assessment</t>
+          <t>business critical functions, security environment, critical data, software assets, ICT risk assessment</t>
         </is>
       </c>
       <c r="AJ170" t="b">
@@ -27395,7 +27395,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>disaster strategy, cut‑over criteria, task sign‑off, document disaster strategy, final task sign‑off</t>
+          <t>disaster strategy, process documentation, cut‑over criteria, task sign‑off, disaster strategy processes</t>
         </is>
       </c>
       <c r="J171" t="n">

--- a/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v7.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v7.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>stakeholder engagement, feedback, communication, empathy, viewpoint elicitation</t>
+          <t>communication, empathy, feedback, stakeholder engagement, viewpoint elicitation</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -815,7 +815,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Compares project concepts against industry best‑practice examples of similar products to identify improvement opportunities.</t>
+          <t>Compares project concepts against industry best‑practice examples of similar products to highlight improvement opportunities.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="AH3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
@@ -982,12 +982,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Generates diverse solutions by leading focused brainstorming sessions to address identified issues.</t>
+          <t>Brainstorms diverse solutions by leading focused sessions to address identified issues.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ideation, brainstorming, idea generation, creative problem solving, group facilitation</t>
+          <t>ideation, creative problem solving, mind mapping, group facilitation, idea generation</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="AH4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Applies systematic analytical methods to collect and assess concepts in complex, non‑routine scenarios.</t>
+          <t>Gathers and evaluates concepts using systematic analytical methods in complex, non‑routine scenarios.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>systematic analytical processes, concept evaluation, analytical methodology, feasibility analysis, design thinking</t>
+          <t>analytical methodology, systematic concept evaluation, feasibility analysis, design thinking, concept evaluation</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="AH5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Applies creative thinking techniques to develop innovative solutions to workplace challenges.</t>
+          <t>Generates innovative solutions to workplace challenges using creative thinking techniques.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ideation, innovation, brainstorming, design thinking, problem solving</t>
+          <t>creative thinking, ideation, innovation, brainstorming, design thinking</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="AH6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="AJ6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>record‑keeping, compliance, audit trail, quality assurance, organisational standards</t>
+          <t>record‑keeping, compliance, audit trail, quality assurance, feedback</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="AJ7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Idea Viability Evaluation</t>
+          <t>Solution Viability Assessment</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Assesses ideas by systematically comparing them against identified viability factors.</t>
+          <t>Evaluates ideas against identified viability factors.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>feasibility analysis, criteria weighting, business case evaluation, market viability, idea viability</t>
+          <t>feasibility analysis, risk assessment, criteria weighting, business case evaluation, solution viability</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -1730,13 +1730,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>keep:0, "Idea Viability Evaluation":4, "Idea Viability Assessment":3</t>
+          <t>keep:0, "Solution Viability Assessment/Idea Viability Assessment":4, "Idea Viability Evaluation":3</t>
         </is>
       </c>
       <c r="Z8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Solution Viability Assessment</t>
+        </is>
+      </c>
       <c r="AB8" t="b">
         <v>0</v>
       </c>
@@ -1754,7 +1758,7 @@
         </is>
       </c>
       <c r="AH8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
@@ -1801,12 +1805,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Selects an issue to be explored, consulting relevant personnel to ensure relevance.</t>
+          <t>Selects an issue to be explored in consultation with relevant personnel for focused analysis.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>stakeholder engagement, problem identification, needs assessment, consultation processes, decision‑making</t>
+          <t>stakeholder engagement, problem identification, issue selection, consultation processes, decision‑making</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1929,7 +1933,7 @@
         </is>
       </c>
       <c r="AJ9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1968,12 +1972,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Prepares proposals and plans for relevant stakeholders incorporating appropriate vocabulary</t>
+          <t>Prepares detailed proposals and plans using sector‑specific terminology for stakeholders.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>stakeholder communication, business case development, grant and RFP responses, technical documentation, persuasive writing</t>
+          <t>proposal writing, stakeholder communication, business case development, grant and RFP responses, persuasive writing</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -2088,7 +2092,7 @@
         </is>
       </c>
       <c r="AJ10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2132,7 +2136,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>literature review, data collection, search strategies, online databases, information research</t>
+          <t>literature review, data collection, search strategies, online databases, research</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -2286,12 +2290,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Selects appropriate solution formats and delivers tailored presentations to stakeholders.</t>
+          <t>Selects appropriate solution formats and presents tailored presentations to stakeholders.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>solution presentation, stakeholder communication, visual presentation tools, format selection, solution pitching</t>
+          <t>stakeholder communication, visual presentation tools, solution pitching, format selection, business briefings</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -2378,7 +2382,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:4, "Solution Presentation":3</t>
         </is>
       </c>
       <c r="Z12" t="b">
@@ -2402,7 +2406,7 @@
         </is>
       </c>
       <c r="AH12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
@@ -2410,7 +2414,7 @@
         </is>
       </c>
       <c r="AJ12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2454,7 +2458,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>requirements analysis, design optimisation, prototype testing, solution finalisation, validation feedback</t>
+          <t>requirements analysis, design optimisation, prototype testing, solution refinement, validation feedback</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -2536,16 +2540,16 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:2, "Solution Refinement":5</t>
         </is>
       </c>
       <c r="Z13" t="b">
@@ -2616,12 +2620,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Evaluates alternative solutions to a business problem, identifying constraints to determine feasible options.</t>
+          <t>Assesses alternative solutions to a business problem, identifying constraints to determine feasible options.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>feasibility analysis, constraint identification, business issue evaluation, risk assessment, decision matrices</t>
+          <t>feasibility analysis, constraint identification, solution viability, risk assessment, decision matrices</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -2724,7 +2728,7 @@
         </is>
       </c>
       <c r="AH14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
@@ -2732,7 +2736,7 @@
         </is>
       </c>
       <c r="AJ14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -2771,12 +2775,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Seeks feedback from stakeholders on ideas to refine concepts and align expectations.</t>
+          <t>Seeks stakeholder input on ideas to inform concepts and expectations.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>stakeholder engagement, feedback collection, surveys, interviews, communication</t>
+          <t>stakeholder engagement, feedback collection, surveys, interviews, solicitation</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -2858,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr">
@@ -2895,7 +2899,7 @@
         </is>
       </c>
       <c r="AJ15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -2934,12 +2938,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Guides group discussions, encourages participation and coordinates tasks to achieve shared outcomes.</t>
+          <t>Collaborates with others to facilitate group discussions, encouraging participation and achieving shared outcomes.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>group dynamics, meeting facilitation, conflict resolution, consensus building, group interaction</t>
+          <t>group dynamics, meeting facilitation, conflict resolution, consensus building, interaction</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -3025,12 +3029,12 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>keep:2, "Group Interaction Facilitation":4, "Discussion Facilitation":1</t>
+          <t>keep:1, "Group Interaction Facilitation/Group Facilitation":6</t>
         </is>
       </c>
       <c r="Z16" t="b">
@@ -3054,7 +3058,7 @@
         </is>
       </c>
       <c r="AH16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
@@ -3101,12 +3105,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Creates and maintains a cyber security awareness program that reflects organisation-wide best practice.</t>
+          <t>Creates and maintains organisation‑wide cyber security awareness programs in line with best practice.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>cyber security, security awareness training, risk management, phishing simulations, compliance governance</t>
+          <t>cyber security, security awareness training, phishing simulations, compliance governance, security awareness program</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -3226,7 +3230,7 @@
         </is>
       </c>
       <c r="AJ17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -3265,12 +3269,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Writes workplace documents using precise cyber security terminology to clearly convey technical information.</t>
+          <t>Documents workplace information using precise cyber security terminology to clearly convey technical details.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>cyber security terminology, technical documentation, information security policies, industry standards (ISO 27001, NIST), risk assessment reporting</t>
+          <t>cyber security terminology, technical documentation, clear writing, information security policies, industry standards (ISO 27001, NIST)</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -3370,7 +3374,7 @@
         </is>
       </c>
       <c r="AH18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
@@ -3378,7 +3382,7 @@
         </is>
       </c>
       <c r="AJ18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -3417,12 +3421,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Assesses cyber security awareness within the work area through surveys and interviews to establish baseline levels.</t>
+          <t>Establishes baseline cyber security awareness levels in the work area through surveys and interviews.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>cyber security, risk awareness, security posture, threat intelligence, security metrics</t>
+          <t>cyber security, risk awareness, security posture, threat intelligence, current level</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -3530,7 +3534,7 @@
         </is>
       </c>
       <c r="AH19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
@@ -3538,7 +3542,7 @@
         </is>
       </c>
       <c r="AJ19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -3582,7 +3586,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>cyber security, policy compliance, risk communication, security standards, stakeholder reporting</t>
+          <t>cyber security, policy compliance, risk communication, security standards, improvement requirements</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -3690,7 +3694,7 @@
         </is>
       </c>
       <c r="AJ20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -3729,12 +3733,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Delivers concise insight presentations derived from reviews and training to designated personnel.</t>
+          <t>Presents concise insight presentations derived from reviews and training to designated personnel.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>insights presentation, stakeholder communication, knowledge transfer, visual storytelling, presentation tools</t>
+          <t>stakeholder communication, knowledge transfer, visual storytelling, insight presentation, presentation tools</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -3842,7 +3846,7 @@
         </is>
       </c>
       <c r="AH21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
@@ -3894,7 +3898,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Notifiable Data Breach, Australian Privacy Act, data protection compliance, privacy law interpretation, regulatory risk assessment</t>
+          <t>Notifiable Data Breach, Australian Privacy Act, data protection compliance, privacy law interpretation, legislation</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -4006,7 +4010,7 @@
         </is>
       </c>
       <c r="AJ22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -4045,12 +4049,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Documents outcomes of the review and suggested improvements for consideration by required personnel.</t>
+          <t>Documents review outcomes and suggested improvements for consideration by required personnel.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>reporting, review outcomes, improvement recommendations, stakeholder communication, record‑keeping</t>
+          <t>reporting, review outcomes, improvement recommendations, stakeholder communication, outcome documentation</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -4166,7 +4170,7 @@
         </is>
       </c>
       <c r="AJ23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -4205,12 +4209,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Drafts cyber security policies and procedures and disseminates them to relevant staff.</t>
+          <t>Develops cyber security policies and procedures and communicates them to required personnel.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>cyber security governance, policy development, cyber security policies, stakeholder communication, compliance frameworks</t>
+          <t>cyber security governance, policy development, risk management, compliance frameworks, drafting</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -4289,7 +4293,7 @@
         <v>1</v>
       </c>
       <c r="W24" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9042857142857142</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -4322,7 +4326,7 @@
         </is>
       </c>
       <c r="AH24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
@@ -4369,12 +4373,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Conducts systematic reviews of cyber security practices to ensure alignment with organisational policies and procedures.</t>
+          <t>Reviews cyber security practices to ensure alignment with organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>cyber security, policy compliance, security governance, audit controls, cyber security practices</t>
+          <t>cyber security, policy compliance, security governance, audit controls, practice review</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -4486,7 +4490,7 @@
         </is>
       </c>
       <c r="AH25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
@@ -4538,7 +4542,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>cyber security documentation, information security records, compliance logging, data governance, audit trail management</t>
+          <t>cyber security documentation, information security records, compliance logging, data governance, record maintenance</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -4654,7 +4658,7 @@
         </is>
       </c>
       <c r="AJ26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -4693,7 +4697,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Consults with stakeholders to inform decision making</t>
+          <t>Engages relevant stakeholders through meetings and surveys to inform decision‑making.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4845,12 +4849,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Works collaboratively with interdisciplinary teams to promote cyber security.</t>
+          <t>Promotes cyber security measures within interdisciplinary teams.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>interdisciplinary teamwork, cyber security coordination, cross‑functional communication, stakeholder engagement, collaboration tools</t>
+          <t>interdisciplinary teamwork, cyber security coordination, cross‑functional communication, stakeholder engagement, team collaboration</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -4962,7 +4966,7 @@
         </is>
       </c>
       <c r="AJ28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -5001,7 +5005,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Selects and operates suitable platforms to deliver cyber security awareness initiatives across the work area.</t>
+          <t>Promotes cyber security awareness initiatives across the work area using suitable platforms.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -5085,7 +5089,7 @@
         <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -5094,7 +5098,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Technology Platform Utilisation":1</t>
         </is>
       </c>
       <c r="Z29" t="b">
@@ -5118,7 +5122,7 @@
         </is>
       </c>
       <c r="AH29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
@@ -5165,7 +5169,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Reviews latest cyber security threats and trends impacting organisations.</t>
+          <t>Reviews current cyber threat reports to identify organisational impacts.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -5249,7 +5253,7 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0.9528571428571428</v>
+        <v>0.95</v>
       </c>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr">
@@ -5325,12 +5329,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Arranges training and information updates as required, maintaining related records.</t>
+          <t>Maintains and updates training records by recording activities.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>training coordination, training schedules, learning management systems, record management, information updates</t>
+          <t>training schedules, learning management systems, record management, information updates, training coordination</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -5601,7 +5605,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Installs and runs latest anti‑malware on each device.</t>
+          <t>Installs and runs up‑to‑date anti‑malware on all workstations to ensure continuous protection.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -5764,12 +5768,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Reviews number of breaches and business impact over the review period.</t>
+          <t>Reviews breach volumes and business impacts across review periods to inform risk mitigation.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>risk assessment, incident tracking, business impact analysis, compliance reporting, security metrics</t>
+          <t>risk assessment, incident tracking, business impact analysis, compliance reporting, breach</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -5847,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr">
@@ -5884,7 +5888,7 @@
         </is>
       </c>
       <c r="AJ35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -5923,12 +5927,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Ensures new devices are updated and configured correctly as part of the initial start‑up procedure.</t>
+          <t>Performs initial device set‑up by updating firmware and configuring settings on new devices.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>device provisioning, firmware updates, configuration management, hardware initialisation, system onboarding</t>
+          <t>device provisioning, firmware updates, configuration management, hardware initialisation, device setup</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -6007,7 +6011,7 @@
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>keep:5, "Device Configuration":2</t>
+          <t>keep:4, "Device Configuration":3</t>
         </is>
       </c>
       <c r="Z36" t="b">
@@ -6031,7 +6035,7 @@
         </is>
       </c>
       <c r="AH36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
@@ -6039,7 +6043,7 @@
         </is>
       </c>
       <c r="AJ36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -6078,7 +6082,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Implements device encryption in accordance with prescribed procedures to secure hardware.</t>
+          <t>Encrypts devices in accordance with prescribed procedures to secure hardware.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -6186,7 +6190,7 @@
         </is>
       </c>
       <c r="AH37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
@@ -6233,12 +6237,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Creates and updates a register of networked devices to support inventory tracking and asset management.</t>
+          <t>Creates and maintains a register of networked devices for inventory tracking and asset management.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>digital device register, IT asset tracking, hardware registers, network inventories, CMDB</t>
+          <t>IT asset tracking, hardware registers, network inventories, device register, asset management software</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -6361,7 +6365,7 @@
         </is>
       </c>
       <c r="AH38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
@@ -6408,7 +6412,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Conducts gap analyses to evaluate best‑practice implementation effectiveness.</t>
+          <t>Conducts gap analysis to evaluate effectiveness of best‑practice implementation.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -6576,7 +6580,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>authentication, password complexity, entropy, cyber security, password managers</t>
+          <t>authentication, password complexity, password strength, cyber security, password managers</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -6687,7 +6691,7 @@
         </is>
       </c>
       <c r="AJ40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -6726,12 +6730,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Develops physical security plan and communicates it to the whole organisation.</t>
+          <t>Develops and plans comprehensive physical security plans and communicates them organisation‑wide to ensure coordinated protection.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>risk assessment, access control systems, security policy development, facility protection, stakeholder communication</t>
+          <t>risk assessment, access control systems, physical security plan, facility protection, stakeholder communication</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -6822,9 +6826,13 @@
         </is>
       </c>
       <c r="Z41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Security Plan Communication</t>
+        </is>
+      </c>
       <c r="AB41" t="b">
         <v>0</v>
       </c>
@@ -6850,7 +6858,7 @@
         </is>
       </c>
       <c r="AJ41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -6889,12 +6897,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Categorises level of risk associated with each device based on sensitivity of information stored.</t>
+          <t>Categorises device data sensitivity to assign appropriate risk categories for security management.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>risk assessment, information sensitivity, device classification, risk categorisation, cyber security</t>
+          <t>risk assessment, information sensitivity, device classification, cyber security, risk categorisation</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -6972,16 +6980,16 @@
         <v>1</v>
       </c>
       <c r="W42" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>keep:3, "Data Risk Categorisation":4</t>
+          <t>keep:0, "Data Risk Categorisation":7</t>
         </is>
       </c>
       <c r="Z42" t="b">
@@ -7032,7 +7040,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Physical Security Plan Communication</t>
+          <t>Security Plan Communication</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -7052,12 +7060,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Delivers organisation‑wide briefings on physical security plans to support understanding and compliance.</t>
+          <t>Communicates the physical security plan to the whole organisation, supporting understanding and compliance.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>physical security, physical security plan, security policy, stakeholder communication, access control</t>
+          <t>physical security, risk assessment, security policy, stakeholder communication, access control</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -7136,29 +7144,21 @@
         </is>
       </c>
       <c r="V43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 4/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>keep:2, "Physical Security Plan Communication":4, "Physical Security Planning":1</t>
+          <t>keep:4, "Physical Security Plan Communication/Physical Security Communication":3</t>
         </is>
       </c>
       <c r="Z43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>Physical Security Planning</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="b">
         <v>0</v>
       </c>
@@ -7176,7 +7176,7 @@
         </is>
       </c>
       <c r="AH43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="AJ43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>risk assessment, encryption standards, device hardening, cyber security governance, protocol compliance</t>
+          <t>risk assessment, encryption standards, device hardening, cyber security governance, security protocol selection</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -7310,7 +7310,7 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr">
@@ -7347,7 +7347,7 @@
         </is>
       </c>
       <c r="AJ44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Supports the organisation in selecting the most appropriate security strategies.</t>
+          <t>Supports the organisation to select the most appropriate security strategies.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Security Development Monitoring</t>
+          <t>Security Trend Monitoring</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Monitors latest developments in digital security.</t>
+          <t>Monitors emerging digital security developments to inform risk assessments and protective measures.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>digital security, cyber security, threat intelligence, vulnerability tracking, security intelligence feeds</t>
+          <t>cyber security, threat intelligence, vulnerability tracking, security intelligence feeds, trend monitoring</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -7629,19 +7629,15 @@
         </is>
       </c>
       <c r="V46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 4/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>keep:3, "Security Development Monitoring":4</t>
+          <t>keep:4, "Security Development Monitoring":3</t>
         </is>
       </c>
       <c r="Z46" t="b">
@@ -7665,7 +7661,7 @@
         </is>
       </c>
       <c r="AH46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
@@ -7712,12 +7708,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Installs software patches on desktop and mobile devices to maintain system security.</t>
+          <t>Applies updates to software and applications on desktop and mobile devices to maintain system security.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>patch management, software updates, endpoint management, mobile device management, security patches</t>
+          <t>patch management, software updates, endpoint management, mobile device management, application updates</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -7836,7 +7832,7 @@
         </is>
       </c>
       <c r="AJ47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -7880,7 +7876,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>two-factor authentication, multi-factor authentication, OTP, access control, cyber security</t>
+          <t>multi‑factor authentication, MFA, OTP, access control, enablement</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -8042,12 +8038,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Develops action plans to implement proposed changes, ensuring a prioritised schedule and alignment with organisational policies and procedures.</t>
+          <t>Develops detailed action plans, prioritising tasks and scheduling implementation in line with organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>project scheduling, prioritisation, policy compliance, change management, implementation planning</t>
+          <t>project scheduling, prioritisation, policy compliance, change management, action plan</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -8112,7 +8108,7 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr">
@@ -8149,7 +8145,7 @@
         </is>
       </c>
       <c r="AJ49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -8338,12 +8334,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Explores emerging digital tools to organise and analyse data and support effective communication.</t>
+          <t>Investigates new digital technologies and applications to manage data and communicate effectively.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>digital technologies, emerging technologies, data management, cloud computing, data visualisation</t>
+          <t>data management, digital collaboration tools, emerging technologies, cloud computing, technology utilisation</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -8441,7 +8437,7 @@
         </is>
       </c>
       <c r="AH51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
@@ -8493,7 +8489,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>technical writing, document review, quality assurance, reporting standards, document evaluation</t>
+          <t>technical writing, document review, quality assurance, reporting standards, document evaluation process</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -8562,12 +8558,12 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>keep:1, "Evaluation Documentation":6</t>
+          <t>keep:1, "Evaluation Documentation":4, "Evaluation Documentation Preparation":2</t>
         </is>
       </c>
       <c r="Z52" t="b">
@@ -8618,7 +8614,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ICT Gap Identification</t>
+          <t>Ict Gap Identification</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -8638,12 +8634,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Analyses strategic objectives against current ICT capability in hybrid environments to identify gaps and propose improvements.</t>
+          <t>Compares strategic plan objectives with the current state of ICT to determine ICT gaps, improvement opportunities and proposed changes, and plans implementation of the identified improvements.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>gap analysis, strategic alignment, ICT gaps, improvement opportunities, proposed changes</t>
+          <t>gap analysis, strategic alignment, technology roadmaps, ICT governance, digital transformation</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -8717,19 +8713,15 @@
         </is>
       </c>
       <c r="V53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 6/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>keep:1, "ICT Gap Identification":6</t>
+          <t>keep:4, "ICT Gap Identification":3</t>
         </is>
       </c>
       <c r="Z53" t="b">
@@ -8753,7 +8745,7 @@
         </is>
       </c>
       <c r="AH53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
@@ -8761,7 +8753,7 @@
         </is>
       </c>
       <c r="AJ53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -8800,7 +8792,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Evaluates impact of proposed ICT system changes against the organisation's strategic objectives.</t>
+          <t>Assesses proposed ICT system changes in hybrid environments for alignment with organisational strategic objectives.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -8915,7 +8907,7 @@
         </is>
       </c>
       <c r="AH54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
@@ -8962,12 +8954,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Investigates new and innovative ideas to continuously improve work practices and processes.</t>
+          <t>Investigates innovative ideas to continuously improve work practices and processes.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>continuous improvement, process optimisation, ideation techniques, creative problem solving, innovation management</t>
+          <t>continuous improvement, process optimisation, ideation techniques, innovative ideas, investigation</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -9032,12 +9024,12 @@
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>keep:6, "Innovative Idea Investigation":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z55" t="b">
@@ -9069,7 +9061,7 @@
         </is>
       </c>
       <c r="AJ55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -9088,7 +9080,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Numerical Data Interpretation</t>
+          <t>Financial Impact Assessment</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -9108,12 +9100,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Interprets numerical data and applies mathematical calculations to assess the financial implications of introducing changes.</t>
+          <t>Interprets numerical data and applies mathematical calculations to assess the financial implications of proposed changes in hybrid environments.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>financial analysis, quantitative modelling, cost‑benefit assessment, Excel, statistical calculations</t>
+          <t>financial analysis, quantitative modelling, cost‑benefit assessment, Excel, impact assessment</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -9175,15 +9167,19 @@
         </is>
       </c>
       <c r="V56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="X56" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/7: </t>
+        </is>
+      </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>keep:3, "Financial Impact Interpretation":3, "Financial Impact Assessment":1</t>
+          <t>keep:0, "Financial Impact Assessment":5, "Financial Impact Interpretation":2</t>
         </is>
       </c>
       <c r="Z56" t="b">
@@ -9215,7 +9211,7 @@
         </is>
       </c>
       <c r="AJ56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -9234,7 +9230,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Policy Compliance Assessment</t>
+          <t>Policy Compliance Documentation</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -9254,7 +9250,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Details standards, targets and implementation methods in action plans to assess policy compliance.</t>
+          <t>Plans policy compliance by detailing standards, targets and implementation approaches within action plans.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -9321,12 +9317,16 @@
         </is>
       </c>
       <c r="V57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W57" t="n">
         <v>0.95</v>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>MIS re-refinement: ...</t>
+        </is>
+      </c>
       <c r="Y57" t="inlineStr">
         <is>
           <t>keep:7</t>
@@ -9341,9 +9341,13 @@
       </c>
       <c r="AC57" t="inlineStr"/>
       <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
       <c r="AF57" t="b">
         <v>0</v>
       </c>
@@ -9405,7 +9409,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>action planning, prioritised schedules, timeline management, resource allocation, critical path</t>
+          <t>action planning, prioritised schedules, timeline management, resource allocation, project scheduling</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -9507,7 +9511,7 @@
         </is>
       </c>
       <c r="AJ58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -9526,7 +9530,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Implementation Difficulty Evaluation</t>
+          <t>Risk Assessment</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -9546,12 +9550,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Evaluates the difficulty of implementing proposed changes to ICT systems and products.</t>
+          <t>Evaluates the difficulty of implementing proposed ICT system changes and products across hybrid environments.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ICT systems, change management, implementation difficulty, risk analysis, impact assessment</t>
+          <t>ICT systems, change management, implementation complexity, risk analysis, proposed changes</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -9620,12 +9624,12 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name uses 'Planning' but evidence describes evaluating difficulty, not planning</t>
+          <t>MIS re-refinement: Skill name includes 'Planning' but evidence only involves evaluating difficulty, not planning</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>keep:6, "Change Implementation Planning":1</t>
+          <t>keep:6, "Implementation Difficulty Assessment":1</t>
         </is>
       </c>
       <c r="Z59" t="b">
@@ -9641,7 +9645,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>Skill name uses 'Planning' but evidence describes evaluating difficulty, not planning</t>
+          <t>Skill name includes 'Planning' but evidence only involves evaluating difficulty, not planning</t>
         </is>
       </c>
       <c r="AF59" t="b">
@@ -9700,7 +9704,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Reports on proposed changes, gaps and improvement opportunities to senior staff.</t>
+          <t>Reports concise information outlining changes, gaps and improvement opportunities for senior staff.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -10020,12 +10024,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Uses structured analytical frameworks to evaluate options and resolve complex, non‑routine problems.</t>
+          <t>Applies structured analytical frameworks to resolve complex, non‑routine problems.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>decision analysis, analytical reasoning, structured methodologies, risk assessment, scenario modelling</t>
+          <t>decision analysis, analytical reasoning, systematic decision making, risk assessment, scenario modelling</t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -10119,7 +10123,7 @@
         </is>
       </c>
       <c r="AH62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI62" t="inlineStr">
         <is>
@@ -10127,7 +10131,7 @@
         </is>
       </c>
       <c r="AJ62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -10166,7 +10170,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Translates technical terminology into plain English to support understanding across diverse staff groups.</t>
+          <t>Translates technical terminology into plain English to communicate understanding across diverse staff groups.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -10265,7 +10269,7 @@
         </is>
       </c>
       <c r="AH63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI63" t="inlineStr">
         <is>
@@ -10317,7 +10321,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>legislative compliance, policy analysis, regulatory standards, legislative text, qualitative analysis</t>
+          <t>legislative compliance, policy analysis, regulatory standards, qualitative analysis, legislative text</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -10445,7 +10449,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Compliance Management</t>
+          <t>Compliance Review</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -10465,12 +10469,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Reviews organisational privacy policy and procedures to determine compliance with industry standard requirements.</t>
+          <t>Reviews organisational privacy policies and procedures to determine compliance with industry standard requirements in hybrid environments.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>privacy policy, regulatory standards, risk assessment, audit, data protection</t>
+          <t>privacy policy, regulatory standards, compliance, audit, data protection</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -10535,12 +10539,16 @@
         </is>
       </c>
       <c r="V65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W65" t="n">
         <v>0.95</v>
       </c>
-      <c r="X65" t="inlineStr"/>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>MIS re-refinement: Skill name uses 'Management' which is not reflected in evidence actions of reviewing and determining compliance</t>
+        </is>
+      </c>
       <c r="Y65" t="inlineStr">
         <is>
           <t>keep:7</t>
@@ -10555,9 +10563,13 @@
       </c>
       <c r="AC65" t="inlineStr"/>
       <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>Skill name uses 'Management' which is not reflected in evidence actions of reviewing and determining compliance</t>
+        </is>
+      </c>
       <c r="AF65" t="b">
         <v>0</v>
       </c>
@@ -10575,7 +10587,7 @@
         </is>
       </c>
       <c r="AJ65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -10614,12 +10626,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Reviews ethical work practices and feedback and determines application of the organisational code of ethics according to organisational requirements.</t>
+          <t>Reviews ethical work practices and feedback and determines application of the organisational code of ethics.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>professional ethics, codes of conduct, compliance, organisational governance, ethical frameworks</t>
+          <t>professional ethics, codes of conduct, compliance, organisational governance, ethical decision making</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -10724,7 +10736,7 @@
         </is>
       </c>
       <c r="AJ66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -10763,12 +10775,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Collects and addresses feedback on review and grievance documentation from designated personnel.</t>
+          <t>Seeks and reviews feedback on review and grievance documentation from designated personnel, documenting the response as required.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>grievance procedures, review processes, stakeholder communication, document management, complaint handling</t>
+          <t>grievance procedures, stakeholder communication, document management, complaint handling, feedback</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -10865,7 +10877,7 @@
         </is>
       </c>
       <c r="AH67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
@@ -10873,7 +10885,7 @@
         </is>
       </c>
       <c r="AJ67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -10912,7 +10924,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Conducts industry‑standard tests to assess information integrity, confidentiality, security and availability.</t>
+          <t>Tests information integrity, confidentiality, security and availability against industry standards.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -11014,7 +11026,7 @@
         </is>
       </c>
       <c r="AH68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI68" t="inlineStr">
         <is>
@@ -11061,7 +11073,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Synthesises diverse sources into cohesive written reports using specialised terminology and supporting documentation.</t>
+          <t>Synthesises diverse sources into cohesive written documents using specialised terminology and supporting materials.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -11163,7 +11175,7 @@
         </is>
       </c>
       <c r="AH69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI69" t="inlineStr">
         <is>
@@ -11210,12 +11222,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Identifies industry standard intellectual property (IP) and copyright legislation, policies and procedures.</t>
+          <t>Identifies intellectual property and copyright legislation to ensure organisational compliance.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>intellectual property law, copyright legislation, policy compliance, legal research, regulatory analysis</t>
+          <t>intellectual property law, copyright legislation, policy compliance, legal research, legislative analysis</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -11320,7 +11332,7 @@
         </is>
       </c>
       <c r="AJ70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -11359,12 +11371,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Delivers updated policies, procedures and ethics documentation to designated personnel.</t>
+          <t>Distributes revised policy, procedures and ethics documentation to required personnel.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>document dissemination, compliance communication, stakeholder engagement, internal governance, ethics training</t>
+          <t>document dissemination, compliance communication, stakeholder engagement, internal governance, policy distribution</t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -11461,7 +11473,7 @@
         </is>
       </c>
       <c r="AH71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI71" t="inlineStr">
         <is>
@@ -11469,7 +11481,7 @@
         </is>
       </c>
       <c r="AJ71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -11513,7 +11525,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>privacy legislation, privacy policy, code of ethics, policy management, regulatory documentation</t>
+          <t>privacy legislation, policy management, codes of ethics, regulatory documentation, privacy policy</t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -11581,16 +11593,16 @@
         <v>1</v>
       </c>
       <c r="W72" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>keep:1, "Privacy Policy Documentation":6</t>
+          <t>keep:0, "Privacy Policy Documentation":7</t>
         </is>
       </c>
       <c r="Z72" t="b">
@@ -11666,7 +11678,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>policy drafting, grievance management, standard operating procedures, process documentation, compliance workflows</t>
+          <t>policy drafting, grievance management, standard operating procedures, process documentation, procedure</t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -11771,7 +11783,7 @@
         </is>
       </c>
       <c r="AJ73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -11810,7 +11822,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Sequences and schedules complex activities, monitors implementation and manages communication.</t>
+          <t>Sequences and schedules complex activities, monitors progress and manages communication to maintain delivery momentum.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -11900,7 +11912,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Foundation Skill describes work style (sequencing, scheduling, monitoring) already embedded in PCs and other skills</t>
+          <t>FS describes work style (planning, scheduling, monitoring) already embedded in PCs and other skills</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -11963,7 +11975,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Monitors and analyses legislative changes to ensure ongoing compliance with rights and responsibilities.</t>
+          <t>Identifies and analyses legislative changes to ensure ongoing compliance with rights and responsibilities.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -12065,7 +12077,7 @@
         </is>
       </c>
       <c r="AH75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI75" t="inlineStr">
         <is>
@@ -12112,12 +12124,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Manages digital information securely by lawfully collecting, storing, accessing and sharing data using compliant systems.</t>
+          <t>Collects digital information securely by lawfully gathering, storing, accessing and sharing data using compliant systems.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>cyber security, data protection, information governance, privacy compliance, access control</t>
+          <t>cyber security, data protection, information governance, privacy compliance, digital handling</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -12190,7 +12202,7 @@
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>keep:3, "Digital Information Handling":3, "Digital Information Security":1</t>
+          <t>keep:6, "Digital Information Handling":1</t>
         </is>
       </c>
       <c r="Z76" t="b">
@@ -12214,7 +12226,7 @@
         </is>
       </c>
       <c r="AH76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
@@ -12222,7 +12234,7 @@
         </is>
       </c>
       <c r="AJ76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -12261,12 +12273,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Distributes updated policies to stakeholders in accordance with organisational protocols.</t>
+          <t>Distributes policies to stakeholders in accordance with organisational protocols.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>policy dissemination, stakeholder engagement, communication protocols, policy distribution, change management</t>
+          <t>policy dissemination, stakeholder engagement, communication protocols, change management, distribution</t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -12338,12 +12350,12 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>keep:1, "Policy Distribution":6</t>
+          <t>keep:3, "Policy Distribution":4</t>
         </is>
       </c>
       <c r="Z77" t="b">
@@ -12371,7 +12383,7 @@
         </is>
       </c>
       <c r="AH77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
@@ -12423,7 +12435,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>active listening, questioning techniques, stakeholder engagement, dialogue facilitation, interpersonal communication</t>
+          <t>active listening, questioning techniques, stakeholder engagement, verbal communication, interpersonal communication</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -12491,7 +12503,7 @@
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>0.9528571428571428</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr">
@@ -12528,7 +12540,7 @@
         </is>
       </c>
       <c r="AJ78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -12567,12 +12579,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Installs and configures blockchain platform components in line with approved design specifications.</t>
+          <t>Designs and plans blockchain platform components in line with approved design specifications.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>distributed ledger, node deployment, consensus configuration, Ethereum, Docker</t>
+          <t>distributed ledger, node deployment, consensus configuration, blockchain platform, Docker</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -12647,12 +12659,12 @@
         <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>keep:6, "Blockchain Platform Installation":1</t>
+          <t>keep:4, "Blockchain Platform Installation":3</t>
         </is>
       </c>
       <c r="Z79" t="b">
@@ -12676,7 +12688,7 @@
         </is>
       </c>
       <c r="AH79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
@@ -12684,7 +12696,7 @@
         </is>
       </c>
       <c r="AJ79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -12723,12 +12735,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Identifies and resolves blockchain anomalies through contextual analysis to detect subtle deviations.</t>
+          <t>Resolves blockchain anomalies through contextual analysis of subtle deviations.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>anomaly detection, blockchain analytics, smart contract debugging, cryptographic forensics, pattern recognition</t>
+          <t>anomaly detection, blockchain analytics, smart contract debugging, cryptographic forensics, resolution</t>
         </is>
       </c>
       <c r="J80" t="n">
@@ -12812,7 +12824,7 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>keep:1, "Blockchain Anomaly Resolution":4, "Blockchain Anomaly Problem Solving":2</t>
+          <t>keep:2, "Blockchain Anomaly Resolution":4, "Blockchain Anomaly Problem Solving":1</t>
         </is>
       </c>
       <c r="Z80" t="b">
@@ -12820,13 +12832,9 @@
       </c>
       <c r="AA80" t="inlineStr"/>
       <c r="AB80" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Foundation Skill describes problem‑solving capability already embedded in other skills and PCs; it is a work style rather than a distinct task</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC80" t="inlineStr"/>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -12840,7 +12848,7 @@
         </is>
       </c>
       <c r="AH80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI80" t="inlineStr">
         <is>
@@ -12848,7 +12856,7 @@
         </is>
       </c>
       <c r="AJ80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -12887,12 +12895,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Establishes blockchain objectives, purpose and requirements according to organisational needs.</t>
+          <t>Establishes blockchain objectives and requirements according to organisational needs in hybrid environments.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>distributed ledger, use‑case definition, stakeholder analysis, smart contract design, governance frameworks</t>
+          <t>distributed ledger, use‑case definition, stakeholder analysis, smart contract design, blockchain objectives</t>
         </is>
       </c>
       <c r="J81" t="n">
@@ -13004,7 +13012,7 @@
         </is>
       </c>
       <c r="AJ81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -13043,12 +13051,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Implements consensus mechanisms by configuring and deploying required system components.</t>
+          <t>Implements consensus mechanisms by implementing required system components.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>blockchain, distributed ledger, consensus algorithms, peer‑to‑peer networking, Byzantine fault tolerance</t>
+          <t>blockchain, distributed ledger, consensus algorithms, consensus mechanism, Byzantine fault tolerance</t>
         </is>
       </c>
       <c r="J82" t="n">
@@ -13152,7 +13160,7 @@
         </is>
       </c>
       <c r="AH82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
@@ -13160,7 +13168,7 @@
         </is>
       </c>
       <c r="AJ82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -13199,7 +13207,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Produces detailed design documentation aligned with organisational requirements to support project delivery.</t>
+          <t>Designs and documents detailed design documentation to plan project delivery according to organisational requirements.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -13308,7 +13316,7 @@
         </is>
       </c>
       <c r="AH83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI83" t="inlineStr">
         <is>
@@ -13355,12 +13363,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Submits documentation for review, seeks feedback and incorporates approved amendments.</t>
+          <t>Submits documentation, seeks feedback and incorporates approved amendments.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>record‑keeping, feedback loops, compliance, workflow approvals, electronic filing</t>
+          <t>record‑keeping, feedback loops, compliance, workflow approvals, documentation submission</t>
         </is>
       </c>
       <c r="J84" t="n">
@@ -13464,7 +13472,7 @@
         </is>
       </c>
       <c r="AH84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI84" t="inlineStr">
         <is>
@@ -13472,7 +13480,7 @@
         </is>
       </c>
       <c r="AJ84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -13511,12 +13519,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Designs integration workflow according to organisational need.</t>
+          <t>Designs integration workflows to meet organisational needs.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>systems integration, workflow orchestration, process automation, ETL, API middleware</t>
+          <t>systems integration, workflow orchestration, process automation, ETL, design integration workflow</t>
         </is>
       </c>
       <c r="J85" t="n">
@@ -13628,7 +13636,7 @@
         </is>
       </c>
       <c r="AJ85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -13667,12 +13675,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Develops and records maintenance schedules aligned with equipment requirements and timelines.</t>
+          <t>Determines and documents maintenance schedules aligned with equipment requirements and timelines.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>preventive maintenance, asset management, CMMS, work order scheduling, reliability engineering</t>
+          <t>preventive maintenance, asset management, CMMS, work order scheduling, maintenance schedule</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -13776,7 +13784,7 @@
         </is>
       </c>
       <c r="AH86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI86" t="inlineStr">
         <is>
@@ -13784,7 +13792,7 @@
         </is>
       </c>
       <c r="AJ86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -13803,7 +13811,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Maintenance Testing</t>
+          <t>Maintenance Testing Execution</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -13823,12 +13831,12 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Plans, selects and conducts maintenance tests to verify equipment functionality and compliance.</t>
+          <t>Determines and conducts maintenance tests to ensure equipment functionality and compliance.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>preventive maintenance, maintenance tests, equipment inspection, reliability testing, compliance standards</t>
+          <t>preventive maintenance, test procedures, equipment inspection, reliability testing, execution</t>
         </is>
       </c>
       <c r="J87" t="n">
@@ -13900,19 +13908,15 @@
         </is>
       </c>
       <c r="V87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W87" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 5/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>keep:2, "Maintenance Testing":5</t>
+          <t>keep:4, "Maintenance Testing":3</t>
         </is>
       </c>
       <c r="Z87" t="b">
@@ -13936,7 +13940,7 @@
         </is>
       </c>
       <c r="AH87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
@@ -13983,12 +13987,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Selects security platforms for blockchain solutions based on risk assessments.</t>
+          <t>Determines security platforms for blockchain solutions based on risk assessments.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>blockchain, security architecture, platform evaluation, cryptography, risk assessment</t>
+          <t>blockchain, security architecture, platform evaluation, cryptography, selection</t>
         </is>
       </c>
       <c r="J88" t="n">
@@ -14100,7 +14104,7 @@
         </is>
       </c>
       <c r="AJ88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -14139,12 +14143,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Executes smart command in required platform according to blockchain solution.</t>
+          <t>Executes smart contracts on approved blockchain platforms in line with solution specifications.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>blockchain, Ethereum, Solidity, decentralised applications, Web3</t>
+          <t>blockchain, Ethereum, Solidity, smart contract, Web3</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -14256,7 +14260,7 @@
         </is>
       </c>
       <c r="AJ89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -14300,7 +14304,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>blockchain, smart contracts, Solidity, distributed ledger, performance scaling</t>
+          <t>blockchain, smart contracts, Solidity, distributed ledger, debugging</t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -14412,7 +14416,7 @@
         </is>
       </c>
       <c r="AJ90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -14456,7 +14460,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>benchmarking, requirements compliance, load testing, service level agreements, performance metrics</t>
+          <t>benchmarking, requirements compliance, load testing, service level agreements, solution performance</t>
         </is>
       </c>
       <c r="J91" t="n">
@@ -14568,7 +14572,7 @@
         </is>
       </c>
       <c r="AJ91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -14612,7 +14616,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>stakeholder engagement, requirements gathering, industry terminology, verbal communication, active listening</t>
+          <t>stakeholder engagement, requirements gathering, industry terminology, verbal communication, oral communication</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -14724,7 +14728,7 @@
         </is>
       </c>
       <c r="AJ92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -14763,7 +14767,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Identifies organisational use case according to organisational needs.</t>
+          <t>Identify organisational use cases aligned with business needs.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -14919,12 +14923,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Ingests data logs into analytics platforms as instructed to support monitoring and analysis.</t>
+          <t>Ingests data logs into analytics platforms as instructed.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>data ingestion, log analytics, ETL pipelines, analytic platform, data logs</t>
+          <t>data ingestion, log analytics, ETL pipelines, analytic platform, user instructions</t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -15039,7 +15043,7 @@
         </is>
       </c>
       <c r="AH94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI94" t="inlineStr">
         <is>
@@ -15091,7 +15095,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>regulatory compliance, legislation, policy analysis, threat intelligence, risk assessment</t>
+          <t>regulatory compliance, legislation, policy analysis, threat intelligence, requirement identification</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -15210,7 +15214,7 @@
         </is>
       </c>
       <c r="AJ95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -15249,12 +15253,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Examines datasets to identify, document and resolve data discrepancies and inconsistencies.</t>
+          <t>Detects and describes discrepancies and inconsistencies in data.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>data validation, anomaly detection, data quality, data auditing, profiling</t>
+          <t>data validation, anomaly detection, data quality, data discrepancy, data auditing</t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -15361,7 +15365,7 @@
         </is>
       </c>
       <c r="AH96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI96" t="inlineStr">
         <is>
@@ -15369,7 +15373,7 @@
         </is>
       </c>
       <c r="AJ96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -15413,7 +15417,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>log analysis, data ingestion, dataset creation, security monitoring, data governance</t>
+          <t>log analysis, data ingestion, security monitoring, data governance, dataset creation</t>
         </is>
       </c>
       <c r="J97" t="n">
@@ -15575,12 +15579,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Reviews test results to identify and correct false positives and false negatives.</t>
+          <t>Checks false positives and false negatives.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>false positives, false negatives, type I error, anomaly detection, precision‑recall analysis</t>
+          <t>type I error, false positives, false negatives, anomaly detection, precision‑recall analysis</t>
         </is>
       </c>
       <c r="J98" t="n">
@@ -15695,7 +15699,7 @@
         </is>
       </c>
       <c r="AH98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI98" t="inlineStr">
         <is>
@@ -15821,7 +15825,7 @@
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X99" t="inlineStr"/>
       <c r="Y99" t="inlineStr">
@@ -15897,12 +15901,12 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Suggests and confirms lessons learned, action steps, recommendations and mitigation strategies with required personnel.</t>
+          <t>Suggests and confirms mitigation strategies, action steps and lessons learned with relevant personnel.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>risk management, lessons learned, action planning, stakeholder engagement, mitigation planning</t>
+          <t>risk management, lessons learned, action planning, stakeholder engagement, recommendation</t>
         </is>
       </c>
       <c r="J100" t="n">
@@ -16021,7 +16025,7 @@
         </is>
       </c>
       <c r="AJ100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -16060,12 +16064,12 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Assesses threats by evaluating likelihood and impact to prioritise risk mitigation actions.</t>
+          <t>Assesses threats by discussing likelihood and impact of risks.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>risk assessment, threat modelling, likelihood of occurrence, impact evaluation, cyber threats</t>
+          <t>risk assessment, probability analysis, threat modelling, impact evaluation, risk matrices</t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -16176,7 +16180,7 @@
         </is>
       </c>
       <c r="AH101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI101" t="inlineStr">
         <is>
@@ -16184,7 +16188,7 @@
         </is>
       </c>
       <c r="AJ101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -16228,7 +16232,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>cyber security, network security, asset inventories, IDS, firewalls</t>
+          <t>cyber security, network security, asset inventories, equipment, firewalls</t>
         </is>
       </c>
       <c r="J102" t="n">
@@ -16343,7 +16347,7 @@
         </is>
       </c>
       <c r="AJ102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -16382,7 +16386,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Ingests data logs into an analytic platform according to user instructions.</t>
+          <t>Ingests security logs into analytics platforms according to user instructions.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -16545,12 +16549,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Communicates threat findings through structured discussions and reviews with relevant personnel.</t>
+          <t>Discusses and reviews threat findings with relevant personnel.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>stakeholder engagement, threat intelligence, risk reporting, data briefings, cyber security communication</t>
+          <t>stakeholder engagement, threat intelligence, risk reporting, data briefings, findings</t>
         </is>
       </c>
       <c r="J104" t="n">
@@ -16628,12 +16632,12 @@
         <v>0</v>
       </c>
       <c r="W104" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X104" t="inlineStr"/>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>keep:4, "Threat Findings Communication":3</t>
+          <t>keep:6, "Threat Findings Communication":1</t>
         </is>
       </c>
       <c r="Z104" t="b">
@@ -16657,7 +16661,7 @@
         </is>
       </c>
       <c r="AH104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI104" t="inlineStr">
         <is>
@@ -16665,7 +16669,7 @@
         </is>
       </c>
       <c r="AJ104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -16704,12 +16708,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Collects alerts, logs and event data and creates a dataset in accordance with organisational data policies.</t>
+          <t>Collects and structures alerts, logs and event data in accordance with organisational data policies.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>threat intelligence, log analysis, SIEM, incident response, security monitoring</t>
+          <t>threat intelligence, log analysis, SIEM, incident response, data collection</t>
         </is>
       </c>
       <c r="J105" t="n">
@@ -16820,7 +16824,7 @@
         </is>
       </c>
       <c r="AH105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI105" t="inlineStr">
         <is>
@@ -16828,7 +16832,7 @@
         </is>
       </c>
       <c r="AJ105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -16867,12 +16871,12 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Monitors operational data to detect contextual anomalies and resolves deviations in a timely manner.</t>
+          <t>Identifies contextual anomalies and resolves deviations in a timely manner.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>outlier analysis, root‑cause analysis, statistical process control, monitoring and diagnostics</t>
+          <t>anomaly detection, troubleshooting, outlier analysis, root‑cause analysis, statistical process control</t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -16973,7 +16977,7 @@
         </is>
       </c>
       <c r="AH106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI106" t="inlineStr">
         <is>
@@ -16981,7 +16985,7 @@
         </is>
       </c>
       <c r="AJ106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -17020,7 +17024,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Implements additional protection plan requirements and asset management processes to safeguard assets.</t>
+          <t>Implements enhanced protection plan requirements and asset management processes to safeguard assets.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -17126,7 +17130,7 @@
         </is>
       </c>
       <c r="AH107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI107" t="inlineStr">
         <is>
@@ -17173,12 +17177,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Researches the organisation's need for critical infrastructure protection and documents findings according to organisational requirements.</t>
+          <t>Researches critical infrastructure to document protection planning and documentation requirements.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>infrastructure protection, risk assessment, threat modelling, resilience analysis, policy compliance</t>
+          <t>infrastructure protection, risk assessment, threat modelling, resilience analysis, critical infrastructure protection</t>
         </is>
       </c>
       <c r="J108" t="n">
@@ -17287,7 +17291,7 @@
         </is>
       </c>
       <c r="AJ108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -17326,12 +17330,12 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Executes scheduled data backups in line with organisational policies and procedures.</t>
+          <t>Backs up data according to organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>disaster recovery, backup software, data retention policies, storage replication, ICT compliance</t>
+          <t>disaster recovery, backup software, data retention policies, storage replication, execution</t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -17432,7 +17436,7 @@
         </is>
       </c>
       <c r="AH109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI109" t="inlineStr">
         <is>
@@ -17440,7 +17444,7 @@
         </is>
       </c>
       <c r="AJ109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -17479,7 +17483,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Implements device security controls in accordance with protection plans and technical specifications.</t>
+          <t>Plans device security controls in accordance with protection plans and technical specifications.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -17585,7 +17589,7 @@
         </is>
       </c>
       <c r="AH110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI110" t="inlineStr">
         <is>
@@ -17632,7 +17636,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Submits protection plan to required personnel and seeks and responds to feedback.</t>
+          <t>Submits protection plans and seeks and responds to feedback.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -17785,12 +17789,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Implements network segmentation according to the protection plan and technical requirements.</t>
+          <t>Implements network segmentation to isolate security zones in line with approved protection plans.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>VLANs, firewall policies, micro‑segmentation, zero‑trust architecture, network security zones</t>
+          <t>VLANs, firewall policies, micro‑segmentation, zero‑trust architecture, deployment</t>
         </is>
       </c>
       <c r="J112" t="n">
@@ -17891,7 +17895,7 @@
         </is>
       </c>
       <c r="AH112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI112" t="inlineStr">
         <is>
@@ -17899,7 +17903,7 @@
         </is>
       </c>
       <c r="AJ112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -17938,12 +17942,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Develops staged operational plans and regularly reviews priorities and performance during execution.</t>
+          <t>Develops staged operational detail and regularly reviews priorities and performance during execution.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>operational planning, performance monitoring, resource allocation, timeline management, Gantt charts</t>
+          <t>operational planning, performance monitoring, resource allocation, timeline management, project coordination</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -18032,7 +18036,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>FS describes work style (planning and coordinating) rather than a distinct task; capability already embedded in strategy development PCs</t>
+          <t>FS describes work style (planning and coordinating operational detail) rather than a distinct task; capability is already embedded in strategy development and implementation PCs</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -18048,7 +18052,7 @@
         </is>
       </c>
       <c r="AH113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
@@ -18056,7 +18060,7 @@
         </is>
       </c>
       <c r="AJ113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -18095,12 +18099,12 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Analyses existing critical infrastructure protection plan to identify gaps and recommend improvements.</t>
+          <t>Analyses critical infrastructure protection plans and plans improvements.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>critical infrastructure, risk assessment, cyber security resilience, ISO 27001, vulnerability analysis</t>
+          <t>critical infrastructure, risk assessment, cyber security resilience, protection plan, vulnerability analysis</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -18172,12 +18176,12 @@
         <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>0.9428571428571428</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X114" t="inlineStr"/>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Critical Infrastructure Protection Analysis":1</t>
         </is>
       </c>
       <c r="Z114" t="b">
@@ -18209,7 +18213,7 @@
         </is>
       </c>
       <c r="AJ114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -18248,12 +18252,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Develops and records critical infrastructure protection plans aligned with organisational policies and procedures.</t>
+          <t>Develops and documents critical infrastructure protection plans according to organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>critical infrastructure, risk assessment, security policy compliance, business continuity planning, incident response frameworks</t>
+          <t>critical infrastructure, risk assessment, security policy compliance, business continuity planning, protection plan</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -18354,7 +18358,7 @@
         </is>
       </c>
       <c r="AH115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI115" t="inlineStr">
         <is>
@@ -18362,7 +18366,7 @@
         </is>
       </c>
       <c r="AJ115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -18401,12 +18405,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Tests deployment of protection plan according to organisational policies and procedures.</t>
+          <t>Plans and tests protection plan deployment in line with organisational policies and procedures.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>protection plan, test deployment, security policies, compliance testing, vulnerability testing</t>
+          <t>cyber security, risk assessment, compliance testing, security policies, protection plan</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -18558,12 +18562,12 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Collects and analyses test results according to organisational policies and procedures.</t>
+          <t>Analyses results for decision‑making purposes.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>data interpretation, performance metrics, compliance reporting, organisational standards, business intelligence</t>
+          <t>data interpretation, performance metrics, compliance reporting, organisational standards, results</t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -18672,7 +18676,7 @@
         </is>
       </c>
       <c r="AJ117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -18711,7 +18715,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Evaluates protection, vulnerability, risk and mitigation levels aligned with organisational requirements.</t>
+          <t>Determines protection, vulnerability, risk and mitigation levels according to organisational requirements.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -18793,7 +18797,7 @@
       <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>keep:4, "Risk Assessment":2, "Risk Evaluation":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z118" t="b">
@@ -18864,12 +18868,12 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Installs software updates in line with documented technical specifications.</t>
+          <t>Applies software patches in line with documented technical specifications.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>patch management, vulnerability remediation, update deployment, configuration management, WSUS</t>
+          <t>patch management, vulnerability remediation, update deployment, configuration management, software patches</t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -18978,7 +18982,7 @@
         </is>
       </c>
       <c r="AJ119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -19170,7 +19174,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Establishes all data types to be included in security architecture.</t>
+          <t>Establishes data types to inform security architecture requirements.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -19257,12 +19261,12 @@
         <v>0</v>
       </c>
       <c r="W121" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X121" t="inlineStr"/>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Data Type Identification":1</t>
         </is>
       </c>
       <c r="Z121" t="b">
@@ -19338,7 +19342,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>documentation, stakeholder communication, feedback loops, record‑keeping, internal reporting</t>
+          <t>documentation, stakeholder communication, feedback loops, record‑keeping, response</t>
         </is>
       </c>
       <c r="J122" t="n">
@@ -19453,7 +19457,7 @@
         </is>
       </c>
       <c r="AJ122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -19492,12 +19496,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Researches industry‑standard design methodologies to inform security architecture planning.</t>
+          <t>Researches and identifies industry‑standard design methodologies to inform security architecture planning.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>security architecture, design methodologies, industry standards, security frameworks, risk assessment</t>
+          <t>security architecture, design methodologies, industry standards, security frameworks, methodology</t>
         </is>
       </c>
       <c r="J123" t="n">
@@ -19608,7 +19612,7 @@
         </is>
       </c>
       <c r="AJ123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -19647,12 +19651,12 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Applies contextual awareness to identify security anomalies and deviations from standard operating patterns.</t>
+          <t>Uses contextual awareness to recognise security anomalies and subtle deviations from normal expectations.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>anomaly detection, pattern recognition, situational awareness, context analysis, subtle deviations</t>
+          <t>anomaly detection, threat analysis, security monitoring, pattern recognition, contextual awareness</t>
         </is>
       </c>
       <c r="J124" t="n">
@@ -19738,12 +19742,12 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>keep:0, "Contextual Anomaly Identification/Security Anomaly Identification":6, "Security Contextual Problem Solving":1</t>
+          <t>keep:0, "Contextual Anomaly Identification":4, "Security Contextual Problem Solving":2, "Contextual Anomaly Detection":1</t>
         </is>
       </c>
       <c r="Z124" t="b">
@@ -19767,7 +19771,7 @@
         </is>
       </c>
       <c r="AH124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI124" t="inlineStr">
         <is>
@@ -19814,12 +19818,12 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Documents security architecture findings and confirms them with relevant personnel.</t>
+          <t>Documents security architecture findings with relevant personnel.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>security architecture, security requirements, documentation, compliance frameworks, ISO 27001</t>
+          <t>security architecture, risk assessment, compliance frameworks, ISO 27001, security requirements documentation</t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -19906,7 +19910,7 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>keep:0, "Security Requirements Documentation":7</t>
+          <t>keep:0, "Security Findings Documentation/Security Requirements Documentation":7</t>
         </is>
       </c>
       <c r="Z125" t="b">
@@ -19977,12 +19981,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Delivers documented security architecture presentations for stakeholder engagement.</t>
+          <t>Documents and presents security architecture for stakeholder engagement.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>information security, enterprise architecture, risk assessment, security frameworks, technical presentations</t>
+          <t>information security, enterprise architecture, security frameworks, technical presentations, security architecture</t>
         </is>
       </c>
       <c r="J126" t="n">
@@ -20097,7 +20101,7 @@
         </is>
       </c>
       <c r="AJ126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -20136,12 +20140,12 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Demonstrates security design utilising major industry‑standard design methodologies.</t>
+          <t>Demonstrates security design using industry‑recognised methodologies.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>security architecture, threat modelling, NIST framework, ISO 27001, risk assessment</t>
+          <t>security architecture, threat modelling, NIST framework, ISO 27001, validation</t>
         </is>
       </c>
       <c r="J127" t="n">
@@ -20256,7 +20260,7 @@
         </is>
       </c>
       <c r="AJ127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -20295,12 +20299,12 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Determines required security level, perimeters, features and protection mode.</t>
+          <t>Determines required security levels, perimeters, features and protection modes for assets.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>risk assessment, access control, security architecture, perimeter security, security policy</t>
+          <t>risk assessment, access control, security architecture, security level, security policy</t>
         </is>
       </c>
       <c r="J128" t="n">
@@ -20419,7 +20423,7 @@
         </is>
       </c>
       <c r="AJ128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -20458,7 +20462,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Develops staged operational plans for security initiatives and reviews progress during delivery.</t>
+          <t>Develops operational detail in stages and reviews priorities and performance during implementation.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -20545,7 +20549,7 @@
         <v>0</v>
       </c>
       <c r="W129" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X129" t="inlineStr"/>
       <c r="Y129" t="inlineStr">
@@ -20578,7 +20582,7 @@
         </is>
       </c>
       <c r="AH129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI129" t="inlineStr">
         <is>
@@ -20780,12 +20784,12 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Designs and documents security solutions according to organisational requirements.</t>
+          <t>Designs and documents security solutions according to organisational standards and requirements.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>cyber security architecture, risk assessment, security compliance, solution documentation, threat modelling</t>
+          <t>cyber security architecture, risk assessment, security compliance, solution documentation, design</t>
         </is>
       </c>
       <c r="J131" t="n">
@@ -20904,7 +20908,7 @@
         </is>
       </c>
       <c r="AJ131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -21106,12 +21110,12 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Reviews technical, manufacturer and organisational documentation to confirm job requirements prior to work commencement.</t>
+          <t>Interprets technical, manufacturer and organisational documentation to determine job requirements prior to work commencement.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>technical documentation, manufacturer manuals, job requirement analysis, engineering drawings, documentation reading</t>
+          <t>technical documentation, specification standards, manufacturer manuals, job requirement analysis, reading</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -21226,7 +21230,7 @@
         </is>
       </c>
       <c r="AH133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI133" t="inlineStr">
         <is>
@@ -21273,12 +21277,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Works autonomously, making high‑level decisions to achieve and improve organisational goals.</t>
+          <t>Makes independent strategic decisions to improve performance.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>autonomy, strategic decision‑making, self‑management, leadership, organisational performance</t>
+          <t>autonomy, strategic decision‑making, self‑management, leadership, autonomous decision making</t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -21414,7 +21418,7 @@
         </is>
       </c>
       <c r="AJ134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -21453,12 +21457,12 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Develops procedures for collecting and protecting forensic evidence during incident response.</t>
+          <t>Develops procedures for collecting and protecting forensic evidence to preserve data during incident response.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>chain of custody, evidence preservation, incident response, digital forensics tools, crime scene documentation</t>
+          <t>chain of custody, evidence preservation, incident response, digital forensics tools, forensic collection</t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -21586,7 +21590,7 @@
         </is>
       </c>
       <c r="AJ135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -21625,7 +21629,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Documents security incident response and actions according to task requirements.</t>
+          <t>Documents detailed incident reports of response actions against task requirements.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -21793,12 +21797,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Evaluates incident response plans for effectiveness across hybrid operating environments.</t>
+          <t>Assesses and documents the efficiency and effectiveness of incident response plans across hybrid operating environments.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>incident response plan, post‑incident analysis, efficiency metrics, response plan documentation, security operations</t>
+          <t>security operations, post‑incident analysis, efficiency metrics, incident response plan, SOC tools</t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -21889,16 +21893,16 @@
         <v>1</v>
       </c>
       <c r="W137" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>keep:2, "Incident Response Plan Evaluation":5</t>
+          <t>keep:0, "Incident Response Plan Evaluation":7</t>
         </is>
       </c>
       <c r="Z137" t="b">
@@ -21922,7 +21926,7 @@
         </is>
       </c>
       <c r="AH137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI137" t="inlineStr">
         <is>
@@ -21969,12 +21973,12 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Develops and records incident response plans aligned with organisational requirements.</t>
+          <t>Develops and documents incident response plans according to organisational requirements.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>cyber security, incident handling, NIST framework, playbook development, risk management</t>
+          <t>cyber security, incident handling, incident response plan, playbook development, risk management</t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -22094,7 +22098,7 @@
         </is>
       </c>
       <c r="AH138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI138" t="inlineStr">
         <is>
@@ -22102,7 +22106,7 @@
         </is>
       </c>
       <c r="AJ138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -22141,7 +22145,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Identifies and documents incident response team services according to organisational requirements.</t>
+          <t>Identifies and documents incident response team roles and services according to organisational requirements.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -22309,12 +22313,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Creates incident response exercises, red‑team activities, and defines staffing and training requirements.</t>
+          <t>Creates incident response exercises, red‑team activities, staffing and training requirements.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>incident response exercises, red-teaming activities, incident response planning, security training programmes, MITRE ATT&amp;CK framework</t>
+          <t>adversary simulation, incident response planning, threat modelling, security training programmes, incident response exercises</t>
         </is>
       </c>
       <c r="J140" t="n">
@@ -22405,16 +22409,16 @@
         <v>1</v>
       </c>
       <c r="W140" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>keep:0, "Incident Response Exercise Design":5, "Incident Response Training":2</t>
+          <t>keep:0, "Incident Response Exercise Design":7</t>
         </is>
       </c>
       <c r="Z140" t="b">
@@ -22657,12 +22661,12 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Interprets and documents numerical and technical system data to support risk assessment.</t>
+          <t>Interprets and documents numerical and technical system data to inform risk assessment.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>technical data interpretation, quantitative analysis, system modelling, data documentation, numerical data</t>
+          <t>quantitative analysis, technical data interpretation, system modelling, data documentation, technical system data</t>
         </is>
       </c>
       <c r="J142" t="n">
@@ -22766,7 +22770,7 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>keep:1, "Technical Data Interpretation/Data Interpretation":6</t>
+          <t>keep:1, "Technical Data Interpretation":6</t>
         </is>
       </c>
       <c r="Z142" t="b">
@@ -22794,7 +22798,7 @@
         </is>
       </c>
       <c r="AH142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI142" t="inlineStr">
         <is>
@@ -22841,12 +22845,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Executes incident response actions in accordance with approved incident response plans.</t>
+          <t>Applies incident response actions in accordance with approved incident response plans.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>incident response, security operations centres, SIEM, playbook execution, forensic analysis</t>
+          <t>incident response, security operations centres, SIEM, playbook execution, handling</t>
         </is>
       </c>
       <c r="J143" t="n">
@@ -22970,7 +22974,7 @@
         </is>
       </c>
       <c r="AH143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI143" t="inlineStr">
         <is>
@@ -22978,7 +22982,7 @@
         </is>
       </c>
       <c r="AJ143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -23017,12 +23021,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Develops and documents incident management policies aligned with organisational specifications.</t>
+          <t>Develops and documents incident management policies according to organisational specifications.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>incident management, risk assessment, governance, compliance, ISO 27001</t>
+          <t>incident management, risk assessment, governance, compliance, policy</t>
         </is>
       </c>
       <c r="J144" t="n">
@@ -23146,7 +23150,7 @@
         </is>
       </c>
       <c r="AH144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI144" t="inlineStr">
         <is>
@@ -23154,7 +23158,7 @@
         </is>
       </c>
       <c r="AJ144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -23193,12 +23197,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Interprets, analyses and documents numerical and technical system data</t>
+          <t>Analyses and records numerical system data to inform technical decision‑making.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>quantitative analysis, technical system data, measurement instrumentation, data documentation, engineering diagnostics</t>
+          <t>quantitative analysis, technical system data, data documentation, engineering diagnostics, interpretation</t>
         </is>
       </c>
       <c r="J145" t="n">
@@ -23326,7 +23330,7 @@
         </is>
       </c>
       <c r="AH145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI145" t="inlineStr">
         <is>
@@ -23334,7 +23338,7 @@
         </is>
       </c>
       <c r="AJ145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -23373,7 +23377,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Assesses system impacts on business continuity to identify risks and mitigation strategies.</t>
+          <t>Evaluates system impacts on business continuity to determine risks and mitigation strategies.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -23491,7 +23495,7 @@
         </is>
       </c>
       <c r="AH146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI146" t="inlineStr">
         <is>
@@ -23538,7 +23542,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Develops and implements strategies to ensure organisational policies, procedures and regulatory requirements are met</t>
+          <t>Develops and implements compliance strategies to ensure organisational processes meet regulatory requirements.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -23644,7 +23648,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>FS describes work style/strategic compliance activity already implicit in other skills and not a distinct task for this unit</t>
+          <t>FS describes work style/strategic compliance rather than a distinct unit task; capability is implicit in other skills and PCs</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -23707,12 +23711,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Develops contingency plans that identify threats.</t>
+          <t>Develops contingency plans by identifying threats and defining response actions.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>risk assessment, business continuity, threat identification, mitigation strategies, scenario analysis</t>
+          <t>risk assessment, business continuity, threat identification, mitigation strategies, contingency planning</t>
         </is>
       </c>
       <c r="J148" t="n">
@@ -23833,7 +23837,7 @@
         </is>
       </c>
       <c r="AH148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI148" t="inlineStr">
         <is>
@@ -23841,7 +23845,7 @@
         </is>
       </c>
       <c r="AJ148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -23880,12 +23884,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Evaluates prevention and recovery options against business specifications and cost constraints.</t>
+          <t>Evaluates prevention and recovery options for compliance and cost effectiveness.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>cost‑benefit analysis, budgeting, risk assessment, business case evaluation, financial modelling</t>
+          <t>cost‑benefit analysis, budgeting, risk assessment, business case evaluation, cost constraints</t>
         </is>
       </c>
       <c r="J149" t="n">
@@ -23998,7 +24002,7 @@
         </is>
       </c>
       <c r="AH149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI149" t="inlineStr">
         <is>
@@ -24006,7 +24010,7 @@
         </is>
       </c>
       <c r="AJ149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -24045,7 +24049,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Develops disaster recovery plan.</t>
+          <t>Develops comprehensive disaster recovery plans detailing procedures, resources and recovery timeframes.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -24134,7 +24138,7 @@
         <v>0</v>
       </c>
       <c r="W150" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X150" t="inlineStr"/>
       <c r="Y150" t="inlineStr">
@@ -24167,7 +24171,7 @@
         </is>
       </c>
       <c r="AH150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI150" t="inlineStr">
         <is>
@@ -24214,12 +24218,12 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Reviews operational procedures against industry benchmarks to verify risk controls.</t>
+          <t>Reviews operational procedures against industry standards and checks required risk safeguards.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>compliance, risk management, standard operating procedures, regulatory guidance, audit</t>
+          <t>compliance, risk management, industry standards, standard operating procedures, regulatory guidance</t>
         </is>
       </c>
       <c r="J151" t="n">
@@ -24332,7 +24336,7 @@
         </is>
       </c>
       <c r="AH151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI151" t="inlineStr">
         <is>
@@ -24340,7 +24344,7 @@
         </is>
       </c>
       <c r="AJ151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -24379,12 +24383,12 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Analyses and documents numerical, financial and technical data to support operational decisions.</t>
+          <t>Analyses, interprets and documents numerical, financial and technical data to inform operational decisions.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>quantitative analysis, financial modelling, technical data interpretation, data reporting, business data analysis</t>
+          <t>quantitative analysis, financial modelling, technical data interpretation, statistical methods, business data analysis</t>
         </is>
       </c>
       <c r="J152" t="n">
@@ -24501,7 +24505,7 @@
         </is>
       </c>
       <c r="AH152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI152" t="inlineStr">
         <is>
@@ -24548,12 +24552,12 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Formulates prevention and recovery strategy to strengthen system resilience.</t>
+          <t>Formulates prevention and recovery strategies to strengthen system resilience.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>risk assessment, mitigation planning, contingency strategies, recovery planning, scenario analysis</t>
+          <t>risk assessment, mitigation planning, contingency strategies, recovery planning, prevention</t>
         </is>
       </c>
       <c r="J153" t="n">
@@ -24678,7 +24682,7 @@
         </is>
       </c>
       <c r="AJ153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -24717,12 +24721,12 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Collects and analyses data, incorporates feedback and refines plans and processes.</t>
+          <t>Gathers and analyses data, seeks feedback and plans processes.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>data analysis, feedback loops, process improvement, root‑cause analysis, continuous improvement</t>
+          <t>data analysis, feedback loops, process improvement, root‑cause analysis, problem solving</t>
         </is>
       </c>
       <c r="J154" t="n">
@@ -24810,7 +24814,7 @@
         <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>0.9142857142857144</v>
+        <v>0.95</v>
       </c>
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="inlineStr">
@@ -24843,7 +24847,7 @@
         </is>
       </c>
       <c r="AH154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI154" t="inlineStr">
         <is>
@@ -24851,7 +24855,7 @@
         </is>
       </c>
       <c r="AJ154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -24890,7 +24894,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Conducts risk analysis and develops disaster recovery and contingency solutions.</t>
+          <t>Carries out risk analysis, disaster recovery and contingency planning.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -25200,7 +25204,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Strategic Planning</t>
+          <t>Priority Planning</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -25220,12 +25224,12 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Develops and aligns hybrid work priorities and outcomes through structured strategic planning.</t>
+          <t>Demonstrates hybrid work priorities and outcomes through structured strategic planning.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>priority alignment, outcome mapping, roadmap development, performance metrics, scenario analysis</t>
+          <t>priority alignment, outcome mapping, strategic planning, performance metrics, scenario analysis</t>
         </is>
       </c>
       <c r="J157" t="n">
@@ -25306,15 +25310,19 @@
         </is>
       </c>
       <c r="V157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W157" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X157" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 6/7: </t>
+        </is>
+      </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>keep:4, "Priority Planning":2, "Strategy Prioritisation":1</t>
+          <t>keep:1, "Priority Planning":6</t>
         </is>
       </c>
       <c r="Z157" t="b">
@@ -25326,7 +25334,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Foundation Skill describes a work style (strategic planning) that is already embedded in other skills and PCs</t>
+          <t>Foundation Skill describes work style (strategic planning) already embedded in other skills and PCs</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -25342,7 +25350,7 @@
         </is>
       </c>
       <c r="AH157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI157" t="inlineStr">
         <is>
@@ -25350,7 +25358,7 @@
         </is>
       </c>
       <c r="AJ157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -25389,12 +25397,12 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Collaborates with team members using communication tools and strategies to maintain effective working relationships.</t>
+          <t>Maintains effective working relationships with team members using communication tools and strategies.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>communication tools, relationship building, stakeholder engagement, collaboration platforms, interpersonal communication</t>
+          <t>communication tools, relationship building, stakeholder engagement, collaboration platforms, team</t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -25507,7 +25515,7 @@
         </is>
       </c>
       <c r="AH158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI158" t="inlineStr">
         <is>
@@ -25515,7 +25523,7 @@
         </is>
       </c>
       <c r="AJ158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -25559,7 +25567,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>specification drafting, process documentation, evaluation reporting, strategic articulation, document control</t>
+          <t>specification drafting, process documentation, evaluation reporting, strategic articulation, technical writing</t>
         </is>
       </c>
       <c r="J159" t="n">
@@ -25680,7 +25688,7 @@
         </is>
       </c>
       <c r="AJ159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
@@ -25719,7 +25727,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Evaluates system threats.</t>
+          <t>Evaluates system vulnerabilities through structured threat identification and analysis to facilitate mitigation planning.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -25808,7 +25816,7 @@
         <v>0</v>
       </c>
       <c r="W160" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X160" t="inlineStr"/>
       <c r="Y160" t="inlineStr">
@@ -25886,12 +25894,12 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Provides clear, evidence‑based answers to queries, supporting statements with relevant data and reasoning.</t>
+          <t>Provides clear, evidence‑based answers to queries, with each response including relevant data or rationale.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>evidence based answers, substantiated responses, query handling, data support, reasoning justification</t>
+          <t>substantiated responses, evidence based answers, query handling, data support, rationale provision</t>
         </is>
       </c>
       <c r="J161" t="n">
@@ -25982,19 +25990,19 @@
       </c>
       <c r="AG161" t="inlineStr">
         <is>
-          <t>Provides clear, evidence‑based answers to queries, supporting statements with relevant data and reasoning.</t>
+          <t>Provides clear, evidence‑based answers to queries, supporting each response with relevant data or rationale.</t>
         </is>
       </c>
       <c r="AH161" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>evidence based answers, substantiated responses, query handling, data support, reasoning justification</t>
+          <t>evidence based answers, substantiated responses, query handling, data support, rationale provision</t>
         </is>
       </c>
       <c r="AJ161" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -26021,7 +26029,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>ASSIST</t>
+          <t>APPLY</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -26031,12 +26039,12 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Confirms and documents the types of information stored on each registered digital device.</t>
+          <t>Confirm the types of information stored on each registered digital device for security purposes.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, registered devices, data mapping, asset documentation</t>
+          <t>device data inventory, information classification, data mapping, asset documentation, registered devices</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -26127,7 +26135,7 @@
       </c>
       <c r="AG162" t="inlineStr">
         <is>
-          <t>Assists in confirming and documenting the types of information stored on each registered digital device.</t>
+          <t>Identify and document the types of information stored on each registered digital device for security purposes.</t>
         </is>
       </c>
       <c r="AH162" t="b">
@@ -26135,7 +26143,7 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, data mapping, asset documentation, digital records</t>
+          <t>device data inventory, information classification, data mapping, asset documentation, security baseline</t>
         </is>
       </c>
       <c r="AJ162" t="b">
@@ -26176,16 +26184,16 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
+          <t>Secures final approval from designated personnel by confirming required documentation.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>sign‑off management, approval process, stakeholder engagement, compliance confirmation, final sign‑off</t>
+          <t>approval process, stakeholder engagement, documentation review, final sign‑off, coordination</t>
         </is>
       </c>
       <c r="J163" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -26249,7 +26257,7 @@
         <v>0</v>
       </c>
       <c r="W163" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="X163" t="inlineStr">
         <is>
@@ -26274,19 +26282,19 @@
       </c>
       <c r="AG163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
+          <t>Secures final approval from designated personnel by organising, presenting, and confirming required documentation.</t>
         </is>
       </c>
       <c r="AH163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>approval process, stakeholder engagement, compliance confirmation, sign‑off management, finalisation</t>
+          <t>approval process, stakeholder engagement, documentation review, final sign‑off, coordination</t>
         </is>
       </c>
       <c r="AJ163" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -26323,16 +26331,16 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Identifies organisational processes and transaction types suitable for blockchain technology and determines relevant legislation, policies and procedures and their impact on the solution.</t>
+          <t>Identifies organisational processes and transaction types and determines relevant legislation, policies and procedures to assess their suitability for blockchain implementation.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>process evaluation, transaction analysis, blockchain suitability, organisational assessment, compliance impact</t>
+          <t>process analysis, transaction evaluation, blockchain suitability, regulatory compliance, transactional types</t>
         </is>
       </c>
       <c r="J164" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -26404,7 +26412,7 @@
         <v>0</v>
       </c>
       <c r="W164" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="X164" t="inlineStr">
         <is>
@@ -26429,7 +26437,7 @@
       </c>
       <c r="AG164" t="inlineStr">
         <is>
-          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation.</t>
+          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation, considering relevant legislation and policies.</t>
         </is>
       </c>
       <c r="AH164" t="b">
@@ -26437,11 +26445,11 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>process evaluation, transaction analysis, blockchain suitability, organisational assessment, compliance impact</t>
+          <t>process analysis, transaction evaluation, blockchain suitability, regulatory compliance, organisational policy</t>
         </is>
       </c>
       <c r="AJ164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -26458,7 +26466,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Data Log Strategy Discussion</t>
+          <t>Log Requirement Consultation</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -26478,12 +26486,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Discusses and confirms data log requirements and processing strategies with relevant personnel.</t>
+          <t>Discusses data log requirements and processing strategy with relevant personnel.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>data log requirements, data log strategy, personnel coordination, discussion facilitation, requirement confirmation</t>
+          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, collaborative discussion</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -26542,7 +26550,7 @@
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>Data Log Strategy Discussion</t>
+          <t>Log Requirement Consultation</t>
         </is>
       </c>
       <c r="V165" t="b">
@@ -26574,7 +26582,7 @@
       </c>
       <c r="AG165" t="inlineStr">
         <is>
-          <t>Facilitates discussions with relevant personnel to confirm data log requirements and processing strategies.</t>
+          <t>Facilitates discussion with relevant personnel to confirm data log requirements and processing strategy.</t>
         </is>
       </c>
       <c r="AH165" t="b">
@@ -26582,11 +26590,11 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel coordination, discussion facilitation, requirement confirmation</t>
+          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, collaborative discussion</t>
         </is>
       </c>
       <c r="AJ165" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -26623,12 +26631,12 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Obtains and analyses results to ensure reliability and consistency across multiple sources and tools.</t>
+          <t>Analyses results for reliability and consistency before further processing.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>reliability assessment, consistency verification, data validation, result evaluation, reliability analysis</t>
+          <t>reliability assessment, consistency verification, data validation, result evaluation, results findings</t>
         </is>
       </c>
       <c r="J166" t="n">
@@ -26719,7 +26727,7 @@
       </c>
       <c r="AG166" t="inlineStr">
         <is>
-          <t>Evaluates gathered threat data results to ensure reliability and consistency across multiple sources and tools.</t>
+          <t>Evaluates gathered threat data results to ensure reliability and consistency before further processing.</t>
         </is>
       </c>
       <c r="AH166" t="b">
@@ -26768,12 +26776,12 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Evaluates how well the current protection plan meets organisational needs and regulatory standards.</t>
+          <t>Determines how well the current protection plan meets organisational needs and regulatory requirements, and identifies operational systems, critical assets, segmentation and legislative requirements.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>plan effectiveness, organisational requirements, critical assets, legislative compliance, operational systems</t>
+          <t>plan effectiveness, organisational alignment, regulatory compliance, critical assets, operational systems</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -26871,19 +26879,19 @@
       </c>
       <c r="AG167" t="inlineStr">
         <is>
-          <t>Evaluates how well the current protection plan meets organisational needs and regulatory standards.</t>
+          <t>Evaluates how well the current protection plan meets organisational needs and regulatory requirements.</t>
         </is>
       </c>
       <c r="AH167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>plan effectiveness, organisational requirements, alignment assessment, critical assets, legislative compliance</t>
+          <t>plan effectiveness, organisational alignment, regulatory compliance, critical assets, operational systems</t>
         </is>
       </c>
       <c r="AJ167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -26900,12 +26908,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Incident Plan Alignment</t>
+          <t>Incident Alignment Documentation</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>DOMAIN_KNOWLEDGE</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -26915,17 +26923,17 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>THEORETICAL</t>
+          <t>PRACTICAL</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Determines the alignment of the current incident response plan with identified requirements, documents the findings, submits the documentation to required personnel, and seeks and responds to feedback.</t>
+          <t>Determines and documents the alignment of the current incident response plan with requirements, and submits the documentation to required personnel while seeking feedback.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment analysis, documentation, requirements mapping, feedback response</t>
+          <t>incident response plan, alignment analysis, documentation, requirements mapping, incident response documentation</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -26998,7 +27006,7 @@
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>Incident Plan Alignment</t>
+          <t>Incident Alignment Documentation</t>
         </is>
       </c>
       <c r="V168" t="b">
@@ -27030,7 +27038,7 @@
       </c>
       <c r="AG168" t="inlineStr">
         <is>
-          <t>Analyzes the current incident response plan, documents its alignment with requirements, and submits it for feedback.</t>
+          <t>Aligns the current incident response plan with requirements and documents the comparison for stakeholders.</t>
         </is>
       </c>
       <c r="AH168" t="b">
@@ -27038,7 +27046,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment analysis, documentation, requirements mapping, feedback submission</t>
+          <t>incident response plan, alignment analysis, documentation, requirements mapping, stakeholder feedback</t>
         </is>
       </c>
       <c r="AJ168" t="b">
@@ -27079,16 +27087,16 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing, and preserving evidence in line with organisational and legal requirements.</t>
+          <t>Assist in gathering, processing, and securely preserving evidence in line with specified incident response requirements.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, forensic evidence, legislative requirements</t>
+          <t>evidence collection, evidence processing, evidence preservation, forensic evidence, incident response</t>
         </is>
       </c>
       <c r="J169" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -27163,7 +27171,7 @@
         <v>0</v>
       </c>
       <c r="W169" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="X169" t="inlineStr">
         <is>
@@ -27188,7 +27196,7 @@
       </c>
       <c r="AG169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing, and preserving evidence in line with organisational and legal requirements.</t>
+          <t>Assist in gathering, processing, and securely preserving evidence in line with specified incident response requirements.</t>
         </is>
       </c>
       <c r="AH169" t="b">
@@ -27196,7 +27204,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, incident response, legal compliance</t>
+          <t>evidence collection, evidence processing, evidence preservation, incident response, assistance</t>
         </is>
       </c>
       <c r="AJ169" t="b">
@@ -27237,12 +27245,12 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Identify essential business functions, data, and software, and assess ICT risk impacts on them.</t>
+          <t>Identifies essential business functions, critical data, and software, and evaluates risk impacts on ICT systems.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>business critical functions, security environment, critical data, software assets, business risk</t>
+          <t>business critical functions, security environment, critical data, software assets, function</t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -27341,7 +27349,7 @@
       </c>
       <c r="AG170" t="inlineStr">
         <is>
-          <t>Identify essential business functions, data, and software, and assess ICT risk impacts on them.</t>
+          <t>Identifies essential business functions, critical data, and software, and evaluates risk impacts on ICT systems.</t>
         </is>
       </c>
       <c r="AH170" t="b">
@@ -27349,7 +27357,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>business critical functions, security environment, critical data, software assets, ICT risk assessment</t>
+          <t>business critical functions, security environment, critical data, software assets, risk impact assessment</t>
         </is>
       </c>
       <c r="AJ170" t="b">
@@ -27390,12 +27398,12 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Creates and records detailed disaster strategy processes, cut‑over criteria, and secures final task sign‑off.</t>
+          <t>Identifies and documents disaster strategy processes, identifies required cut‑over criteria and plans, and obtains final task sign‑off.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>disaster strategy, process documentation, cut‑over criteria, task sign‑off, disaster strategy processes</t>
+          <t>disaster strategy, process documentation, cut‑over criteria, task sign‑off, disaster recovery plan</t>
         </is>
       </c>
       <c r="J171" t="n">
@@ -27498,7 +27506,7 @@
         </is>
       </c>
       <c r="AH171" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI171" t="inlineStr">
         <is>
